--- a/nas_bench_201_experiments/gvae/training_metrics_CIFAR10.xlsx
+++ b/nas_bench_201_experiments/gvae/training_metrics_CIFAR10.xlsx
@@ -480,28 +480,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1214.541868649414</v>
+        <v>2829.698616421875</v>
       </c>
       <c r="C2" t="n">
-        <v>3.805249834075928</v>
+        <v>4.209622672821045</v>
       </c>
       <c r="D2" t="n">
-        <v>1.495007352867126</v>
+        <v>1.286140682806015</v>
       </c>
       <c r="E2" t="n">
-        <v>1210.729129974609</v>
+        <v>2825.482628662109</v>
       </c>
       <c r="F2" t="n">
-        <v>176.0929451434336</v>
+        <v>330.1222347250809</v>
       </c>
       <c r="G2" t="n">
-        <v>2.694449186838471</v>
+        <v>3.616067743472524</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3907683831988112</v>
+        <v>0.2200801106990842</v>
       </c>
       <c r="I2" t="n">
-        <v>173.3965406468253</v>
+        <v>326.5050675807536</v>
       </c>
     </row>
     <row r="3">
@@ -509,28 +509,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>60.823107640625</v>
+        <v>142.899214376709</v>
       </c>
       <c r="C3" t="n">
-        <v>1.924742109046936</v>
+        <v>2.899441441070556</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2905405248527527</v>
+        <v>0.136955597486496</v>
       </c>
       <c r="E3" t="n">
-        <v>58.89691311639405</v>
+        <v>139.9990872416992</v>
       </c>
       <c r="F3" t="n">
-        <v>9.172598784479387</v>
+        <v>33.14607781638912</v>
       </c>
       <c r="G3" t="n">
-        <v>1.617104682766788</v>
+        <v>2.181138876857415</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2522445905733653</v>
+        <v>0.07271475783666234</v>
       </c>
       <c r="I3" t="n">
-        <v>7.554232888369537</v>
+        <v>30.96457563689638</v>
       </c>
     </row>
     <row r="4">
@@ -538,28 +538,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>5.614221283340454</v>
+        <v>12.41168791061401</v>
       </c>
       <c r="C4" t="n">
-        <v>1.606007071548462</v>
+        <v>1.732522409896851</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4354937023544311</v>
+        <v>0.06836840230321885</v>
       </c>
       <c r="E4" t="n">
-        <v>4.006036712688446</v>
+        <v>10.6788236153717</v>
       </c>
       <c r="F4" t="n">
-        <v>14.81842453457208</v>
+        <v>3.200705068410902</v>
       </c>
       <c r="G4" t="n">
-        <v>1.597601846131765</v>
+        <v>1.611800336339929</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6106061103565658</v>
+        <v>0.0653490529344288</v>
       </c>
       <c r="I4" t="n">
-        <v>13.21776951981213</v>
+        <v>1.588577971131728</v>
       </c>
     </row>
     <row r="5">
@@ -567,28 +567,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.104978771484375</v>
+        <v>2.278641802459717</v>
       </c>
       <c r="C5" t="n">
-        <v>1.58091146912384</v>
+        <v>1.60315927456665</v>
       </c>
       <c r="D5" t="n">
-        <v>0.518207572265625</v>
+        <v>0.1314532008295059</v>
       </c>
       <c r="E5" t="n">
-        <v>2.52147625112915</v>
+        <v>0.6748252634447515</v>
       </c>
       <c r="F5" t="n">
-        <v>1.726412806347572</v>
+        <v>1.604569298104789</v>
       </c>
       <c r="G5" t="n">
-        <v>1.542865806380454</v>
+        <v>1.590187376708424</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4292166126280002</v>
+        <v>0.1421884035548806</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1814009287899898</v>
+        <v>0.01367097766058091</v>
       </c>
     </row>
     <row r="6">
@@ -596,28 +596,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2.214123746582031</v>
+        <v>2.100968530914307</v>
       </c>
       <c r="C6" t="n">
-        <v>1.503206331542969</v>
+        <v>1.55460174092102</v>
       </c>
       <c r="D6" t="n">
-        <v>0.458499192615509</v>
+        <v>0.1418426569414139</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7086248921203613</v>
+        <v>0.5456576077438593</v>
       </c>
       <c r="F6" t="n">
-        <v>1.438587687859527</v>
+        <v>1.550459633659188</v>
       </c>
       <c r="G6" t="n">
-        <v>1.419661162712446</v>
+        <v>1.513156667642453</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4580647431326146</v>
+        <v>0.1719507875148857</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01663617806591179</v>
+        <v>0.03644320952464472</v>
       </c>
     </row>
     <row r="7">
@@ -625,28 +625,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.604524566223144</v>
+        <v>1.651511676956177</v>
       </c>
       <c r="C7" t="n">
-        <v>1.359714469238281</v>
+        <v>1.433867741729736</v>
       </c>
       <c r="D7" t="n">
-        <v>0.573598526851654</v>
+        <v>0.2263250950984955</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2419421111822128</v>
+        <v>0.2165123108334541</v>
       </c>
       <c r="F7" t="n">
-        <v>1.295243488633808</v>
+        <v>1.472333734397204</v>
       </c>
       <c r="G7" t="n">
-        <v>1.262592032861943</v>
+        <v>1.37520833573178</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6138321917442086</v>
+        <v>0.3193896747705015</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02958229277835973</v>
+        <v>0.09552843465258597</v>
       </c>
     </row>
     <row r="8">
@@ -654,28 +654,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.385548761543274</v>
+        <v>1.426993190216064</v>
       </c>
       <c r="C8" t="n">
-        <v>1.224210997886658</v>
+        <v>1.281685873580933</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6663758378677368</v>
+        <v>0.3316302190208435</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1580058754118681</v>
+        <v>0.1436491640894413</v>
       </c>
       <c r="F8" t="n">
-        <v>1.55656489244682</v>
+        <v>1.236217895619826</v>
       </c>
       <c r="G8" t="n">
-        <v>1.163646304657953</v>
+        <v>1.202418554167568</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6256629960688642</v>
+        <v>0.3906393757943811</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3897902594091064</v>
+        <v>0.03184613493026567</v>
       </c>
     </row>
     <row r="9">
@@ -683,28 +683,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.184658949508667</v>
+        <v>1.245749489311218</v>
       </c>
       <c r="C9" t="n">
-        <v>1.066290513771057</v>
+        <v>1.127865677238464</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7087236853256226</v>
+        <v>0.4018709621105194</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1148248108143806</v>
+        <v>0.1158744682674408</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9863390321249285</v>
+        <v>1.341397999301431</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9328786916250505</v>
+        <v>1.148911194816888</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8238780664814238</v>
+        <v>0.4832886889941541</v>
       </c>
       <c r="I9" t="n">
-        <v>0.04934094757109054</v>
+        <v>0.1900703509732911</v>
       </c>
     </row>
     <row r="10">
@@ -712,28 +712,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.9725011850891113</v>
+        <v>1.039186649623871</v>
       </c>
       <c r="C10" t="n">
-        <v>0.883746832244873</v>
+        <v>0.954121156074524</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8038132775802612</v>
+        <v>0.4879699144821167</v>
       </c>
       <c r="E10" t="n">
-        <v>0.08473528798782826</v>
+        <v>0.08262564628505707</v>
       </c>
       <c r="F10" t="n">
-        <v>1.022218395181815</v>
+        <v>1.037225621427253</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9490973225542227</v>
+        <v>0.9223179142743495</v>
       </c>
       <c r="H10" t="n">
-        <v>0.921814117342185</v>
+        <v>0.5168341865858479</v>
       </c>
       <c r="I10" t="n">
-        <v>0.06851200508011496</v>
+        <v>0.1123235617259587</v>
       </c>
     </row>
     <row r="11">
@@ -741,28 +741,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.8102298966979981</v>
+        <v>0.8678046284828186</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7097996659317016</v>
+        <v>0.7776542139549255</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9325698937225342</v>
+        <v>0.5816375133323669</v>
       </c>
       <c r="E11" t="n">
-        <v>0.09576738308143616</v>
+        <v>0.08724221681499481</v>
       </c>
       <c r="F11" t="n">
-        <v>0.64667933968502</v>
+        <v>0.6963354498527179</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6054314291652225</v>
+        <v>0.6531850198392573</v>
       </c>
       <c r="H11" t="n">
-        <v>1.047334040856478</v>
+        <v>0.6509198880623449</v>
       </c>
       <c r="I11" t="n">
-        <v>0.03601124605750376</v>
+        <v>0.03989581969419272</v>
       </c>
     </row>
     <row r="12">
@@ -770,28 +770,28 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.618551682352066</v>
+        <v>0.7211013138084411</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5437040363731385</v>
+        <v>0.6301271969585419</v>
       </c>
       <c r="D12" t="n">
-        <v>1.072563454063415</v>
+        <v>0.7254580606956482</v>
       </c>
       <c r="E12" t="n">
-        <v>0.06948482955932617</v>
+        <v>0.0873468188598156</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6314366847344751</v>
+        <v>0.7666528925071143</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5385567771474455</v>
+        <v>0.5670325716362498</v>
       </c>
       <c r="H12" t="n">
-        <v>1.10118529265312</v>
+        <v>0.7123533051904613</v>
       </c>
       <c r="I12" t="n">
-        <v>0.08737396956462455</v>
+        <v>0.1960585653266549</v>
       </c>
     </row>
     <row r="13">
@@ -799,28 +799,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5139607513656617</v>
+        <v>0.6005751844978332</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4167716212959289</v>
+        <v>0.4966997263488769</v>
       </c>
       <c r="D13" t="n">
-        <v>1.191364781242371</v>
+        <v>0.8487793091659546</v>
       </c>
       <c r="E13" t="n">
-        <v>0.09123230399250984</v>
+        <v>0.09963156293106079</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3795182989899914</v>
+        <v>0.417377758057238</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3205546320029223</v>
+        <v>0.3774571340546911</v>
       </c>
       <c r="H13" t="n">
-        <v>1.357294402534771</v>
+        <v>0.9357296453214586</v>
       </c>
       <c r="I13" t="n">
-        <v>0.05217719454287899</v>
+        <v>0.03524197400418425</v>
       </c>
     </row>
     <row r="14">
@@ -828,28 +828,28 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.4103350480289459</v>
+        <v>0.4734503971729279</v>
       </c>
       <c r="C14" t="n">
-        <v>0.324431022480011</v>
+        <v>0.3804008762626648</v>
       </c>
       <c r="D14" t="n">
-        <v>1.304055672195435</v>
+        <v>0.9460607755851745</v>
       </c>
       <c r="E14" t="n">
-        <v>0.07938374469637871</v>
+        <v>0.08831921589875222</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4694550324944843</v>
+        <v>0.4908945821412819</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3951363820722403</v>
+        <v>0.2996135416466494</v>
       </c>
       <c r="H14" t="n">
-        <v>1.353773701910483</v>
+        <v>0.923595534176072</v>
       </c>
       <c r="I14" t="n">
-        <v>0.06754978365065807</v>
+        <v>0.1866630612928755</v>
       </c>
     </row>
     <row r="15">
@@ -857,28 +857,28 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3595178721504211</v>
+        <v>0.4072033515701294</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2739468863019943</v>
+        <v>0.3090429863262176</v>
       </c>
       <c r="D15" t="n">
-        <v>1.362825844947815</v>
+        <v>1.019733646751404</v>
       </c>
       <c r="E15" t="n">
-        <v>0.07875685858726501</v>
+        <v>0.09306169778347015</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2592352065876685</v>
+        <v>0.2576058489560692</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2251178277122255</v>
+        <v>0.224247994497783</v>
       </c>
       <c r="H15" t="n">
-        <v>1.336390593709214</v>
+        <v>1.116250233595756</v>
       </c>
       <c r="I15" t="n">
-        <v>0.02743542030842619</v>
+        <v>0.02777660255647017</v>
       </c>
     </row>
     <row r="16">
@@ -886,28 +886,28 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.3101422896928787</v>
+        <v>0.334031101650238</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2365813731994629</v>
+        <v>0.2496975070886612</v>
       </c>
       <c r="D16" t="n">
-        <v>1.352616628837585</v>
+        <v>1.085087297584534</v>
       </c>
       <c r="E16" t="n">
-        <v>0.06679783410263061</v>
+        <v>0.07890815959775448</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3854453457704765</v>
+        <v>0.3909976814563279</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2863360977717364</v>
+        <v>0.3161634846437619</v>
       </c>
       <c r="H16" t="n">
-        <v>1.32226276050773</v>
+        <v>1.137581051792251</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0924979293759651</v>
+        <v>0.06914629521611075</v>
       </c>
     </row>
     <row r="17">
@@ -915,28 +915,28 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.2695275658569336</v>
+        <v>0.2917920146045685</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2005266415176392</v>
+        <v>0.2138838249406814</v>
       </c>
       <c r="D17" t="n">
-        <v>1.332577539054871</v>
+        <v>1.097956543380737</v>
       </c>
       <c r="E17" t="n">
-        <v>0.06233803725337982</v>
+        <v>0.07241840912008285</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1705357330016561</v>
+        <v>0.2167198207891785</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1439407110583724</v>
+        <v>0.1852843886312419</v>
       </c>
       <c r="H17" t="n">
-        <v>1.32625566891706</v>
+        <v>1.12337585652244</v>
       </c>
       <c r="I17" t="n">
-        <v>0.01996374476245235</v>
+        <v>0.02581855067785762</v>
       </c>
     </row>
     <row r="18">
@@ -944,28 +944,28 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.2277037254629135</v>
+        <v>0.2466543483963013</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1728887305755615</v>
+        <v>0.1813738663101196</v>
       </c>
       <c r="D18" t="n">
-        <v>1.292758416175842</v>
+        <v>1.092924616203308</v>
       </c>
       <c r="E18" t="n">
-        <v>0.04835120318102837</v>
+        <v>0.05981586048269272</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2701267065387371</v>
+        <v>0.2897476115370652</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1935418006160325</v>
+        <v>0.2081364768724068</v>
       </c>
       <c r="H18" t="n">
-        <v>1.285074859178864</v>
+        <v>1.061827612934455</v>
       </c>
       <c r="I18" t="n">
-        <v>0.07015953229652143</v>
+        <v>0.07630199569619305</v>
       </c>
     </row>
     <row r="19">
@@ -973,28 +973,28 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.1900635454206467</v>
+        <v>0.2183232340431213</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1427522611675262</v>
+        <v>0.1600530150289536</v>
       </c>
       <c r="D19" t="n">
-        <v>1.234225169509888</v>
+        <v>1.054112839241028</v>
       </c>
       <c r="E19" t="n">
-        <v>0.04114015858101844</v>
+        <v>0.0529996523885727</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1555012966738634</v>
+        <v>0.1516172613988693</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1202380670147658</v>
+        <v>0.1256167858897376</v>
       </c>
       <c r="H19" t="n">
-        <v>1.213241427500913</v>
+        <v>1.035356816280919</v>
       </c>
       <c r="I19" t="n">
-        <v>0.02919702370467233</v>
+        <v>0.02082369171046511</v>
       </c>
     </row>
     <row r="20">
@@ -1002,28 +1002,28 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.1592258638086319</v>
+        <v>0.1833904741258621</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1147277527856827</v>
+        <v>0.1348865144052505</v>
       </c>
       <c r="D20" t="n">
-        <v>1.159565597671509</v>
+        <v>1.028280436599731</v>
       </c>
       <c r="E20" t="n">
-        <v>0.03870028205657005</v>
+        <v>0.04336255882847309</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1546121607694113</v>
+        <v>0.1658815305384687</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1054258272489366</v>
+        <v>0.1187874650960062</v>
       </c>
       <c r="H20" t="n">
-        <v>1.045103813578993</v>
+        <v>1.014590467978846</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0439608169061422</v>
+        <v>0.04202111325684029</v>
       </c>
     </row>
     <row r="21">
@@ -1031,28 +1031,28 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.1313223268890381</v>
+        <v>0.1551310419826508</v>
       </c>
       <c r="C21" t="n">
-        <v>0.088548603682518</v>
+        <v>0.1097207639303207</v>
       </c>
       <c r="D21" t="n">
-        <v>1.131036696594238</v>
+        <v>0.9845005021743775</v>
       </c>
       <c r="E21" t="n">
-        <v>0.03711853976178169</v>
+        <v>0.04048777644395828</v>
       </c>
       <c r="F21" t="n">
-        <v>0.09028678213888824</v>
+        <v>0.1145396403158858</v>
       </c>
       <c r="G21" t="n">
-        <v>0.06730349621171858</v>
+        <v>0.08429200666958123</v>
       </c>
       <c r="H21" t="n">
-        <v>1.097365322424187</v>
+        <v>1.000355631562275</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0174964600713957</v>
+        <v>0.02524585561896712</v>
       </c>
     </row>
     <row r="22">
@@ -1060,28 +1060,28 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>0.1065401191139221</v>
+        <v>0.1283751298379898</v>
       </c>
       <c r="C22" t="n">
-        <v>0.06995898443436623</v>
+        <v>0.0896181292462349</v>
       </c>
       <c r="D22" t="n">
-        <v>1.058940071769714</v>
+        <v>0.957324460861206</v>
       </c>
       <c r="E22" t="n">
-        <v>0.03128643522047996</v>
+        <v>0.0339703791949749</v>
       </c>
       <c r="F22" t="n">
-        <v>0.09982189030962317</v>
+        <v>0.1201556448096358</v>
       </c>
       <c r="G22" t="n">
-        <v>0.04510738680792478</v>
+        <v>0.06588037338284061</v>
       </c>
       <c r="H22" t="n">
-        <v>1.041717811393116</v>
+        <v>0.9672445175037104</v>
       </c>
       <c r="I22" t="n">
-        <v>0.04950591511015597</v>
+        <v>0.0494390490096895</v>
       </c>
     </row>
     <row r="23">
@@ -1089,28 +1089,28 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>0.08839706643581391</v>
+        <v>0.1148774818797112</v>
       </c>
       <c r="C23" t="n">
-        <v>0.05192554076695442</v>
+        <v>0.07453029955625534</v>
       </c>
       <c r="D23" t="n">
-        <v>1.031899417984009</v>
+        <v>0.9282411042556763</v>
       </c>
       <c r="E23" t="n">
-        <v>0.03131202825856209</v>
+        <v>0.03570597656726837</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1271565733395432</v>
+        <v>0.1043339753598218</v>
       </c>
       <c r="G23" t="n">
-        <v>0.03688320776523618</v>
+        <v>0.06938979264597908</v>
       </c>
       <c r="H23" t="n">
-        <v>0.853160572417603</v>
+        <v>0.9254929740782858</v>
       </c>
       <c r="I23" t="n">
-        <v>0.08600756292825422</v>
+        <v>0.03031671888676592</v>
       </c>
     </row>
     <row r="24">
@@ -1118,28 +1118,28 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>0.07752804815292358</v>
+        <v>0.09647062932395935</v>
       </c>
       <c r="C24" t="n">
-        <v>0.04267861054301262</v>
+        <v>0.06177103912377357</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9961980665740967</v>
+        <v>0.9056298047599792</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0298684475171566</v>
+        <v>0.03017144153058529</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0861816093563839</v>
+        <v>0.08105967715261034</v>
       </c>
       <c r="G24" t="n">
-        <v>0.03245089899560172</v>
+        <v>0.04598951114891598</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8953813201179318</v>
+        <v>0.876561835236106</v>
       </c>
       <c r="I24" t="n">
-        <v>0.04925380422619777</v>
+        <v>0.03068735671228141</v>
       </c>
     </row>
     <row r="25">
@@ -1147,28 +1147,28 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>0.06600739983415603</v>
+        <v>0.08433647884941101</v>
       </c>
       <c r="C25" t="n">
-        <v>0.03287658333945274</v>
+        <v>0.04873157121515274</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9279551652183533</v>
+        <v>0.8790462491378784</v>
       </c>
       <c r="E25" t="n">
-        <v>0.02849104071581364</v>
+        <v>0.03120967710387707</v>
       </c>
       <c r="F25" t="n">
-        <v>0.04763528806398977</v>
+        <v>0.07111588633322988</v>
       </c>
       <c r="G25" t="n">
-        <v>0.02085326267530926</v>
+        <v>0.04762279788685467</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9735168756863033</v>
+        <v>0.8522503939927305</v>
       </c>
       <c r="I25" t="n">
-        <v>0.02191444114883708</v>
+        <v>0.01923183653230185</v>
       </c>
     </row>
     <row r="26">
@@ -1176,28 +1176,28 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>0.05474543625831604</v>
+        <v>0.0746732430100441</v>
       </c>
       <c r="C26" t="n">
-        <v>0.02664751319670677</v>
+        <v>0.03955415602648258</v>
       </c>
       <c r="D26" t="n">
-        <v>0.8898728830757141</v>
+        <v>0.8598348340835571</v>
       </c>
       <c r="E26" t="n">
-        <v>0.02364855898952484</v>
+        <v>0.03081991266059875</v>
       </c>
       <c r="F26" t="n">
-        <v>0.04241998011462062</v>
+        <v>0.06630797726878529</v>
       </c>
       <c r="G26" t="n">
-        <v>0.02025739091170456</v>
+        <v>0.03531017821701472</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8967958587573364</v>
+        <v>0.8601785369020496</v>
       </c>
       <c r="I26" t="n">
-        <v>0.01767860990011575</v>
+        <v>0.02669690660864941</v>
       </c>
     </row>
     <row r="27">
@@ -1205,28 +1205,28 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>0.04812633278167248</v>
+        <v>0.06111034177017212</v>
       </c>
       <c r="C27" t="n">
-        <v>0.02100158958232403</v>
+        <v>0.03036750496780872</v>
       </c>
       <c r="D27" t="n">
-        <v>0.8375436591644287</v>
+        <v>0.8140559975433349</v>
       </c>
       <c r="E27" t="n">
-        <v>0.02293702512800693</v>
+        <v>0.02667255628657341</v>
       </c>
       <c r="F27" t="n">
-        <v>0.05726188753012926</v>
+        <v>0.09180153255264288</v>
       </c>
       <c r="G27" t="n">
-        <v>0.03449023335102526</v>
+        <v>0.01945564430760034</v>
       </c>
       <c r="H27" t="n">
-        <v>0.8139775521409064</v>
+        <v>0.7656667154959326</v>
       </c>
       <c r="I27" t="n">
-        <v>0.01870176764396528</v>
+        <v>0.06851755488998156</v>
       </c>
     </row>
     <row r="28">
@@ -1234,28 +1234,28 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>0.04264451077115536</v>
+        <v>0.05438463150882721</v>
       </c>
       <c r="C28" t="n">
-        <v>0.01991694828262925</v>
+        <v>0.0261018169541359</v>
       </c>
       <c r="D28" t="n">
-        <v>0.7755898835678101</v>
+        <v>0.7778074256362915</v>
       </c>
       <c r="E28" t="n">
-        <v>0.01884961328065395</v>
+        <v>0.02439377768838406</v>
       </c>
       <c r="F28" t="n">
-        <v>0.05733501484790789</v>
+        <v>0.06099795796840071</v>
       </c>
       <c r="G28" t="n">
-        <v>0.008970503644990396</v>
+        <v>0.04366890367345359</v>
       </c>
       <c r="H28" t="n">
-        <v>0.7326772819063209</v>
+        <v>0.774524664334333</v>
       </c>
       <c r="I28" t="n">
-        <v>0.04470112432614819</v>
+        <v>0.0134564309452355</v>
       </c>
     </row>
     <row r="29">
@@ -1263,28 +1263,28 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>0.03922814948368072</v>
+        <v>0.04879491052532196</v>
       </c>
       <c r="C29" t="n">
-        <v>0.01459116272234917</v>
+        <v>0.02075458095669746</v>
       </c>
       <c r="D29" t="n">
-        <v>0.7158098342819214</v>
+        <v>0.7493258737831116</v>
       </c>
       <c r="E29" t="n">
-        <v>0.02105793756687641</v>
+        <v>0.02429370027399063</v>
       </c>
       <c r="F29" t="n">
-        <v>0.03326764423685789</v>
+        <v>0.05355648368548414</v>
       </c>
       <c r="G29" t="n">
-        <v>0.01222766778743286</v>
+        <v>0.02690930340518084</v>
       </c>
       <c r="H29" t="n">
-        <v>0.7143592467743655</v>
+        <v>0.7038863855162802</v>
       </c>
       <c r="I29" t="n">
-        <v>0.01746818085479114</v>
+        <v>0.02312774820657383</v>
       </c>
     </row>
     <row r="30">
@@ -1292,28 +1292,28 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>0.03228606251478195</v>
+        <v>0.04393622764015197</v>
       </c>
       <c r="C30" t="n">
-        <v>0.01001686516037583</v>
+        <v>0.0174347329941392</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6541318928031922</v>
+        <v>0.7006719835510254</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0189985380859375</v>
+        <v>0.02299813508009911</v>
       </c>
       <c r="F30" t="n">
-        <v>0.04696436565326827</v>
+        <v>0.04723550480545831</v>
       </c>
       <c r="G30" t="n">
-        <v>0.01992131570035054</v>
+        <v>0.01048905333227571</v>
       </c>
       <c r="H30" t="n">
-        <v>0.6648241206716752</v>
+        <v>0.6752590357654441</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0237189290384484</v>
+        <v>0.03337015640045263</v>
       </c>
     </row>
     <row r="31">
@@ -1321,28 +1321,28 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>0.02885154506874085</v>
+        <v>0.03755404525756836</v>
       </c>
       <c r="C31" t="n">
-        <v>0.008992667819350958</v>
+        <v>0.01340363625359535</v>
       </c>
       <c r="D31" t="n">
-        <v>0.6063257937316895</v>
+        <v>0.6510425229949951</v>
       </c>
       <c r="E31" t="n">
-        <v>0.01682724844014645</v>
+        <v>0.02089519657254219</v>
       </c>
       <c r="F31" t="n">
-        <v>0.03582794240355297</v>
+        <v>0.02844248881675971</v>
       </c>
       <c r="G31" t="n">
-        <v>0.01462747574976811</v>
+        <v>0.004745590255746153</v>
       </c>
       <c r="H31" t="n">
-        <v>0.5954497151118118</v>
+        <v>0.6435177262572247</v>
       </c>
       <c r="I31" t="n">
-        <v>0.01822321835267213</v>
+        <v>0.02047931025992793</v>
       </c>
     </row>
     <row r="32">
@@ -1350,28 +1350,28 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>0.02718002459275723</v>
+        <v>0.03337450854897499</v>
       </c>
       <c r="C32" t="n">
-        <v>0.01098608421258628</v>
+        <v>0.01037203907936811</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5571717702407837</v>
+        <v>0.6051939407348633</v>
       </c>
       <c r="E32" t="n">
-        <v>0.01340808169859648</v>
+        <v>0.01997649965250492</v>
       </c>
       <c r="F32" t="n">
-        <v>0.02689084345641961</v>
+        <v>0.02681035384778875</v>
       </c>
       <c r="G32" t="n">
-        <v>0.002488513704598995</v>
+        <v>0.005726385339760324</v>
       </c>
       <c r="H32" t="n">
-        <v>0.5045919972609541</v>
+        <v>0.5684807681648416</v>
       </c>
       <c r="I32" t="n">
-        <v>0.02187936959098447</v>
+        <v>0.01824156485583031</v>
       </c>
     </row>
     <row r="33">
@@ -1379,28 +1379,28 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>0.02318884317731857</v>
+        <v>0.02770763749527931</v>
       </c>
       <c r="C33" t="n">
-        <v>0.006513730818599462</v>
+        <v>0.009619382409572601</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4981473876667022</v>
+        <v>0.5550186683883667</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0141843756557703</v>
+        <v>0.01531316181111336</v>
       </c>
       <c r="F33" t="n">
-        <v>0.01683148424324942</v>
+        <v>0.03682306966083473</v>
       </c>
       <c r="G33" t="n">
-        <v>0.002660980755007457</v>
+        <v>0.004666821986139063</v>
       </c>
       <c r="H33" t="n">
-        <v>0.4848436267340941</v>
+        <v>0.4932026856661232</v>
       </c>
       <c r="I33" t="n">
-        <v>0.01174628556242629</v>
+        <v>0.02969023433646117</v>
       </c>
     </row>
     <row r="34">
@@ -1408,28 +1408,28 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>0.01876523024058342</v>
+        <v>0.02576371378159523</v>
       </c>
       <c r="C34" t="n">
-        <v>0.006074802087858319</v>
+        <v>0.007078635133862496</v>
       </c>
       <c r="D34" t="n">
-        <v>0.4674658675956726</v>
+        <v>0.5114336895179749</v>
       </c>
       <c r="E34" t="n">
-        <v>0.01035309895658493</v>
+        <v>0.01612791023090482</v>
       </c>
       <c r="F34" t="n">
-        <v>0.04832891982419456</v>
+        <v>0.0221653872964141</v>
       </c>
       <c r="G34" t="n">
-        <v>0.002417910121044001</v>
+        <v>0.006400754064759072</v>
       </c>
       <c r="H34" t="n">
-        <v>0.5055676838079829</v>
+        <v>0.4808337283270588</v>
       </c>
       <c r="I34" t="n">
-        <v>0.04338317166679641</v>
+        <v>0.01336046469141084</v>
       </c>
     </row>
     <row r="35">
@@ -1437,28 +1437,28 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>0.01854936226332188</v>
+        <v>0.02321203760528565</v>
       </c>
       <c r="C35" t="n">
-        <v>0.002589301167167723</v>
+        <v>0.006519515363574028</v>
       </c>
       <c r="D35" t="n">
-        <v>0.4341637420444489</v>
+        <v>0.4694226662521362</v>
       </c>
       <c r="E35" t="n">
-        <v>0.01378924244230986</v>
+        <v>0.01434540879386663</v>
       </c>
       <c r="F35" t="n">
-        <v>0.01915408706052463</v>
+        <v>0.03355997984721455</v>
       </c>
       <c r="G35" t="n">
-        <v>0.002363881965336461</v>
+        <v>0.003906060318609921</v>
       </c>
       <c r="H35" t="n">
-        <v>0.3990586950650612</v>
+        <v>0.4415124204361031</v>
       </c>
       <c r="I35" t="n">
-        <v>0.0147949116467992</v>
+        <v>0.02744635691103597</v>
       </c>
     </row>
     <row r="36">
@@ -1466,28 +1466,28 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>0.01810838118422031</v>
+        <v>0.02312908048796654</v>
       </c>
       <c r="C36" t="n">
-        <v>0.005994490381754935</v>
+        <v>0.008836727886058391</v>
       </c>
       <c r="D36" t="n">
-        <v>0.383195786359787</v>
+        <v>0.4345752161655426</v>
       </c>
       <c r="E36" t="n">
-        <v>0.01019791209805012</v>
+        <v>0.01211947658187151</v>
       </c>
       <c r="F36" t="n">
-        <v>0.01869719425553599</v>
+        <v>0.01947022922653067</v>
       </c>
       <c r="G36" t="n">
-        <v>0.003883008869276739</v>
+        <v>0.001762564033391425</v>
       </c>
       <c r="H36" t="n">
-        <v>0.3892550136467372</v>
+        <v>0.4082020714796387</v>
       </c>
       <c r="I36" t="n">
-        <v>0.01286791029855682</v>
+        <v>0.01566665479059515</v>
       </c>
     </row>
     <row r="37">
@@ -1495,28 +1495,28 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>0.01413600095587969</v>
+        <v>0.01783796822190285</v>
       </c>
       <c r="C37" t="n">
-        <v>0.001821649722740054</v>
+        <v>0.003246444691926241</v>
       </c>
       <c r="D37" t="n">
-        <v>0.355122678987503</v>
+        <v>0.3987300926704407</v>
       </c>
       <c r="E37" t="n">
-        <v>0.01053873793572187</v>
+        <v>0.01259787309479713</v>
       </c>
       <c r="F37" t="n">
-        <v>0.02238311048578866</v>
+        <v>0.0323290915855284</v>
       </c>
       <c r="G37" t="n">
-        <v>0.002409873515820255</v>
+        <v>0.002936860429545406</v>
       </c>
       <c r="H37" t="n">
-        <v>0.3362523679884962</v>
+        <v>0.3865400572235393</v>
       </c>
       <c r="I37" t="n">
-        <v>0.01829197504416375</v>
+        <v>0.02745953071066353</v>
       </c>
     </row>
     <row r="38">
@@ -1524,28 +1524,28 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>0.01548892236298323</v>
+        <v>0.01793717230057717</v>
       </c>
       <c r="C38" t="n">
-        <v>0.005716466460268944</v>
+        <v>0.004805244800329208</v>
       </c>
       <c r="D38" t="n">
-        <v>0.3211593762454987</v>
+        <v>0.3714289158630371</v>
       </c>
       <c r="E38" t="n">
-        <v>0.00816665902748704</v>
+        <v>0.01127478318491578</v>
       </c>
       <c r="F38" t="n">
-        <v>0.01231416600763944</v>
+        <v>0.03298760766281972</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0004566142543961202</v>
+        <v>0.02277125362859854</v>
       </c>
       <c r="H38" t="n">
-        <v>0.3060424158604266</v>
+        <v>0.3602618229894809</v>
       </c>
       <c r="I38" t="n">
-        <v>0.01032733975813935</v>
+        <v>0.008415044748313956</v>
       </c>
     </row>
     <row r="39">
@@ -1553,28 +1553,28 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>0.01317614325201511</v>
+        <v>0.01456737000203133</v>
       </c>
       <c r="C39" t="n">
-        <v>0.003818196210071444</v>
+        <v>0.002766948701262474</v>
       </c>
       <c r="D39" t="n">
-        <v>0.2983467050533294</v>
+        <v>0.3366108083229065</v>
       </c>
       <c r="E39" t="n">
-        <v>0.007866213455915452</v>
+        <v>0.01011736718553305</v>
       </c>
       <c r="F39" t="n">
-        <v>0.01981815042907029</v>
+        <v>0.02521711106182701</v>
       </c>
       <c r="G39" t="n">
-        <v>0.009455976136770178</v>
+        <v>0.001292566315234498</v>
       </c>
       <c r="H39" t="n">
-        <v>0.3067587302092821</v>
+        <v>0.3189810880945713</v>
       </c>
       <c r="I39" t="n">
-        <v>0.008828380609548015</v>
+        <v>0.02232963978782369</v>
       </c>
     </row>
     <row r="40">
@@ -1582,28 +1582,28 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>0.01399819090253115</v>
+        <v>0.01569318313825131</v>
       </c>
       <c r="C40" t="n">
-        <v>0.006091336330104619</v>
+        <v>0.004367683837726712</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2802593859481812</v>
+        <v>0.3120444354400635</v>
       </c>
       <c r="E40" t="n">
-        <v>0.006505557561665773</v>
+        <v>0.009765277401983737</v>
       </c>
       <c r="F40" t="n">
-        <v>0.01522308395248739</v>
+        <v>0.02064031923830898</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0005698109307549712</v>
+        <v>0.001055374167727376</v>
       </c>
       <c r="H40" t="n">
-        <v>0.2463783824550775</v>
+        <v>0.303902223954193</v>
       </c>
       <c r="I40" t="n">
-        <v>0.01342138111111245</v>
+        <v>0.01806543410735943</v>
       </c>
     </row>
     <row r="41">
@@ -1611,28 +1611,28 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>0.01123508670723438</v>
+        <v>0.01253401461523771</v>
       </c>
       <c r="C41" t="n">
-        <v>0.003421778706654906</v>
+        <v>0.001499737721677869</v>
       </c>
       <c r="D41" t="n">
-        <v>0.2617321978712082</v>
+        <v>0.2863470199871063</v>
       </c>
       <c r="E41" t="n">
-        <v>0.006504646909177303</v>
+        <v>0.009602541824638844</v>
       </c>
       <c r="F41" t="n">
-        <v>0.01834645740882316</v>
+        <v>0.01417477758719812</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0007784811280505218</v>
+        <v>0.001579324600953749</v>
       </c>
       <c r="H41" t="n">
-        <v>0.2450584304031307</v>
+        <v>0.2763505188578688</v>
       </c>
       <c r="I41" t="n">
-        <v>0.01634268425903351</v>
+        <v>0.01121370033724127</v>
       </c>
     </row>
     <row r="42">
@@ -1640,28 +1640,28 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>0.009306573443651199</v>
+        <v>0.01125692127966881</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0009732153538875282</v>
+        <v>0.001255226190820336</v>
       </c>
       <c r="D42" t="n">
-        <v>0.2484328872861862</v>
+        <v>0.264711246635437</v>
       </c>
       <c r="E42" t="n">
-        <v>0.007091193690478802</v>
+        <v>0.008678138888835908</v>
       </c>
       <c r="F42" t="n">
-        <v>0.01378501555962917</v>
+        <v>0.01959337356258761</v>
       </c>
       <c r="G42" t="n">
-        <v>0.001221609271486969</v>
+        <v>0.001474147617070955</v>
       </c>
       <c r="H42" t="n">
-        <v>0.2556876340367471</v>
+        <v>0.2518472483865978</v>
       </c>
       <c r="I42" t="n">
-        <v>0.01128496822759776</v>
+        <v>0.01685998966081788</v>
       </c>
     </row>
     <row r="43">
@@ -1669,28 +1669,28 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>0.01190390253019333</v>
+        <v>0.01193574571931362</v>
       </c>
       <c r="C43" t="n">
-        <v>0.005195795804023743</v>
+        <v>0.003558390390865505</v>
       </c>
       <c r="D43" t="n">
-        <v>0.2271595313930511</v>
+        <v>0.2468089034061432</v>
       </c>
       <c r="E43" t="n">
-        <v>0.005572309107631445</v>
+        <v>0.007143310841083527</v>
       </c>
       <c r="F43" t="n">
-        <v>0.02059533688873296</v>
+        <v>0.02289819074736917</v>
       </c>
       <c r="G43" t="n">
-        <v>0.01193372558607898</v>
+        <v>0.001267788738238688</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2341708767102943</v>
+        <v>0.2286492172034296</v>
       </c>
       <c r="I43" t="n">
-        <v>0.007490756806794427</v>
+        <v>0.02048715607984809</v>
       </c>
     </row>
     <row r="44">
@@ -1698,28 +1698,28 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>0.007891858940839767</v>
+        <v>0.009882484277963639</v>
       </c>
       <c r="C44" t="n">
-        <v>0.001092481497503817</v>
+        <v>0.001048522770553827</v>
       </c>
       <c r="D44" t="n">
-        <v>0.2175416523294449</v>
+        <v>0.2300481845989227</v>
       </c>
       <c r="E44" t="n">
-        <v>0.005711669165432453</v>
+        <v>0.007683720572650433</v>
       </c>
       <c r="F44" t="n">
-        <v>0.01187434212625221</v>
+        <v>0.01410663536246896</v>
       </c>
       <c r="G44" t="n">
-        <v>0.001630968978274522</v>
+        <v>0.00226822886777036</v>
       </c>
       <c r="H44" t="n">
-        <v>0.2364424281835945</v>
+        <v>0.2360647964992881</v>
       </c>
       <c r="I44" t="n">
-        <v>0.009061160866310897</v>
+        <v>0.01065808245441215</v>
       </c>
     </row>
     <row r="45">
@@ -1727,28 +1727,28 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>0.007217327287852764</v>
+        <v>0.008839043303608895</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0006330988323912024</v>
+        <v>0.001018965213149786</v>
       </c>
       <c r="D45" t="n">
-        <v>0.2065668535528183</v>
+        <v>0.2207197236948013</v>
       </c>
       <c r="E45" t="n">
-        <v>0.005551394206106662</v>
+        <v>0.006716479544252157</v>
       </c>
       <c r="F45" t="n">
-        <v>0.01031842427738436</v>
+        <v>0.01994083382250045</v>
       </c>
       <c r="G45" t="n">
-        <v>0.0004560902678152489</v>
+        <v>0.00151425614069576</v>
       </c>
       <c r="H45" t="n">
-        <v>0.2044985990189806</v>
+        <v>0.2042859669980178</v>
       </c>
       <c r="I45" t="n">
-        <v>0.008839840947682278</v>
+        <v>0.01740514786983878</v>
       </c>
     </row>
     <row r="46">
@@ -1756,28 +1756,28 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>0.007506955657184124</v>
+        <v>0.008754622764408589</v>
       </c>
       <c r="C46" t="n">
-        <v>0.001884134619109333</v>
+        <v>0.0008141576568558812</v>
       </c>
       <c r="D46" t="n">
-        <v>0.2049520360040665</v>
+        <v>0.2101550433120727</v>
       </c>
       <c r="E46" t="n">
-        <v>0.004598060866564512</v>
+        <v>0.006889689819067716</v>
       </c>
       <c r="F46" t="n">
-        <v>0.01334046461769846</v>
+        <v>0.01037454470736848</v>
       </c>
       <c r="G46" t="n">
-        <v>0.0004042909600047264</v>
+        <v>0.001059408230269495</v>
       </c>
       <c r="H46" t="n">
-        <v>0.1810402656155737</v>
+        <v>0.2043631356993468</v>
       </c>
       <c r="I46" t="n">
-        <v>0.01203097239088079</v>
+        <v>0.008293320773743689</v>
       </c>
     </row>
     <row r="47">
@@ -1785,28 +1785,28 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>0.006792582184672356</v>
+        <v>0.008411004809260368</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0007343005895614624</v>
+        <v>0.001106857921361923</v>
       </c>
       <c r="D47" t="n">
-        <v>0.1939705638904572</v>
+        <v>0.1980507969369888</v>
       </c>
       <c r="E47" t="n">
-        <v>0.005088428760677576</v>
+        <v>0.006313892864391208</v>
       </c>
       <c r="F47" t="n">
-        <v>0.04386683992202869</v>
+        <v>0.05724010434907179</v>
       </c>
       <c r="G47" t="n">
-        <v>0.03512275127952289</v>
+        <v>0.04934548271737908</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2111596016150703</v>
+        <v>0.2158754863970431</v>
       </c>
       <c r="I47" t="n">
-        <v>0.007688291444614846</v>
+        <v>0.006815244925905743</v>
       </c>
     </row>
     <row r="48">
@@ -1814,28 +1814,28 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>0.007324367795884609</v>
+        <v>0.008445852024585008</v>
       </c>
       <c r="C48" t="n">
-        <v>0.002055955704998225</v>
+        <v>0.002247326550103724</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1817502159910202</v>
+        <v>0.1868288736047745</v>
       </c>
       <c r="E48" t="n">
-        <v>0.004359661034747958</v>
+        <v>0.00526438109138608</v>
       </c>
       <c r="F48" t="n">
-        <v>0.008885941631867145</v>
+        <v>0.009008242665846235</v>
       </c>
       <c r="G48" t="n">
-        <v>0.0007777568464491024</v>
+        <v>0.0003366064073249765</v>
       </c>
       <c r="H48" t="n">
-        <v>0.1734852652983409</v>
+        <v>0.1882046264662828</v>
       </c>
       <c r="I48" t="n">
-        <v>0.007240758440738353</v>
+        <v>0.007730613138107355</v>
       </c>
     </row>
     <row r="49">
@@ -1843,28 +1843,28 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>0.006158254690915346</v>
+        <v>0.007041797049462796</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0005256291794553399</v>
+        <v>0.0005908925145771354</v>
       </c>
       <c r="D49" t="n">
-        <v>0.175275730509758</v>
+        <v>0.1814273012895584</v>
       </c>
       <c r="E49" t="n">
-        <v>0.00475624691811204</v>
+        <v>0.005543768016397953</v>
       </c>
       <c r="F49" t="n">
-        <v>0.01041677347805236</v>
+        <v>0.0101369302835905</v>
       </c>
       <c r="G49" t="n">
-        <v>0.0003823585965162444</v>
+        <v>0.0008561855202068257</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1755138065326856</v>
+        <v>0.1846160314230895</v>
       </c>
       <c r="I49" t="n">
-        <v>0.009156846015442156</v>
+        <v>0.008357664741891729</v>
       </c>
     </row>
     <row r="50">
@@ -1872,28 +1872,28 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>0.005653826912403107</v>
+        <v>0.009568115921050311</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0004401813838481903</v>
+        <v>0.003703861084342934</v>
       </c>
       <c r="D50" t="n">
-        <v>0.1684905392360687</v>
+        <v>0.1774260390625</v>
       </c>
       <c r="E50" t="n">
-        <v>0.004371192820638418</v>
+        <v>0.004977124469414353</v>
       </c>
       <c r="F50" t="n">
-        <v>0.0096534366099252</v>
+        <v>0.008711318071463661</v>
       </c>
       <c r="G50" t="n">
-        <v>0.0002688137568961859</v>
+        <v>0.0002723550801161603</v>
       </c>
       <c r="H50" t="n">
-        <v>0.1598178216401749</v>
+        <v>0.1693706230646634</v>
       </c>
       <c r="I50" t="n">
-        <v>0.008585533918858449</v>
+        <v>0.007592109954394826</v>
       </c>
     </row>
     <row r="51">
@@ -1901,28 +1901,28 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>0.005261177456974984</v>
+        <v>0.006395804050177336</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0004404234823845327</v>
+        <v>0.0005190154575575143</v>
       </c>
       <c r="D51" t="n">
-        <v>0.1616174089584351</v>
+        <v>0.1671913355283737</v>
       </c>
       <c r="E51" t="n">
-        <v>0.004012666959285736</v>
+        <v>0.00504083194771409</v>
       </c>
       <c r="F51" t="n">
-        <v>0.01030732112427715</v>
+        <v>0.01147860109222655</v>
       </c>
       <c r="G51" t="n">
-        <v>0.001013309573488793</v>
+        <v>0.0004932531690757515</v>
       </c>
       <c r="H51" t="n">
-        <v>0.1632806457197491</v>
+        <v>0.1585813387523468</v>
       </c>
       <c r="I51" t="n">
-        <v>0.008477608218825563</v>
+        <v>0.0101924413840057</v>
       </c>
     </row>
     <row r="52">
@@ -1930,28 +1930,28 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>0.006558535727292299</v>
+        <v>0.008774567217350007</v>
       </c>
       <c r="C52" t="n">
-        <v>0.002717744182312861</v>
+        <v>0.003690711890780367</v>
       </c>
       <c r="D52" t="n">
-        <v>0.1653992681903839</v>
+        <v>0.1641595370731354</v>
       </c>
       <c r="E52" t="n">
-        <v>0.003013795250236988</v>
+        <v>0.004263057569891215</v>
       </c>
       <c r="F52" t="n">
-        <v>0.008917658757084151</v>
+        <v>0.01057386229103385</v>
       </c>
       <c r="G52" t="n">
-        <v>0.0001528212897334062</v>
+        <v>0.0002116807874521548</v>
       </c>
       <c r="H52" t="n">
-        <v>0.1642398019774314</v>
+        <v>0.1579617267205315</v>
       </c>
       <c r="I52" t="n">
-        <v>0.007943638450607389</v>
+        <v>0.009572372908839199</v>
       </c>
     </row>
     <row r="53">
@@ -1959,28 +1959,28 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>0.008204851608723402</v>
+        <v>0.005334808741182089</v>
       </c>
       <c r="C53" t="n">
-        <v>0.004269428296392783</v>
+        <v>0.000432028359869495</v>
       </c>
       <c r="D53" t="n">
-        <v>0.1622046382255554</v>
+        <v>0.1531555536651611</v>
       </c>
       <c r="E53" t="n">
-        <v>0.003124400190606713</v>
+        <v>0.004137002643197775</v>
       </c>
       <c r="F53" t="n">
-        <v>0.009025708961362842</v>
+        <v>0.01084074634967484</v>
       </c>
       <c r="G53" t="n">
-        <v>0.0002839457374130684</v>
+        <v>0.001200139920081378</v>
       </c>
       <c r="H53" t="n">
-        <v>0.1506993084591715</v>
+        <v>0.1535406614925111</v>
       </c>
       <c r="I53" t="n">
-        <v>0.007988266672811443</v>
+        <v>0.008872903153835075</v>
       </c>
     </row>
     <row r="54">
@@ -1988,28 +1988,28 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>0.00478137601518631</v>
+        <v>0.00685195623087883</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0003995627345386893</v>
+        <v>0.001905091806488112</v>
       </c>
       <c r="D54" t="n">
-        <v>0.1530811142187118</v>
+        <v>0.1519282486124039</v>
       </c>
       <c r="E54" t="n">
-        <v>0.003616407711938024</v>
+        <v>0.004187223194822669</v>
       </c>
       <c r="F54" t="n">
-        <v>0.008324623972566442</v>
+        <v>0.007345210858066164</v>
       </c>
       <c r="G54" t="n">
-        <v>0.0005874146603056964</v>
+        <v>0.0002442015189454142</v>
       </c>
       <c r="H54" t="n">
-        <v>0.156633155663873</v>
+        <v>0.1602140373205477</v>
       </c>
       <c r="I54" t="n">
-        <v>0.006954043479803433</v>
+        <v>0.006299939174053137</v>
       </c>
     </row>
     <row r="55">
@@ -2017,28 +2017,28 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>0.004525409804344177</v>
+        <v>0.004877950332164764</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0004222285277098417</v>
+        <v>0.0003869372085779906</v>
       </c>
       <c r="D55" t="n">
-        <v>0.1508655811510086</v>
+        <v>0.1481495807247162</v>
       </c>
       <c r="E55" t="n">
-        <v>0.003348853434205055</v>
+        <v>0.003750265237629414</v>
       </c>
       <c r="F55" t="n">
-        <v>0.009453962509190667</v>
+        <v>0.0108505970925749</v>
       </c>
       <c r="G55" t="n">
-        <v>0.000496199164838875</v>
+        <v>0.0004050232101874472</v>
       </c>
       <c r="H55" t="n">
-        <v>0.1556768017005765</v>
+        <v>0.1507630560847324</v>
       </c>
       <c r="I55" t="n">
-        <v>0.008179379251966372</v>
+        <v>0.00969175859489653</v>
       </c>
     </row>
     <row r="56">
@@ -2046,28 +2046,28 @@
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>0.004300186196103692</v>
+        <v>0.005062714124202728</v>
       </c>
       <c r="C56" t="n">
-        <v>0.0003915814901068806</v>
+        <v>0.0004191560442000627</v>
       </c>
       <c r="D56" t="n">
-        <v>0.1493728618164062</v>
+        <v>0.1454851017599106</v>
       </c>
       <c r="E56" t="n">
-        <v>0.00316174037976563</v>
+        <v>0.003916132581055164</v>
       </c>
       <c r="F56" t="n">
-        <v>0.008080069709076968</v>
+        <v>0.008726427391548238</v>
       </c>
       <c r="G56" t="n">
-        <v>0.0005436418819215398</v>
+        <v>0.0006034487316675095</v>
       </c>
       <c r="H56" t="n">
-        <v>0.1598201273481375</v>
+        <v>0.1436304137922617</v>
       </c>
       <c r="I56" t="n">
-        <v>0.006737327169730262</v>
+        <v>0.007404826432466507</v>
       </c>
     </row>
     <row r="57">
@@ -2075,28 +2075,28 @@
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>0.004042321699172258</v>
+        <v>0.00472944397264719</v>
       </c>
       <c r="C57" t="n">
-        <v>0.0004343408524245024</v>
+        <v>0.0004050574989169836</v>
       </c>
       <c r="D57" t="n">
-        <v>0.1496755669603348</v>
+        <v>0.1429492666940689</v>
       </c>
       <c r="E57" t="n">
-        <v>0.002859603009723127</v>
+        <v>0.003609640159934759</v>
       </c>
       <c r="F57" t="n">
-        <v>0.02704450724126853</v>
+        <v>0.0106363230819706</v>
       </c>
       <c r="G57" t="n">
-        <v>0.01936956382424952</v>
+        <v>0.0003079999536564528</v>
       </c>
       <c r="H57" t="n">
-        <v>0.1634108855158431</v>
+        <v>0.1421620727159071</v>
       </c>
       <c r="I57" t="n">
-        <v>0.006857888974115666</v>
+        <v>0.009617512740778204</v>
       </c>
     </row>
     <row r="58">
@@ -2104,28 +2104,28 @@
         <v>56</v>
       </c>
       <c r="B58" t="n">
-        <v>0.004547623964160681</v>
+        <v>0.005509748999476433</v>
       </c>
       <c r="C58" t="n">
-        <v>0.001162605378905311</v>
+        <v>0.001865068827752024</v>
       </c>
       <c r="D58" t="n">
-        <v>0.1474399627809524</v>
+        <v>0.1419223052606583</v>
       </c>
       <c r="E58" t="n">
-        <v>0.002647818775601685</v>
+        <v>0.002935068626970053</v>
       </c>
       <c r="F58" t="n">
-        <v>0.007923714864397418</v>
+        <v>0.01269577677363186</v>
       </c>
       <c r="G58" t="n">
-        <v>0.000279018641219719</v>
+        <v>0.0003759673035279719</v>
       </c>
       <c r="H58" t="n">
-        <v>0.1421128640857451</v>
+        <v>0.1394012625775563</v>
       </c>
       <c r="I58" t="n">
-        <v>0.006934131961255099</v>
+        <v>0.01162280311896109</v>
       </c>
     </row>
     <row r="59">
@@ -2133,28 +2133,28 @@
         <v>57</v>
       </c>
       <c r="B59" t="n">
-        <v>0.003904568150624633</v>
+        <v>0.004402923055186868</v>
       </c>
       <c r="C59" t="n">
-        <v>0.0003638336256798357</v>
+        <v>0.0003845647604754195</v>
       </c>
       <c r="D59" t="n">
-        <v>0.1425981484937668</v>
+        <v>0.1393488510761261</v>
       </c>
       <c r="E59" t="n">
-        <v>0.00282774378926307</v>
+        <v>0.003321614041797817</v>
       </c>
       <c r="F59" t="n">
-        <v>0.00952168865916342</v>
+        <v>0.00838429548545189</v>
       </c>
       <c r="G59" t="n">
-        <v>0.0002512817490628661</v>
+        <v>0.000263156101685306</v>
       </c>
       <c r="H59" t="n">
-        <v>0.1421986122796431</v>
+        <v>0.1320102515257591</v>
       </c>
       <c r="I59" t="n">
-        <v>0.008559413873279076</v>
+        <v>0.007461088153960557</v>
       </c>
     </row>
     <row r="60">
@@ -2162,28 +2162,28 @@
         <v>58</v>
       </c>
       <c r="B60" t="n">
-        <v>0.003948974886119365</v>
+        <v>0.004989333342969418</v>
       </c>
       <c r="C60" t="n">
-        <v>0.0003579520691316575</v>
+        <v>0.001421789245356806</v>
       </c>
       <c r="D60" t="n">
-        <v>0.1398443134851456</v>
+        <v>0.140820488779068</v>
       </c>
       <c r="E60" t="n">
-        <v>0.002891801279738546</v>
+        <v>0.002863441719830036</v>
       </c>
       <c r="F60" t="n">
-        <v>0.007850006285015658</v>
+        <v>0.007248050739250312</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0004514642299432459</v>
+        <v>0.0001659652257344243</v>
       </c>
       <c r="H60" t="n">
-        <v>0.1502592884142675</v>
+        <v>0.1411829162723283</v>
       </c>
       <c r="I60" t="n">
-        <v>0.006647245573095649</v>
+        <v>0.006376170931235077</v>
       </c>
     </row>
     <row r="61">
@@ -2191,28 +2191,28 @@
         <v>59</v>
       </c>
       <c r="B61" t="n">
-        <v>0.00495137962654233</v>
+        <v>0.004085425647318363</v>
       </c>
       <c r="C61" t="n">
-        <v>0.002058248100014403</v>
+        <v>0.0005007332696523517</v>
       </c>
       <c r="D61" t="n">
-        <v>0.1429061153650284</v>
+        <v>0.138383982383728</v>
       </c>
       <c r="E61" t="n">
-        <v>0.002178600936926901</v>
+        <v>0.002892772451043129</v>
       </c>
       <c r="F61" t="n">
-        <v>0.00677759989919855</v>
+        <v>0.007815417268998665</v>
       </c>
       <c r="G61" t="n">
-        <v>0.000230272109873804</v>
+        <v>0.0005712041673843018</v>
       </c>
       <c r="H61" t="n">
-        <v>0.1478303397110197</v>
+        <v>0.1386386311676529</v>
       </c>
       <c r="I61" t="n">
-        <v>0.005808176045559748</v>
+        <v>0.006551019882245467</v>
       </c>
     </row>
     <row r="62">
@@ -2220,28 +2220,28 @@
         <v>60</v>
       </c>
       <c r="B62" t="n">
-        <v>0.003546647129580379</v>
+        <v>0.004114875872939825</v>
       </c>
       <c r="C62" t="n">
-        <v>0.0003372864874433726</v>
+        <v>0.0008878374761417509</v>
       </c>
       <c r="D62" t="n">
-        <v>0.1379681681928635</v>
+        <v>0.1375777935562134</v>
       </c>
       <c r="E62" t="n">
-        <v>0.002519519783109427</v>
+        <v>0.002539149461060763</v>
       </c>
       <c r="F62" t="n">
-        <v>0.007478593710299465</v>
+        <v>0.008355914917979603</v>
       </c>
       <c r="G62" t="n">
-        <v>0.0005259044032443625</v>
+        <v>0.0002416075043884284</v>
       </c>
       <c r="H62" t="n">
-        <v>0.1418235602726944</v>
+        <v>0.1324932811602488</v>
       </c>
       <c r="I62" t="n">
-        <v>0.006243571520070462</v>
+        <v>0.00745184100331772</v>
       </c>
     </row>
     <row r="63">
@@ -2249,28 +2249,28 @@
         <v>61</v>
       </c>
       <c r="B63" t="n">
-        <v>0.003895924406170845</v>
+        <v>0.003824426950499415</v>
       </c>
       <c r="C63" t="n">
-        <v>0.0008528362265825272</v>
+        <v>0.000375796180287376</v>
       </c>
       <c r="D63" t="n">
-        <v>0.138634289642334</v>
+        <v>0.1341593520812988</v>
       </c>
       <c r="E63" t="n">
-        <v>0.002349916748680174</v>
+        <v>0.002777834059685469</v>
       </c>
       <c r="F63" t="n">
-        <v>0.02223863366960896</v>
+        <v>0.00932520724887706</v>
       </c>
       <c r="G63" t="n">
-        <v>0.01570522500600113</v>
+        <v>0.0002823117248000665</v>
       </c>
       <c r="H63" t="n">
-        <v>0.1486813119000362</v>
+        <v>0.1356329692528259</v>
       </c>
       <c r="I63" t="n">
-        <v>0.00579000243664906</v>
+        <v>0.008364730682862136</v>
       </c>
     </row>
     <row r="64">
@@ -2278,28 +2278,28 @@
         <v>62</v>
       </c>
       <c r="B64" t="n">
-        <v>0.003504838679015636</v>
+        <v>0.003840703770160675</v>
       </c>
       <c r="C64" t="n">
-        <v>0.0007301939272582531</v>
+        <v>0.0003355274443440139</v>
       </c>
       <c r="D64" t="n">
-        <v>0.1363501728420257</v>
+        <v>0.1322735148048401</v>
       </c>
       <c r="E64" t="n">
-        <v>0.002092893943816423</v>
+        <v>0.002843808733612299</v>
       </c>
       <c r="F64" t="n">
-        <v>0.009256156776009239</v>
+        <v>0.008267697129416815</v>
       </c>
       <c r="G64" t="n">
-        <v>0.0004743632323527936</v>
+        <v>0.000924768486876059</v>
       </c>
       <c r="H64" t="n">
-        <v>0.1370442546026547</v>
+        <v>0.1281692293845421</v>
       </c>
       <c r="I64" t="n">
-        <v>0.008096572194236283</v>
+        <v>0.006702082517297048</v>
       </c>
     </row>
     <row r="65">
@@ -2307,28 +2307,28 @@
         <v>63</v>
       </c>
       <c r="B65" t="n">
-        <v>0.00329596560126543</v>
+        <v>0.003599424778282642</v>
       </c>
       <c r="C65" t="n">
-        <v>0.0003444951527146623</v>
+        <v>0.0003483776023294777</v>
       </c>
       <c r="D65" t="n">
-        <v>0.1374617674894333</v>
+        <v>0.1302781831684112</v>
       </c>
       <c r="E65" t="n">
-        <v>0.002264161625847221</v>
+        <v>0.002599656257726252</v>
       </c>
       <c r="F65" t="n">
-        <v>0.007139260835252812</v>
+        <v>0.00913255080270777</v>
       </c>
       <c r="G65" t="n">
-        <v>0.0002143181901230275</v>
+        <v>0.0001948528886128135</v>
       </c>
       <c r="H65" t="n">
-        <v>0.1402689225327521</v>
+        <v>0.1276084543917735</v>
       </c>
       <c r="I65" t="n">
-        <v>0.006223598065653885</v>
+        <v>0.008299655771129089</v>
       </c>
     </row>
     <row r="66">
@@ -2336,28 +2336,28 @@
         <v>64</v>
       </c>
       <c r="B66" t="n">
-        <v>0.003795597582295537</v>
+        <v>0.003587091343462467</v>
       </c>
       <c r="C66" t="n">
-        <v>0.001179653135307133</v>
+        <v>0.0003267078519333154</v>
       </c>
       <c r="D66" t="n">
-        <v>0.136727654501915</v>
+        <v>0.1299499995937347</v>
       </c>
       <c r="E66" t="n">
-        <v>0.001932306177034974</v>
+        <v>0.002610633458808064</v>
       </c>
       <c r="F66" t="n">
-        <v>0.007179578534565976</v>
+        <v>0.008084834778884982</v>
       </c>
       <c r="G66" t="n">
-        <v>0.0001743116531274958</v>
+        <v>0.0002878029642704127</v>
       </c>
       <c r="H66" t="n">
-        <v>0.1368702095785888</v>
+        <v>0.1275047720878782</v>
       </c>
       <c r="I66" t="n">
-        <v>0.006320915878408545</v>
+        <v>0.007159507963593691</v>
       </c>
     </row>
     <row r="67">
@@ -2365,28 +2365,28 @@
         <v>65</v>
       </c>
       <c r="B67" t="n">
-        <v>0.002943743105962873</v>
+        <v>0.003367906016439199</v>
       </c>
       <c r="C67" t="n">
-        <v>0.0003169446075744927</v>
+        <v>0.0003285042871944606</v>
       </c>
       <c r="D67" t="n">
-        <v>0.132944696436882</v>
+        <v>0.1288811988992691</v>
       </c>
       <c r="E67" t="n">
-        <v>0.001962075019940734</v>
+        <v>0.002394995782062411</v>
       </c>
       <c r="F67" t="n">
-        <v>0.009219693784308765</v>
+        <v>0.0103948077029544</v>
       </c>
       <c r="G67" t="n">
-        <v>0.0002288717040917449</v>
+        <v>0.0002747139567053508</v>
       </c>
       <c r="H67" t="n">
-        <v>0.1337742855906681</v>
+        <v>0.1263177847803903</v>
       </c>
       <c r="I67" t="n">
-        <v>0.008321950776323214</v>
+        <v>0.009488504864275455</v>
       </c>
     </row>
     <row r="68">
@@ -2394,28 +2394,28 @@
         <v>66</v>
       </c>
       <c r="B68" t="n">
-        <v>0.003019904679715634</v>
+        <v>0.003426152200430632</v>
       </c>
       <c r="C68" t="n">
-        <v>0.0002979899775143713</v>
+        <v>0.0003360161583311856</v>
       </c>
       <c r="D68" t="n">
-        <v>0.1333284629592895</v>
+        <v>0.1291935822610855</v>
       </c>
       <c r="E68" t="n">
-        <v>0.002055272399798036</v>
+        <v>0.002444168140754104</v>
       </c>
       <c r="F68" t="n">
-        <v>0.009789426427753871</v>
+        <v>0.00790861840950869</v>
       </c>
       <c r="G68" t="n">
-        <v>0.0002700229025777083</v>
+        <v>0.0003384202897288878</v>
       </c>
       <c r="H68" t="n">
-        <v>0.1253349628942437</v>
+        <v>0.1300948316004693</v>
       </c>
       <c r="I68" t="n">
-        <v>0.008892728667128922</v>
+        <v>0.006919723991152708</v>
       </c>
     </row>
     <row r="69">
@@ -2423,28 +2423,28 @@
         <v>67</v>
       </c>
       <c r="B69" t="n">
-        <v>0.003050381489545107</v>
+        <v>0.003148660000175238</v>
       </c>
       <c r="C69" t="n">
-        <v>0.0006668332973886281</v>
+        <v>0.0003187150883302093</v>
       </c>
       <c r="D69" t="n">
-        <v>0.138568565861702</v>
+        <v>0.1282841452894211</v>
       </c>
       <c r="E69" t="n">
-        <v>0.001690705396458507</v>
+        <v>0.002188524177290499</v>
       </c>
       <c r="F69" t="n">
-        <v>0.01000820081705322</v>
+        <v>0.009111112347799452</v>
       </c>
       <c r="G69" t="n">
-        <v>0.0002886291024055587</v>
+        <v>0.0002309340259974114</v>
       </c>
       <c r="H69" t="n">
-        <v>0.1312116970712559</v>
+        <v>0.1257830810041256</v>
       </c>
       <c r="I69" t="n">
-        <v>0.009063513262188259</v>
+        <v>0.008251262901177657</v>
       </c>
     </row>
     <row r="70">
@@ -2452,28 +2452,28 @@
         <v>68</v>
       </c>
       <c r="B70" t="n">
-        <v>0.002911890427783132</v>
+        <v>0.003398857153713703</v>
       </c>
       <c r="C70" t="n">
-        <v>0.0003199574769921601</v>
+        <v>0.0007007367617283016</v>
       </c>
       <c r="D70" t="n">
-        <v>0.1346713455915451</v>
+        <v>0.1267205370292664</v>
       </c>
       <c r="E70" t="n">
-        <v>0.001918576207265258</v>
+        <v>0.002064517727896571</v>
       </c>
       <c r="F70" t="n">
-        <v>0.007511274174439187</v>
+        <v>0.0078548311322417</v>
       </c>
       <c r="G70" t="n">
-        <v>0.0002928091314462504</v>
+        <v>0.0002032480264412236</v>
       </c>
       <c r="H70" t="n">
-        <v>0.139482395452543</v>
+        <v>0.1275457323744869</v>
       </c>
       <c r="I70" t="n">
-        <v>0.006521053093790911</v>
+        <v>0.007013854509793817</v>
       </c>
     </row>
     <row r="71">
@@ -2481,28 +2481,28 @@
         <v>69</v>
       </c>
       <c r="B71" t="n">
-        <v>0.002905487509220839</v>
+        <v>0.00295578901168704</v>
       </c>
       <c r="C71" t="n">
-        <v>0.0003220820763073861</v>
+        <v>0.0003171195376589894</v>
       </c>
       <c r="D71" t="n">
-        <v>0.133816508348465</v>
+        <v>0.1250833065605164</v>
       </c>
       <c r="E71" t="n">
-        <v>0.001914322900056839</v>
+        <v>0.002013252950370312</v>
       </c>
       <c r="F71" t="n">
-        <v>0.007659541537672233</v>
+        <v>0.007435240276236859</v>
       </c>
       <c r="G71" t="n">
-        <v>0.0002031348241338518</v>
+        <v>0.000313993638315273</v>
       </c>
       <c r="H71" t="n">
-        <v>0.1364056508566388</v>
+        <v>0.1256023092312681</v>
       </c>
       <c r="I71" t="n">
-        <v>0.006774378454686427</v>
+        <v>0.006493235071103103</v>
       </c>
     </row>
     <row r="72">
@@ -2510,28 +2510,28 @@
         <v>70</v>
       </c>
       <c r="B72" t="n">
-        <v>0.002712564662262797</v>
+        <v>0.003068957712769509</v>
       </c>
       <c r="C72" t="n">
-        <v>0.0002965811663335189</v>
+        <v>0.0003033604119215161</v>
       </c>
       <c r="D72" t="n">
-        <v>0.1316707982130051</v>
+        <v>0.1240345256896019</v>
       </c>
       <c r="E72" t="n">
-        <v>0.001757629504792392</v>
+        <v>0.002145424658186734</v>
       </c>
       <c r="F72" t="n">
-        <v>0.007292775299649254</v>
+        <v>0.009333491158317683</v>
       </c>
       <c r="G72" t="n">
-        <v>0.0003214815745531273</v>
+        <v>0.0001980574166692404</v>
       </c>
       <c r="H72" t="n">
-        <v>0.1275366374368963</v>
+        <v>0.120277488968209</v>
       </c>
       <c r="I72" t="n">
-        <v>0.006333610491939558</v>
+        <v>0.008534046329047416</v>
       </c>
     </row>
     <row r="73">
@@ -2539,28 +2539,28 @@
         <v>71</v>
       </c>
       <c r="B73" t="n">
-        <v>0.002637716030016541</v>
+        <v>0.002851292007952929</v>
       </c>
       <c r="C73" t="n">
-        <v>0.0002927828550618142</v>
+        <v>0.0002910931799001991</v>
       </c>
       <c r="D73" t="n">
-        <v>0.13091847660923</v>
+        <v>0.1248259959487915</v>
       </c>
       <c r="E73" t="n">
-        <v>0.001690340804792941</v>
+        <v>0.001936068856015801</v>
       </c>
       <c r="F73" t="n">
-        <v>0.008306958209267449</v>
+        <v>0.008453142547928295</v>
       </c>
       <c r="G73" t="n">
-        <v>0.0002051602375701596</v>
+        <v>0.0007663727175789242</v>
       </c>
       <c r="H73" t="n">
-        <v>0.1279459264918214</v>
+        <v>0.1319370248179646</v>
       </c>
       <c r="I73" t="n">
-        <v>0.007462068237394678</v>
+        <v>0.007027084699438408</v>
       </c>
     </row>
     <row r="74">
@@ -2568,28 +2568,28 @@
         <v>72</v>
       </c>
       <c r="B74" t="n">
-        <v>0.002594775061309338</v>
+        <v>0.00280175096064806</v>
       </c>
       <c r="C74" t="n">
-        <v>0.0002794581128284335</v>
+        <v>0.0003049204441234469</v>
       </c>
       <c r="D74" t="n">
-        <v>0.1286618233633041</v>
+        <v>0.1249552593135834</v>
       </c>
       <c r="E74" t="n">
-        <v>0.001672007850050926</v>
+        <v>0.001872054239034653</v>
       </c>
       <c r="F74" t="n">
-        <v>0.007362864993324239</v>
+        <v>0.007784157644525827</v>
       </c>
       <c r="G74" t="n">
-        <v>0.0003345757747618983</v>
+        <v>0.0002323565713272751</v>
       </c>
       <c r="H74" t="n">
-        <v>0.1309761532513975</v>
+        <v>0.1213745131680277</v>
       </c>
       <c r="I74" t="n">
-        <v>0.006373408329787058</v>
+        <v>0.006944928662350088</v>
       </c>
     </row>
     <row r="75">
@@ -2597,28 +2597,28 @@
         <v>73</v>
       </c>
       <c r="B75" t="n">
-        <v>0.002535276066944003</v>
+        <v>0.002725875383108854</v>
       </c>
       <c r="C75" t="n">
-        <v>0.0002892465704167262</v>
+        <v>0.0002875901037966833</v>
       </c>
       <c r="D75" t="n">
-        <v>0.1299999480056763</v>
+        <v>0.1238431645598412</v>
       </c>
       <c r="E75" t="n">
-        <v>0.001596029760465026</v>
+        <v>0.001819069475360215</v>
       </c>
       <c r="F75" t="n">
-        <v>0.006927806635555883</v>
+        <v>0.007463235988556658</v>
       </c>
       <c r="G75" t="n">
-        <v>0.0002039631333938598</v>
+        <v>0.0006330599935936512</v>
       </c>
       <c r="H75" t="n">
-        <v>0.1315681869229135</v>
+        <v>0.1216886463732159</v>
       </c>
       <c r="I75" t="n">
-        <v>0.006066002593289144</v>
+        <v>0.006221732805174628</v>
       </c>
     </row>
     <row r="76">
@@ -2626,28 +2626,28 @@
         <v>74</v>
       </c>
       <c r="B76" t="n">
-        <v>0.002531481521159411</v>
+        <v>0.002681098662942648</v>
       </c>
       <c r="C76" t="n">
-        <v>0.000291676760353148</v>
+        <v>0.0002955544663667679</v>
       </c>
       <c r="D76" t="n">
-        <v>0.1300407116508484</v>
+        <v>0.1245531756162643</v>
       </c>
       <c r="E76" t="n">
-        <v>0.001589601205743849</v>
+        <v>0.001762778331436217</v>
       </c>
       <c r="F76" t="n">
-        <v>0.007436224980854093</v>
+        <v>0.0088701200969578</v>
       </c>
       <c r="G76" t="n">
-        <v>0.0001694221865935752</v>
+        <v>0.0002054824286281415</v>
       </c>
       <c r="H76" t="n">
-        <v>0.1308278102032707</v>
+        <v>0.1247853584580281</v>
       </c>
       <c r="I76" t="n">
-        <v>0.0066126637680374</v>
+        <v>0.008040710902160571</v>
       </c>
     </row>
     <row r="77">
@@ -2655,28 +2655,28 @@
         <v>75</v>
       </c>
       <c r="B77" t="n">
-        <v>0.002427920574650168</v>
+        <v>0.002615274787932634</v>
       </c>
       <c r="C77" t="n">
-        <v>0.0002706186864394695</v>
+        <v>0.0002707640019739047</v>
       </c>
       <c r="D77" t="n">
-        <v>0.1283109637756348</v>
+        <v>0.1246495676879883</v>
       </c>
       <c r="E77" t="n">
-        <v>0.001515747076041996</v>
+        <v>0.001721262959636748</v>
       </c>
       <c r="F77" t="n">
-        <v>0.006476415316156472</v>
+        <v>0.007530798080482111</v>
       </c>
       <c r="G77" t="n">
-        <v>0.0002582114922216232</v>
+        <v>0.0002003221721135818</v>
       </c>
       <c r="H77" t="n">
-        <v>0.1330746234970419</v>
+        <v>0.1265400655103352</v>
       </c>
       <c r="I77" t="n">
-        <v>0.005552830721903441</v>
+        <v>0.006697775593474143</v>
       </c>
     </row>
     <row r="78">
@@ -2684,28 +2684,28 @@
         <v>76</v>
       </c>
       <c r="B78" t="n">
-        <v>0.002344851551055908</v>
+        <v>0.002619251066729426</v>
       </c>
       <c r="C78" t="n">
-        <v>0.0002758987068179995</v>
+        <v>0.0002914588163271546</v>
       </c>
       <c r="D78" t="n">
-        <v>0.1285830701131821</v>
+        <v>0.124766064786911</v>
       </c>
       <c r="E78" t="n">
-        <v>0.001426037510588765</v>
+        <v>0.001703961946547031</v>
       </c>
       <c r="F78" t="n">
-        <v>0.007883783011814218</v>
+        <v>0.008516070820135937</v>
       </c>
       <c r="G78" t="n">
-        <v>0.0002783387330843844</v>
+        <v>0.0002333956287304383</v>
       </c>
       <c r="H78" t="n">
-        <v>0.125746042108069</v>
+        <v>0.1214191102257172</v>
       </c>
       <c r="I78" t="n">
-        <v>0.006976714073870252</v>
+        <v>0.007675579705930408</v>
       </c>
     </row>
     <row r="79">
@@ -2713,28 +2713,28 @@
         <v>77</v>
       </c>
       <c r="B79" t="n">
-        <v>0.002360122548155486</v>
+        <v>0.0024934321680516</v>
       </c>
       <c r="C79" t="n">
-        <v>0.0002767765794433653</v>
+        <v>0.000272044265977107</v>
       </c>
       <c r="D79" t="n">
-        <v>0.1282020364904404</v>
+        <v>0.1239886246128082</v>
       </c>
       <c r="E79" t="n">
-        <v>0.001442335804656148</v>
+        <v>0.001601444794125855</v>
       </c>
       <c r="F79" t="n">
-        <v>0.006850510524436953</v>
+        <v>0.007672144387032819</v>
       </c>
       <c r="G79" t="n">
-        <v>0.0002762232931747844</v>
+        <v>0.0003308295333840798</v>
       </c>
       <c r="H79" t="n">
-        <v>0.127733994457889</v>
+        <v>0.120642316394879</v>
       </c>
       <c r="I79" t="n">
-        <v>0.005935617246882318</v>
+        <v>0.006738103261402828</v>
       </c>
     </row>
     <row r="80">
@@ -2742,28 +2742,28 @@
         <v>78</v>
       </c>
       <c r="B80" t="n">
-        <v>0.002245401737213135</v>
+        <v>0.002465741247206926</v>
       </c>
       <c r="C80" t="n">
-        <v>0.0002694219336211682</v>
+        <v>0.0002623142584636807</v>
       </c>
       <c r="D80" t="n">
-        <v>0.1278888307228088</v>
+        <v>0.1223532947368622</v>
       </c>
       <c r="E80" t="n">
-        <v>0.001336535674512386</v>
+        <v>0.001591660531662405</v>
       </c>
       <c r="F80" t="n">
-        <v>0.008131889939569484</v>
+        <v>0.0083348943170944</v>
       </c>
       <c r="G80" t="n">
-        <v>0.0002413438172398673</v>
+        <v>0.000195550099843247</v>
       </c>
       <c r="H80" t="n">
-        <v>0.1271049200720344</v>
+        <v>0.1215031707281973</v>
       </c>
       <c r="I80" t="n">
-        <v>0.007255021465173504</v>
+        <v>0.007531828296022888</v>
       </c>
     </row>
     <row r="81">
@@ -2771,28 +2771,28 @@
         <v>79</v>
       </c>
       <c r="B81" t="n">
-        <v>0.002225249904617667</v>
+        <v>0.002370311262995005</v>
       </c>
       <c r="C81" t="n">
-        <v>0.0002720931651517749</v>
+        <v>0.0002899603194510564</v>
       </c>
       <c r="D81" t="n">
-        <v>0.1286853595142365</v>
+        <v>0.1236371140141487</v>
       </c>
       <c r="E81" t="n">
-        <v>0.00130972996275872</v>
+        <v>0.0014621654015854</v>
       </c>
       <c r="F81" t="n">
-        <v>0.007649163199348609</v>
+        <v>0.007206665360099875</v>
       </c>
       <c r="G81" t="n">
-        <v>0.0003241932152263018</v>
+        <v>0.0004358090779407567</v>
       </c>
       <c r="H81" t="n">
-        <v>0.1298240493269573</v>
+        <v>0.1241473271718422</v>
       </c>
       <c r="I81" t="n">
-        <v>0.006675849813712703</v>
+        <v>0.00615011952148954</v>
       </c>
     </row>
     <row r="82">
@@ -2800,28 +2800,28 @@
         <v>80</v>
       </c>
       <c r="B82" t="n">
-        <v>0.002159387367472052</v>
+        <v>0.002357746341690421</v>
       </c>
       <c r="C82" t="n">
-        <v>0.000263488413695246</v>
+        <v>0.0002685503764534369</v>
       </c>
       <c r="D82" t="n">
-        <v>0.1268876198811531</v>
+        <v>0.1232197542133331</v>
       </c>
       <c r="E82" t="n">
-        <v>0.001261460863597691</v>
+        <v>0.001473097203634679</v>
       </c>
       <c r="F82" t="n">
-        <v>0.007987553291569721</v>
+        <v>0.007076926613089798</v>
       </c>
       <c r="G82" t="n">
-        <v>0.0002277757624885125</v>
+        <v>0.0003617267587566277</v>
       </c>
       <c r="H82" t="n">
-        <v>0.1232153687080396</v>
+        <v>0.1218740514620871</v>
       </c>
       <c r="I82" t="n">
-        <v>0.007143700746105312</v>
+        <v>0.006105829558683161</v>
       </c>
     </row>
     <row r="83">
@@ -2829,28 +2829,28 @@
         <v>81</v>
       </c>
       <c r="B83" t="n">
-        <v>0.002164910951882601</v>
+        <v>0.002255650191903114</v>
       </c>
       <c r="C83" t="n">
-        <v>0.0002580256890859455</v>
+        <v>0.00025519354669936</v>
       </c>
       <c r="D83" t="n">
-        <v>0.1257618213224411</v>
+        <v>0.1224796914567947</v>
       </c>
       <c r="E83" t="n">
-        <v>0.001278076133020222</v>
+        <v>0.001388058225542307</v>
       </c>
       <c r="F83" t="n">
-        <v>0.007042824985979043</v>
+        <v>0.009555893585049406</v>
       </c>
       <c r="G83" t="n">
-        <v>0.000278962084485695</v>
+        <v>0.000264032884023485</v>
       </c>
       <c r="H83" t="n">
-        <v>0.1302907660345852</v>
+        <v>0.1238743984242248</v>
       </c>
       <c r="I83" t="n">
-        <v>0.006112409167502191</v>
+        <v>0.008672488561024674</v>
       </c>
     </row>
     <row r="84">
@@ -2858,28 +2858,28 @@
         <v>82</v>
       </c>
       <c r="B84" t="n">
-        <v>0.002093699528202415</v>
+        <v>0.002216973273575306</v>
       </c>
       <c r="C84" t="n">
-        <v>0.0002539344227444381</v>
+        <v>0.0002550658981846646</v>
       </c>
       <c r="D84" t="n">
-        <v>0.1277421850447655</v>
+        <v>0.122511455034256</v>
       </c>
       <c r="E84" t="n">
-        <v>0.001201054202802479</v>
+        <v>0.001349350131824613</v>
       </c>
       <c r="F84" t="n">
-        <v>0.008478553751164509</v>
+        <v>0.007641543311600195</v>
       </c>
       <c r="G84" t="n">
-        <v>0.0002151040204699633</v>
+        <v>0.0006577396050375107</v>
       </c>
       <c r="H84" t="n">
-        <v>0.1181310249070164</v>
+        <v>0.1218502092667738</v>
       </c>
       <c r="I84" t="n">
-        <v>0.007672794715335766</v>
+        <v>0.006374552656591036</v>
       </c>
     </row>
     <row r="85">
@@ -2887,28 +2887,28 @@
         <v>83</v>
       </c>
       <c r="B85" t="n">
-        <v>0.002049788957595825</v>
+        <v>0.002156799478113651</v>
       </c>
       <c r="C85" t="n">
-        <v>0.0002501320101395249</v>
+        <v>0.0002654647213499993</v>
       </c>
       <c r="D85" t="n">
-        <v>0.1266173793878555</v>
+        <v>0.1229385449781418</v>
       </c>
       <c r="E85" t="n">
-        <v>0.001166570078425109</v>
+        <v>0.001276642051562667</v>
       </c>
       <c r="F85" t="n">
-        <v>0.007389414217961165</v>
+        <v>0.007676859888602139</v>
       </c>
       <c r="G85" t="n">
-        <v>0.0001880804850601365</v>
+        <v>0.000182838741505517</v>
       </c>
       <c r="H85" t="n">
-        <v>0.1265030670613294</v>
+        <v>0.12371788225594</v>
       </c>
       <c r="I85" t="n">
-        <v>0.006568818334641989</v>
+        <v>0.006875431670322649</v>
       </c>
     </row>
     <row r="86">
@@ -2916,28 +2916,28 @@
         <v>84</v>
       </c>
       <c r="B86" t="n">
-        <v>0.002016929607436061</v>
+        <v>0.002117606880001724</v>
       </c>
       <c r="C86" t="n">
-        <v>0.0002502228248696774</v>
+        <v>0.0002518910955842585</v>
       </c>
       <c r="D86" t="n">
-        <v>0.1266939972896576</v>
+        <v>0.1213664961218834</v>
       </c>
       <c r="E86" t="n">
-        <v>0.001133236810512841</v>
+        <v>0.001258883333384991</v>
       </c>
       <c r="F86" t="n">
-        <v>0.007326996957193483</v>
+        <v>0.006866526993486854</v>
       </c>
       <c r="G86" t="n">
-        <v>0.0003704897121398681</v>
+        <v>0.0002562989407089094</v>
       </c>
       <c r="H86" t="n">
-        <v>0.1302452058902961</v>
+        <v>0.1243909978472778</v>
       </c>
       <c r="I86" t="n">
-        <v>0.006305281275041632</v>
+        <v>0.005988273128538984</v>
       </c>
     </row>
     <row r="87">
@@ -2945,28 +2945,28 @@
         <v>85</v>
       </c>
       <c r="B87" t="n">
-        <v>0.001997237769216299</v>
+        <v>0.00206493141630292</v>
       </c>
       <c r="C87" t="n">
-        <v>0.0002452252588309348</v>
+        <v>0.0002548046205639839</v>
       </c>
       <c r="D87" t="n">
-        <v>0.1264917012290954</v>
+        <v>0.121360134054184</v>
       </c>
       <c r="E87" t="n">
-        <v>0.001119554023012519</v>
+        <v>0.001203326149769127</v>
       </c>
       <c r="F87" t="n">
-        <v>0.007858003026594637</v>
+        <v>0.008767004212878073</v>
       </c>
       <c r="G87" t="n">
-        <v>0.0001930115417530608</v>
+        <v>0.0002267550198514346</v>
       </c>
       <c r="H87" t="n">
-        <v>0.125573742525807</v>
+        <v>0.1134343423326097</v>
       </c>
       <c r="I87" t="n">
-        <v>0.007037122815810934</v>
+        <v>0.007973077521761227</v>
       </c>
     </row>
     <row r="88">
@@ -2974,28 +2974,28 @@
         <v>86</v>
       </c>
       <c r="B88" t="n">
-        <v>0.001962433571621775</v>
+        <v>0.002068978782467544</v>
       </c>
       <c r="C88" t="n">
-        <v>0.0002466841706745327</v>
+        <v>0.0002488772364798933</v>
       </c>
       <c r="D88" t="n">
-        <v>0.1257411040639877</v>
+        <v>0.1219266350021362</v>
       </c>
       <c r="E88" t="n">
-        <v>0.001087043882742524</v>
+        <v>0.00121046837040782</v>
       </c>
       <c r="F88" t="n">
-        <v>0.006874828427470917</v>
+        <v>0.007256944261789079</v>
       </c>
       <c r="G88" t="n">
-        <v>0.0002731908970078693</v>
+        <v>0.000240626933233931</v>
       </c>
       <c r="H88" t="n">
-        <v>0.1287339069296835</v>
+        <v>0.1204395429456992</v>
       </c>
       <c r="I88" t="n">
-        <v>0.005957967979350351</v>
+        <v>0.006414119565850322</v>
       </c>
     </row>
     <row r="89">
@@ -3003,28 +3003,28 @@
         <v>87</v>
       </c>
       <c r="B89" t="n">
-        <v>0.001908081692293286</v>
+        <v>0.001974729790061712</v>
       </c>
       <c r="C89" t="n">
-        <v>0.0002478564642164856</v>
+        <v>0.0002478459353363142</v>
       </c>
       <c r="D89" t="n">
-        <v>0.1261516547222137</v>
+        <v>0.1230555490932465</v>
       </c>
       <c r="E89" t="n">
-        <v>0.001029466971922666</v>
+        <v>0.001111606126204133</v>
       </c>
       <c r="F89" t="n">
-        <v>0.00818640766227785</v>
+        <v>0.007097172210415366</v>
       </c>
       <c r="G89" t="n">
-        <v>0.0001934623345020523</v>
+        <v>0.0002098135558440507</v>
       </c>
       <c r="H89" t="n">
-        <v>0.1255460322856125</v>
+        <v>0.125589612544458</v>
       </c>
       <c r="I89" t="n">
-        <v>0.007365215151414251</v>
+        <v>0.006259410613099475</v>
       </c>
     </row>
     <row r="90">
@@ -3032,28 +3032,28 @@
         <v>88</v>
       </c>
       <c r="B90" t="n">
-        <v>0.001844549382261932</v>
+        <v>0.002016853271692991</v>
       </c>
       <c r="C90" t="n">
-        <v>0.0002455832991478965</v>
+        <v>0.0002419883803203702</v>
       </c>
       <c r="D90" t="n">
-        <v>0.1261474839615822</v>
+        <v>0.1214382257852554</v>
       </c>
       <c r="E90" t="n">
-        <v>0.0009682286807745695</v>
+        <v>0.001167673768110573</v>
       </c>
       <c r="F90" t="n">
-        <v>0.00755162856552209</v>
+        <v>0.008520678045990805</v>
       </c>
       <c r="G90" t="n">
-        <v>0.0002112654642573046</v>
+        <v>0.0002148501641281499</v>
       </c>
       <c r="H90" t="n">
-        <v>0.1251726893353812</v>
+        <v>0.1245191115695151</v>
       </c>
       <c r="I90" t="n">
-        <v>0.006714499735442062</v>
+        <v>0.007683232281338818</v>
       </c>
     </row>
     <row r="91">
@@ -3061,28 +3061,28 @@
         <v>89</v>
       </c>
       <c r="B91" t="n">
-        <v>0.001850209773167968</v>
+        <v>0.001960657370254397</v>
       </c>
       <c r="C91" t="n">
-        <v>0.0002389944467842579</v>
+        <v>0.0002539699651524424</v>
       </c>
       <c r="D91" t="n">
-        <v>0.1258904025907517</v>
+        <v>0.1216943507990837</v>
       </c>
       <c r="E91" t="n">
-        <v>0.0009817633136548101</v>
+        <v>0.001098215649433434</v>
       </c>
       <c r="F91" t="n">
-        <v>0.008177984121086937</v>
+        <v>0.006657649399454403</v>
       </c>
       <c r="G91" t="n">
-        <v>0.000179301495211834</v>
+        <v>0.0002443365669278671</v>
       </c>
       <c r="H91" t="n">
-        <v>0.1298933472378608</v>
+        <v>0.1242003180103629</v>
       </c>
       <c r="I91" t="n">
-        <v>0.007349215818183165</v>
+        <v>0.005792311189504763</v>
       </c>
     </row>
     <row r="92">
@@ -3090,28 +3090,28 @@
         <v>90</v>
       </c>
       <c r="B92" t="n">
-        <v>0.001780749604582786</v>
+        <v>0.001926018142059445</v>
       </c>
       <c r="C92" t="n">
-        <v>0.0002359954640129581</v>
+        <v>0.0002411881252992898</v>
       </c>
       <c r="D92" t="n">
-        <v>0.1267723380250931</v>
+        <v>0.1214730313272476</v>
       </c>
       <c r="E92" t="n">
-        <v>0.0009108924598842859</v>
+        <v>0.001077464865136892</v>
       </c>
       <c r="F92" t="n">
-        <v>0.007094257987282112</v>
+        <v>0.007765554536808568</v>
       </c>
       <c r="G92" t="n">
-        <v>0.0002981903349284119</v>
+        <v>0.0002096566607422449</v>
       </c>
       <c r="H92" t="n">
-        <v>0.1280421354136693</v>
+        <v>0.1215019691807216</v>
       </c>
       <c r="I92" t="n">
-        <v>0.00615585698847937</v>
+        <v>0.006948388155738157</v>
       </c>
     </row>
     <row r="93">
@@ -3119,28 +3119,28 @@
         <v>91</v>
       </c>
       <c r="B93" t="n">
-        <v>0.001751260262787342</v>
+        <v>0.001836655035838485</v>
       </c>
       <c r="C93" t="n">
-        <v>0.0002393954341616481</v>
+        <v>0.0002467269622674212</v>
       </c>
       <c r="D93" t="n">
-        <v>0.1249385959925652</v>
+        <v>0.1213825535526276</v>
       </c>
       <c r="E93" t="n">
-        <v>0.0008871718589067459</v>
+        <v>0.0009830153148695827</v>
       </c>
       <c r="F93" t="n">
-        <v>0.008182847558096853</v>
+        <v>0.006643566840114057</v>
       </c>
       <c r="G93" t="n">
-        <v>0.0002043593425260398</v>
+        <v>0.0002613079648249939</v>
       </c>
       <c r="H93" t="n">
-        <v>0.1224136185043204</v>
+        <v>0.1230024910595444</v>
       </c>
       <c r="I93" t="n">
-        <v>0.007366420072495792</v>
+        <v>0.005767246406969005</v>
       </c>
     </row>
     <row r="94">
@@ -3148,28 +3148,28 @@
         <v>92</v>
       </c>
       <c r="B94" t="n">
-        <v>0.0017590478695333</v>
+        <v>0.001856487320303917</v>
       </c>
       <c r="C94" t="n">
-        <v>0.0002342947061089799</v>
+        <v>0.0002401567695718259</v>
       </c>
       <c r="D94" t="n">
-        <v>0.1247597109537125</v>
+        <v>0.1206685609192848</v>
       </c>
       <c r="E94" t="n">
-        <v>0.0009009546181410551</v>
+        <v>0.001012987767621875</v>
       </c>
       <c r="F94" t="n">
-        <v>0.007038088133209195</v>
+        <v>0.007695111152434913</v>
       </c>
       <c r="G94" t="n">
-        <v>0.0003289508930241103</v>
+        <v>0.000192451163690361</v>
       </c>
       <c r="H94" t="n">
-        <v>0.1227973507974315</v>
+        <v>0.1176273373138846</v>
       </c>
       <c r="I94" t="n">
-        <v>0.00609515049341355</v>
+        <v>0.006914523272375541</v>
       </c>
     </row>
     <row r="95">
@@ -3177,28 +3177,28 @@
         <v>93</v>
       </c>
       <c r="B95" t="n">
-        <v>0.00164913624894619</v>
+        <v>0.001792098270580173</v>
       </c>
       <c r="C95" t="n">
-        <v>0.0002370997679643333</v>
+        <v>0.0002311686879275367</v>
       </c>
       <c r="D95" t="n">
-        <v>0.1246564126434326</v>
+        <v>0.1203237036366463</v>
       </c>
       <c r="E95" t="n">
-        <v>0.0007887544367015362</v>
+        <v>0.0009593110843002797</v>
       </c>
       <c r="F95" t="n">
-        <v>0.006938136155469431</v>
+        <v>0.007136466389379144</v>
       </c>
       <c r="G95" t="n">
-        <v>0.0001914233146110006</v>
+        <v>0.0003481619585218853</v>
       </c>
       <c r="H95" t="n">
-        <v>0.1229911927229818</v>
+        <v>0.1205624175237015</v>
       </c>
       <c r="I95" t="n">
-        <v>0.006131756868802898</v>
+        <v>0.006185492398232514</v>
       </c>
     </row>
     <row r="96">
@@ -3206,28 +3206,28 @@
         <v>94</v>
       </c>
       <c r="B96" t="n">
-        <v>0.00169929599673301</v>
+        <v>0.001703478489249945</v>
       </c>
       <c r="C96" t="n">
-        <v>0.0002256388870188966</v>
+        <v>0.0002318094838643446</v>
       </c>
       <c r="D96" t="n">
-        <v>0.1253163625760078</v>
+        <v>0.1194217830920219</v>
       </c>
       <c r="E96" t="n">
-        <v>0.0008470752961188554</v>
+        <v>0.0008745601142086089</v>
       </c>
       <c r="F96" t="n">
-        <v>0.007262222251078481</v>
+        <v>0.006565716483282323</v>
       </c>
       <c r="G96" t="n">
-        <v>0.0002879219833889833</v>
+        <v>0.0002016583517306601</v>
       </c>
       <c r="H96" t="n">
-        <v>0.1218170789380058</v>
+        <v>0.1234449691256147</v>
       </c>
       <c r="I96" t="n">
-        <v>0.006365214914940358</v>
+        <v>0.005746833360427307</v>
       </c>
     </row>
     <row r="97">
@@ -3235,28 +3235,28 @@
         <v>95</v>
       </c>
       <c r="B97" t="n">
-        <v>0.001668929595559835</v>
+        <v>0.001780120352864265</v>
       </c>
       <c r="C97" t="n">
-        <v>0.0002360234949337319</v>
+        <v>0.0002275637841317803</v>
       </c>
       <c r="D97" t="n">
-        <v>0.1242558480377197</v>
+        <v>0.1207292504973412</v>
       </c>
       <c r="E97" t="n">
-        <v>0.0008116268869191409</v>
+        <v>0.0009489103370979428</v>
       </c>
       <c r="F97" t="n">
-        <v>0.008074759464060697</v>
+        <v>0.009093346569328576</v>
       </c>
       <c r="G97" t="n">
-        <v>0.0001961261412285673</v>
+        <v>0.0002033125139472073</v>
       </c>
       <c r="H97" t="n">
-        <v>0.1227958059490797</v>
+        <v>0.1206526081013641</v>
       </c>
       <c r="I97" t="n">
-        <v>0.007264654315205908</v>
+        <v>0.008286771064055978</v>
       </c>
     </row>
     <row r="98">
@@ -3264,28 +3264,28 @@
         <v>96</v>
       </c>
       <c r="B98" t="n">
-        <v>0.001635016309566796</v>
+        <v>0.001727679281249642</v>
       </c>
       <c r="C98" t="n">
-        <v>0.0002253855405347422</v>
+        <v>0.0002251445614947006</v>
       </c>
       <c r="D98" t="n">
-        <v>0.1240997959218025</v>
+        <v>0.1212474474563599</v>
       </c>
       <c r="E98" t="n">
-        <v>0.000789131810059771</v>
+        <v>0.0008962975066751242</v>
       </c>
       <c r="F98" t="n">
-        <v>0.00723982326944661</v>
+        <v>0.00660915018264417</v>
       </c>
       <c r="G98" t="n">
-        <v>0.0002228805733685872</v>
+        <v>0.0002229764545174941</v>
       </c>
       <c r="H98" t="n">
-        <v>0.122382572268973</v>
+        <v>0.1260321806743133</v>
       </c>
       <c r="I98" t="n">
-        <v>0.006405029905592297</v>
+        <v>0.005756012866574341</v>
       </c>
     </row>
     <row r="99">
@@ -3293,28 +3293,28 @@
         <v>97</v>
       </c>
       <c r="B99" t="n">
-        <v>0.001615341113656759</v>
+        <v>0.001695202600046992</v>
       </c>
       <c r="C99" t="n">
-        <v>0.0002225109317395836</v>
+        <v>0.0002301982436068356</v>
       </c>
       <c r="D99" t="n">
-        <v>0.123677942173481</v>
+        <v>0.12116580646801</v>
       </c>
       <c r="E99" t="n">
-        <v>0.0007744404908008874</v>
+        <v>0.0008591753384172917</v>
       </c>
       <c r="F99" t="n">
-        <v>0.008146853435474643</v>
+        <v>0.008490596623395434</v>
       </c>
       <c r="G99" t="n">
-        <v>0.0002757545771437346</v>
+        <v>0.0001953380992402494</v>
       </c>
       <c r="H99" t="n">
-        <v>0.1207691661685365</v>
+        <v>0.1211493556101793</v>
       </c>
       <c r="I99" t="n">
-        <v>0.007267253084038346</v>
+        <v>0.007689511721792705</v>
       </c>
     </row>
     <row r="100">
@@ -3322,28 +3322,28 @@
         <v>98</v>
       </c>
       <c r="B100" t="n">
-        <v>0.001561192274399102</v>
+        <v>0.001655171535544097</v>
       </c>
       <c r="C100" t="n">
-        <v>0.0002299277839716524</v>
+        <v>0.0002246683582449332</v>
       </c>
       <c r="D100" t="n">
-        <v>0.124254970685482</v>
+        <v>0.1209778276252747</v>
       </c>
       <c r="E100" t="n">
-        <v>0.0007099896457269788</v>
+        <v>0.000825614050462842</v>
       </c>
       <c r="F100" t="n">
-        <v>0.006764579017693708</v>
+        <v>0.007246232850455829</v>
       </c>
       <c r="G100" t="n">
-        <v>0.0002294839400251899</v>
+        <v>0.0002522629182987055</v>
       </c>
       <c r="H100" t="n">
-        <v>0.1259329633008792</v>
+        <v>0.1231924765956927</v>
       </c>
       <c r="I100" t="n">
-        <v>0.005905430191705462</v>
+        <v>0.006378007588230475</v>
       </c>
     </row>
     <row r="101">
@@ -3351,28 +3351,28 @@
         <v>99</v>
       </c>
       <c r="B101" t="n">
-        <v>0.001550982524365187</v>
+        <v>0.001632784248992801</v>
       </c>
       <c r="C101" t="n">
-        <v>0.000219753052726388</v>
+        <v>0.0002319763839598745</v>
       </c>
       <c r="D101" t="n">
-        <v>0.1242485816159248</v>
+        <v>0.1211489258728027</v>
       </c>
       <c r="E101" t="n">
-        <v>0.0007099865847229957</v>
+        <v>0.0007950632558017969</v>
       </c>
       <c r="F101" t="n">
-        <v>0.007576946513286715</v>
+        <v>0.007914255090471096</v>
       </c>
       <c r="G101" t="n">
-        <v>0.0002351550371881778</v>
+        <v>0.0002070000278431129</v>
       </c>
       <c r="H101" t="n">
-        <v>0.1226596431470617</v>
+        <v>0.1202357498477373</v>
       </c>
       <c r="I101" t="n">
-        <v>0.00672849328577713</v>
+        <v>0.007106076379414484</v>
       </c>
     </row>
     <row r="102">
@@ -3380,28 +3380,28 @@
         <v>100</v>
       </c>
       <c r="B102" t="n">
-        <v>0.001510760505795479</v>
+        <v>0.001575866983965039</v>
       </c>
       <c r="C102" t="n">
-        <v>0.0002236195176197216</v>
+        <v>0.0002209301683250815</v>
       </c>
       <c r="D102" t="n">
-        <v>0.1246402846956253</v>
+        <v>0.1210446735844612</v>
       </c>
       <c r="E102" t="n">
-        <v>0.0006639395834393799</v>
+        <v>0.0007497134729288518</v>
       </c>
       <c r="F102" t="n">
-        <v>0.007443481101418981</v>
+        <v>0.00708698887736529</v>
       </c>
       <c r="G102" t="n">
-        <v>0.000259841797747277</v>
+        <v>0.0002802830510738581</v>
       </c>
       <c r="H102" t="n">
-        <v>0.1279169415970611</v>
+        <v>0.1182721389866575</v>
       </c>
       <c r="I102" t="n">
-        <v>0.006544054561517951</v>
+        <v>0.006215345094293404</v>
       </c>
     </row>
     <row r="103">
@@ -3409,28 +3409,28 @@
         <v>101</v>
       </c>
       <c r="B103" t="n">
-        <v>0.001497475216276944</v>
+        <v>0.001597020766295493</v>
       </c>
       <c r="C103" t="n">
-        <v>0.0002174790464816615</v>
+        <v>0.0002235048886304721</v>
       </c>
       <c r="D103" t="n">
-        <v>0.1248959026417732</v>
+        <v>0.120597373105526</v>
       </c>
       <c r="E103" t="n">
-        <v>0.0006555166642852128</v>
+        <v>0.0007705290260836482</v>
       </c>
       <c r="F103" t="n">
-        <v>0.007661460798300596</v>
+        <v>0.006653375957847906</v>
       </c>
       <c r="G103" t="n">
-        <v>0.0002140037209645588</v>
+        <v>0.0002254513004324877</v>
       </c>
       <c r="H103" t="n">
-        <v>0.1216491218375537</v>
+        <v>0.1211068951038319</v>
       </c>
       <c r="I103" t="n">
-        <v>0.006839211539503606</v>
+        <v>0.005822390199929087</v>
       </c>
     </row>
     <row r="104">
@@ -3438,28 +3438,28 @@
         <v>102</v>
       </c>
       <c r="B104" t="n">
-        <v>0.001478135554209352</v>
+        <v>0.001545961397700012</v>
       </c>
       <c r="C104" t="n">
-        <v>0.0002228916734550148</v>
+        <v>0.0002182418710589409</v>
       </c>
       <c r="D104" t="n">
-        <v>0.1237877905726433</v>
+        <v>0.1212262766909599</v>
       </c>
       <c r="E104" t="n">
-        <v>0.0006363049270138144</v>
+        <v>0.0007215881427526474</v>
       </c>
       <c r="F104" t="n">
-        <v>0.007228906472953459</v>
+        <v>0.008140371893555364</v>
       </c>
       <c r="G104" t="n">
-        <v>0.0002516889651127458</v>
+        <v>0.0002057143138217562</v>
       </c>
       <c r="H104" t="n">
-        <v>0.1227620373586068</v>
+        <v>0.119185553577168</v>
       </c>
       <c r="I104" t="n">
-        <v>0.006363407355622308</v>
+        <v>0.007338729721219029</v>
       </c>
     </row>
     <row r="105">
@@ -3467,28 +3467,28 @@
         <v>103</v>
       </c>
       <c r="B105" t="n">
-        <v>0.001506871013075113</v>
+        <v>0.001546700217038393</v>
       </c>
       <c r="C105" t="n">
-        <v>0.000214682332450524</v>
+        <v>0.0002211392657859251</v>
       </c>
       <c r="D105" t="n">
-        <v>0.1246766132421493</v>
+        <v>0.1203028591136932</v>
       </c>
       <c r="E105" t="n">
-        <v>0.0006688056303970516</v>
+        <v>0.0007240466712415218</v>
       </c>
       <c r="F105" t="n">
-        <v>0.007147326923384168</v>
+        <v>0.00651913180540135</v>
       </c>
       <c r="G105" t="n">
-        <v>0.0002043139490784719</v>
+        <v>0.000238798776620408</v>
       </c>
       <c r="H105" t="n">
-        <v>0.127194872761045</v>
+        <v>0.1240944089279867</v>
       </c>
       <c r="I105" t="n">
-        <v>0.006307038632487395</v>
+        <v>0.005659860961114893</v>
       </c>
     </row>
     <row r="106">
@@ -3496,28 +3496,28 @@
         <v>104</v>
       </c>
       <c r="B106" t="n">
-        <v>0.001410242360912263</v>
+        <v>0.001505479407958686</v>
       </c>
       <c r="C106" t="n">
-        <v>0.0002195072638895363</v>
+        <v>0.0002212557616326958</v>
       </c>
       <c r="D106" t="n">
-        <v>0.123678805024147</v>
+        <v>0.1201240554332733</v>
       </c>
       <c r="E106" t="n">
-        <v>0.0005723410892412066</v>
+        <v>0.0006836033932939171</v>
       </c>
       <c r="F106" t="n">
-        <v>0.006217337869606049</v>
+        <v>0.008100863784630624</v>
       </c>
       <c r="G106" t="n">
-        <v>0.0002123792138344534</v>
+        <v>0.0002000522409893533</v>
       </c>
       <c r="H106" t="n">
-        <v>0.1291075407107153</v>
+        <v>0.1206236180945088</v>
       </c>
       <c r="I106" t="n">
-        <v>0.005359420934889532</v>
+        <v>0.007297693563391246</v>
       </c>
     </row>
     <row r="107">
@@ -3525,28 +3525,28 @@
         <v>105</v>
       </c>
       <c r="B107" t="n">
-        <v>0.001418085063189268</v>
+        <v>0.001481323425121605</v>
       </c>
       <c r="C107" t="n">
-        <v>0.0002134684684379026</v>
+        <v>0.0002105341321416199</v>
       </c>
       <c r="D107" t="n">
-        <v>0.1241339886922836</v>
+        <v>0.1202830305356979</v>
       </c>
       <c r="E107" t="n">
-        <v>0.0005839466716051102</v>
+        <v>0.0006693741654604673</v>
       </c>
       <c r="F107" t="n">
-        <v>0.007236015866092766</v>
+        <v>0.007538163409420998</v>
       </c>
       <c r="G107" t="n">
-        <v>0.0001901874905923111</v>
+        <v>0.0002022571992478523</v>
       </c>
       <c r="H107" t="n">
-        <v>0.1253653056664335</v>
+        <v>0.1210044536490425</v>
       </c>
       <c r="I107" t="n">
-        <v>0.006419001851461791</v>
+        <v>0.006730883899942454</v>
       </c>
     </row>
     <row r="108">
@@ -3554,28 +3554,28 @@
         <v>106</v>
       </c>
       <c r="B108" t="n">
-        <v>0.001386875414125621</v>
+        <v>0.001482136129066348</v>
       </c>
       <c r="C108" t="n">
-        <v>0.0002159609826039523</v>
+        <v>0.0002173566592270508</v>
       </c>
       <c r="D108" t="n">
-        <v>0.1246621565408707</v>
+        <v>0.1205450075211525</v>
       </c>
       <c r="E108" t="n">
-        <v>0.0005476036633700132</v>
+        <v>0.0006620544508360326</v>
       </c>
       <c r="F108" t="n">
-        <v>0.006472641225041272</v>
+        <v>0.006575739754524939</v>
       </c>
       <c r="G108" t="n">
-        <v>0.0001963580271533385</v>
+        <v>0.0002608102290502933</v>
       </c>
       <c r="H108" t="n">
-        <v>0.1275632559057161</v>
+        <v>0.1224343522590681</v>
       </c>
       <c r="I108" t="n">
-        <v>0.005638466942174205</v>
+        <v>0.005702757781544673</v>
       </c>
     </row>
     <row r="109">
@@ -3583,28 +3583,28 @@
         <v>107</v>
       </c>
       <c r="B109" t="n">
-        <v>0.001396529209680855</v>
+        <v>0.001454909569203854</v>
       </c>
       <c r="C109" t="n">
-        <v>0.0002153955549513921</v>
+        <v>0.0002148328542858362</v>
       </c>
       <c r="D109" t="n">
-        <v>0.1241168879089355</v>
+        <v>0.120761657772541</v>
       </c>
       <c r="E109" t="n">
-        <v>0.0005605492359921336</v>
+        <v>0.0006362684284485876</v>
       </c>
       <c r="F109" t="n">
-        <v>0.008122108534501097</v>
+        <v>0.007389407610888387</v>
       </c>
       <c r="G109" t="n">
-        <v>0.000193259157078017</v>
+        <v>0.0001834618136334973</v>
       </c>
       <c r="H109" t="n">
-        <v>0.1221816987679211</v>
+        <v>0.1190837878348582</v>
       </c>
       <c r="I109" t="n">
-        <v>0.007317941017406362</v>
+        <v>0.006610526927271296</v>
       </c>
     </row>
     <row r="110">
@@ -3612,28 +3612,28 @@
         <v>108</v>
       </c>
       <c r="B110" t="n">
-        <v>0.001360782482147217</v>
+        <v>0.001417351125925779</v>
       </c>
       <c r="C110" t="n">
-        <v>0.0002104076950708404</v>
+        <v>0.0002156896136142313</v>
       </c>
       <c r="D110" t="n">
-        <v>0.1242910954046249</v>
+        <v>0.1202429667725563</v>
       </c>
       <c r="E110" t="n">
-        <v>0.0005289193325638771</v>
+        <v>0.0006004466907083988</v>
       </c>
       <c r="F110" t="n">
-        <v>0.007750557749235902</v>
+        <v>0.006809162271754485</v>
       </c>
       <c r="G110" t="n">
-        <v>0.0002047975712919571</v>
+        <v>0.0002330212639752991</v>
       </c>
       <c r="H110" t="n">
-        <v>0.1223742691917287</v>
+        <v>0.1218297914404659</v>
       </c>
       <c r="I110" t="n">
-        <v>0.006933888746410316</v>
+        <v>0.005966992049582825</v>
       </c>
     </row>
     <row r="111">
@@ -3641,28 +3641,28 @@
         <v>109</v>
       </c>
       <c r="B111" t="n">
-        <v>0.001346184910133481</v>
+        <v>0.00141653953961283</v>
       </c>
       <c r="C111" t="n">
-        <v>0.0002106532559497282</v>
+        <v>0.0002115888306759298</v>
       </c>
       <c r="D111" t="n">
-        <v>0.124126355922699</v>
+        <v>0.1206521624240875</v>
       </c>
       <c r="E111" t="n">
-        <v>0.0005148998920638115</v>
+        <v>0.0006016899165548384</v>
       </c>
       <c r="F111" t="n">
-        <v>0.007179124816146119</v>
+        <v>0.006949331414890377</v>
       </c>
       <c r="G111" t="n">
-        <v>0.0002305068554953774</v>
+        <v>0.0001993357496306477</v>
       </c>
       <c r="H111" t="n">
-        <v>0.1235586811949728</v>
+        <v>0.1184349853568521</v>
       </c>
       <c r="I111" t="n">
-        <v>0.006330824639970288</v>
+        <v>0.006157820788052596</v>
       </c>
     </row>
     <row r="112">
@@ -3670,28 +3670,28 @@
         <v>110</v>
       </c>
       <c r="B112" t="n">
-        <v>0.001339798162586987</v>
+        <v>0.001406862830117345</v>
       </c>
       <c r="C112" t="n">
-        <v>0.0002059215652393177</v>
+        <v>0.0002110840820353478</v>
       </c>
       <c r="D112" t="n">
-        <v>0.1244407280068398</v>
+        <v>0.1200012637991905</v>
       </c>
       <c r="E112" t="n">
-        <v>0.000511672959022224</v>
+        <v>0.0005957724267914891</v>
       </c>
       <c r="F112" t="n">
-        <v>0.006847122710799802</v>
+        <v>0.006569237050708219</v>
       </c>
       <c r="G112" t="n">
-        <v>0.0001865181773479384</v>
+        <v>0.0002019029826681292</v>
       </c>
       <c r="H112" t="n">
-        <v>0.122859508590636</v>
+        <v>0.1208002782947282</v>
       </c>
       <c r="I112" t="n">
-        <v>0.006046306957440606</v>
+        <v>0.005763332740560199</v>
       </c>
     </row>
     <row r="113">
@@ -3699,28 +3699,28 @@
         <v>111</v>
       </c>
       <c r="B113" t="n">
-        <v>0.001332115645475686</v>
+        <v>0.001346067487820983</v>
       </c>
       <c r="C113" t="n">
-        <v>0.0002088847715295851</v>
+        <v>0.0002084111578315496</v>
       </c>
       <c r="D113" t="n">
-        <v>0.1244011955718994</v>
+        <v>0.1201816346898079</v>
       </c>
       <c r="E113" t="n">
-        <v>0.0005012248979043215</v>
+        <v>0.0005367481719888747</v>
       </c>
       <c r="F113" t="n">
-        <v>0.00694097946126008</v>
+        <v>0.007188101638302961</v>
       </c>
       <c r="G113" t="n">
-        <v>0.0002401910143863367</v>
+        <v>0.0001938089220780806</v>
       </c>
       <c r="H113" t="n">
-        <v>0.1256269827917777</v>
+        <v>0.1212952954262544</v>
       </c>
       <c r="I113" t="n">
-        <v>0.006072653515072962</v>
+        <v>0.00638781621878994</v>
       </c>
     </row>
     <row r="114">
@@ -3728,28 +3728,28 @@
         <v>112</v>
       </c>
       <c r="B114" t="n">
-        <v>0.001300011467918754</v>
+        <v>0.001368612908154726</v>
       </c>
       <c r="C114" t="n">
-        <v>0.0002074654186870903</v>
+        <v>0.0002105160661293194</v>
       </c>
       <c r="D114" t="n">
-        <v>0.1246848735542297</v>
+        <v>0.119983066737175</v>
       </c>
       <c r="E114" t="n">
-        <v>0.0004691217111349106</v>
+        <v>0.0005581815222017467</v>
       </c>
       <c r="F114" t="n">
-        <v>0.007247169075099232</v>
+        <v>0.006520005326663397</v>
       </c>
       <c r="G114" t="n">
-        <v>0.0002080305938595271</v>
+        <v>0.0002154514180174626</v>
       </c>
       <c r="H114" t="n">
-        <v>0.1214366916745755</v>
+        <v>0.1212187938000794</v>
       </c>
       <c r="I114" t="n">
-        <v>0.006431955097768863</v>
+        <v>0.005698459973896065</v>
       </c>
     </row>
     <row r="115">
@@ -3757,28 +3757,28 @@
         <v>113</v>
       </c>
       <c r="B115" t="n">
-        <v>0.001294585784763098</v>
+        <v>0.001324387527152896</v>
       </c>
       <c r="C115" t="n">
-        <v>0.0002090384587608278</v>
+        <v>0.0002075822202181444</v>
       </c>
       <c r="D115" t="n">
-        <v>0.1241974031376839</v>
+        <v>0.1200454883713722</v>
       </c>
       <c r="E115" t="n">
-        <v>0.0004645603089947254</v>
+        <v>0.0005165778749939054</v>
       </c>
       <c r="F115" t="n">
-        <v>0.007660858798012453</v>
+        <v>0.007889527243761069</v>
       </c>
       <c r="G115" t="n">
-        <v>0.0002087815304903608</v>
+        <v>0.0002103931157799213</v>
       </c>
       <c r="H115" t="n">
-        <v>0.1222759434580803</v>
+        <v>0.1194699221543153</v>
       </c>
       <c r="I115" t="n">
-        <v>0.006840697557104791</v>
+        <v>0.007081784534391143</v>
       </c>
     </row>
     <row r="116">
@@ -3786,28 +3786,28 @@
         <v>114</v>
       </c>
       <c r="B116" t="n">
-        <v>0.001274703474834561</v>
+        <v>0.001332629250392318</v>
       </c>
       <c r="C116" t="n">
-        <v>0.0002051350305797532</v>
+        <v>0.000206484976362437</v>
       </c>
       <c r="D116" t="n">
-        <v>0.1239945302906036</v>
+        <v>0.1198109846816063</v>
       </c>
       <c r="E116" t="n">
-        <v>0.0004495958048868924</v>
+        <v>0.0005270893518850207</v>
       </c>
       <c r="F116" t="n">
-        <v>0.007630391627106494</v>
+        <v>0.006495343414948096</v>
       </c>
       <c r="G116" t="n">
-        <v>0.0002070871069273405</v>
+        <v>0.0002137091790592195</v>
       </c>
       <c r="H116" t="n">
-        <v>0.1215411585248508</v>
+        <v>0.1202729760176011</v>
       </c>
       <c r="I116" t="n">
-        <v>0.006815598784515947</v>
+        <v>0.005680269397047711</v>
       </c>
     </row>
     <row r="117">
@@ -3815,28 +3815,28 @@
         <v>115</v>
       </c>
       <c r="B117" t="n">
-        <v>0.001272067036338151</v>
+        <v>0.001316188136458397</v>
       </c>
       <c r="C117" t="n">
-        <v>0.000203697797623463</v>
+        <v>0.0002038778814636171</v>
       </c>
       <c r="D117" t="n">
-        <v>0.1242231484107971</v>
+        <v>0.1211190251550675</v>
       </c>
       <c r="E117" t="n">
-        <v>0.0004472535011023283</v>
+        <v>0.0005067151366956532</v>
       </c>
       <c r="F117" t="n">
-        <v>0.007225971087588523</v>
+        <v>0.007519926559939665</v>
       </c>
       <c r="G117" t="n">
-        <v>0.0002186228736365658</v>
+        <v>0.0001883670009456523</v>
       </c>
       <c r="H117" t="n">
-        <v>0.1245104294485408</v>
+        <v>0.1210170846671887</v>
       </c>
       <c r="I117" t="n">
-        <v>0.006384796130776308</v>
+        <v>0.006726474125624967</v>
       </c>
     </row>
     <row r="118">
@@ -3844,28 +3844,28 @@
         <v>116</v>
       </c>
       <c r="B118" t="n">
-        <v>0.001251756500907242</v>
+        <v>0.001286070445537567</v>
       </c>
       <c r="C118" t="n">
-        <v>0.0002039617748167366</v>
+        <v>0.0002068651011670008</v>
       </c>
       <c r="D118" t="n">
-        <v>0.1242388562364578</v>
+        <v>0.1208601201591492</v>
       </c>
       <c r="E118" t="n">
-        <v>0.0004266004459187389</v>
+        <v>0.0004749047605805099</v>
       </c>
       <c r="F118" t="n">
-        <v>0.00814585679743992</v>
+        <v>0.006497880711537736</v>
       </c>
       <c r="G118" t="n">
-        <v>0.0002038954534208201</v>
+        <v>0.0001923708881853151</v>
       </c>
       <c r="H118" t="n">
-        <v>0.122583284154899</v>
+        <v>0.1237681056634442</v>
       </c>
       <c r="I118" t="n">
-        <v>0.00732904501301867</v>
+        <v>0.005686669293092184</v>
       </c>
     </row>
     <row r="119">
@@ -3873,28 +3873,28 @@
         <v>117</v>
       </c>
       <c r="B119" t="n">
-        <v>0.001230337938755751</v>
+        <v>0.001265245264723897</v>
       </c>
       <c r="C119" t="n">
-        <v>0.0002019389362363145</v>
+        <v>0.0002063365067066625</v>
       </c>
       <c r="D119" t="n">
-        <v>0.12415625912714</v>
+        <v>0.1205211926393509</v>
       </c>
       <c r="E119" t="n">
-        <v>0.0004076177202314138</v>
+        <v>0.0004563028147909791</v>
       </c>
       <c r="F119" t="n">
-        <v>0.006872753618166556</v>
+        <v>0.007719462855580774</v>
       </c>
       <c r="G119" t="n">
-        <v>0.0002124223898179741</v>
+        <v>0.0001885851865731556</v>
       </c>
       <c r="H119" t="n">
-        <v>0.1238814717540928</v>
+        <v>0.1197937052649542</v>
       </c>
       <c r="I119" t="n">
-        <v>0.006040923874886011</v>
+        <v>0.006931909193842387</v>
       </c>
     </row>
     <row r="120">
@@ -3902,28 +3902,28 @@
         <v>118</v>
       </c>
       <c r="B120" t="n">
-        <v>0.001219316172666848</v>
+        <v>0.001222168386019766</v>
       </c>
       <c r="C120" t="n">
-        <v>0.0002023686009366065</v>
+        <v>0.0002024650377510116</v>
       </c>
       <c r="D120" t="n">
-        <v>0.1246979267864227</v>
+        <v>0.1200105537548065</v>
       </c>
       <c r="E120" t="n">
-        <v>0.0003934579434394837</v>
+        <v>0.000419650598777458</v>
       </c>
       <c r="F120" t="n">
-        <v>0.007087629498704223</v>
+        <v>0.007264785292341114</v>
       </c>
       <c r="G120" t="n">
-        <v>0.0001923008215813829</v>
+        <v>0.0002084483562373871</v>
       </c>
       <c r="H120" t="n">
-        <v>0.1231006301003607</v>
+        <v>0.1186470864078738</v>
       </c>
       <c r="I120" t="n">
-        <v>0.006279825572817788</v>
+        <v>0.006463101609635849</v>
       </c>
     </row>
     <row r="121">
@@ -3931,28 +3931,28 @@
         <v>119</v>
       </c>
       <c r="B121" t="n">
-        <v>0.001200846335336566</v>
+        <v>0.001237639409556985</v>
       </c>
       <c r="C121" t="n">
-        <v>0.0002020188957285136</v>
+        <v>0.0001993565082186833</v>
       </c>
       <c r="D121" t="n">
-        <v>0.1239204270677566</v>
+        <v>0.1207969944682121</v>
       </c>
       <c r="E121" t="n">
-        <v>0.0003792253175005317</v>
+        <v>0.0004342979431468993</v>
       </c>
       <c r="F121" t="n">
-        <v>0.00686709291939768</v>
+        <v>0.006894060844376221</v>
       </c>
       <c r="G121" t="n">
-        <v>0.0001950107480569851</v>
+        <v>0.0002234978555700913</v>
       </c>
       <c r="H121" t="n">
-        <v>0.126574918372985</v>
+        <v>0.1212607043830839</v>
       </c>
       <c r="I121" t="n">
-        <v>0.00603920763147293</v>
+        <v>0.006064259462167933</v>
       </c>
     </row>
     <row r="122">
@@ -3960,28 +3960,28 @@
         <v>120</v>
       </c>
       <c r="B122" t="n">
-        <v>0.00119315774679184</v>
+        <v>0.001230636479847133</v>
       </c>
       <c r="C122" t="n">
-        <v>0.0002019163340721279</v>
+        <v>0.0002012450391119346</v>
       </c>
       <c r="D122" t="n">
-        <v>0.1245525603113175</v>
+        <v>0.1213432973337173</v>
       </c>
       <c r="E122" t="n">
-        <v>0.0003684786188621074</v>
+        <v>0.0004226749649811536</v>
       </c>
       <c r="F122" t="n">
-        <v>0.007230599011077286</v>
+        <v>0.007192117937036818</v>
       </c>
       <c r="G122" t="n">
-        <v>0.0001852350628569792</v>
+        <v>0.0002024995302629534</v>
       </c>
       <c r="H122" t="n">
-        <v>0.124563456014844</v>
+        <v>0.1197606986513146</v>
       </c>
       <c r="I122" t="n">
-        <v>0.006422546781101195</v>
+        <v>0.006390814816497181</v>
       </c>
     </row>
     <row r="123">
@@ -3989,28 +3989,28 @@
         <v>121</v>
       </c>
       <c r="B123" t="n">
-        <v>0.001179411083050072</v>
+        <v>0.001220985155180097</v>
       </c>
       <c r="C123" t="n">
-        <v>0.0001975273128291592</v>
+        <v>0.0002015743536716327</v>
       </c>
       <c r="D123" t="n">
-        <v>0.1246861690921783</v>
+        <v>0.1211313009033203</v>
       </c>
       <c r="E123" t="n">
-        <v>0.0003584529469888657</v>
+        <v>0.0004137543284371495</v>
       </c>
       <c r="F123" t="n">
-        <v>0.007117198729738715</v>
+        <v>0.006811960488253959</v>
       </c>
       <c r="G123" t="n">
-        <v>0.0001860395623293142</v>
+        <v>0.0002065914172858082</v>
       </c>
       <c r="H123" t="n">
-        <v>0.1252272526523612</v>
+        <v>0.1226203690500866</v>
       </c>
       <c r="I123" t="n">
-        <v>0.006305022845698025</v>
+        <v>0.005992267221686404</v>
       </c>
     </row>
     <row r="124">
@@ -4018,28 +4018,28 @@
         <v>122</v>
       </c>
       <c r="B124" t="n">
-        <v>0.00117409008936584</v>
+        <v>0.001201439327672124</v>
       </c>
       <c r="C124" t="n">
-        <v>0.0001984668263737112</v>
+        <v>0.0001974954163460061</v>
       </c>
       <c r="D124" t="n">
-        <v>0.1247519172244072</v>
+        <v>0.1214204484667778</v>
       </c>
       <c r="E124" t="n">
-        <v>0.0003518636909760535</v>
+        <v>0.0003968416804857552</v>
       </c>
       <c r="F124" t="n">
-        <v>0.007222144088022666</v>
+        <v>0.007586600057671354</v>
       </c>
       <c r="G124" t="n">
-        <v>0.0002114550926470764</v>
+        <v>0.000185270842275283</v>
       </c>
       <c r="H124" t="n">
-        <v>0.1250073520851369</v>
+        <v>0.1207725742352339</v>
       </c>
       <c r="I124" t="n">
-        <v>0.006385652216768187</v>
+        <v>0.006797466288923877</v>
       </c>
     </row>
     <row r="125">
@@ -4047,28 +4047,28 @@
         <v>123</v>
       </c>
       <c r="B125" t="n">
-        <v>0.001146764127507806</v>
+        <v>0.001192562716305256</v>
       </c>
       <c r="C125" t="n">
-        <v>0.0002014311917601153</v>
+        <v>0.0001995252337828279</v>
       </c>
       <c r="D125" t="n">
-        <v>0.1243064233241081</v>
+        <v>0.1213492552676201</v>
       </c>
       <c r="E125" t="n">
-        <v>0.0003238008352313191</v>
+        <v>0.0003862912208177149</v>
       </c>
       <c r="F125" t="n">
-        <v>0.007508738108137304</v>
+        <v>0.006628584889649469</v>
       </c>
       <c r="G125" t="n">
-        <v>0.0001969387261666051</v>
+        <v>0.0002030297010858979</v>
       </c>
       <c r="H125" t="n">
-        <v>0.1222568494810755</v>
+        <v>0.1214494826203458</v>
       </c>
       <c r="I125" t="n">
-        <v>0.00670051521550238</v>
+        <v>0.005818307756326279</v>
       </c>
     </row>
     <row r="126">
@@ -4076,28 +4076,28 @@
         <v>124</v>
       </c>
       <c r="B126" t="n">
-        <v>0.001146701680406928</v>
+        <v>0.001177896197609603</v>
       </c>
       <c r="C126" t="n">
-        <v>0.000195956008112058</v>
+        <v>0.0001985064667696133</v>
       </c>
       <c r="D126" t="n">
-        <v>0.1246884887876511</v>
+        <v>0.121232104575634</v>
       </c>
       <c r="E126" t="n">
-        <v>0.0003273032460976392</v>
+        <v>0.000373229213302955</v>
       </c>
       <c r="F126" t="n">
-        <v>0.006703409786817738</v>
+        <v>0.007370462772994018</v>
       </c>
       <c r="G126" t="n">
-        <v>0.0002234722192592533</v>
+        <v>0.0001915349506926502</v>
       </c>
       <c r="H126" t="n">
-        <v>0.1237673655580152</v>
+        <v>0.1198110312738776</v>
       </c>
       <c r="I126" t="n">
-        <v>0.00586110074480245</v>
+        <v>0.006579872768031977</v>
       </c>
     </row>
     <row r="127">
@@ -4105,28 +4105,28 @@
         <v>125</v>
       </c>
       <c r="B127" t="n">
-        <v>0.001130444906324148</v>
+        <v>0.00115876440897584</v>
       </c>
       <c r="C127" t="n">
-        <v>0.0001966218215906993</v>
+        <v>0.0001979463082989678</v>
       </c>
       <c r="D127" t="n">
-        <v>0.1248172268838882</v>
+        <v>0.1213535271811485</v>
       </c>
       <c r="E127" t="n">
-        <v>0.0003097369787748903</v>
+        <v>0.0003540504840053618</v>
       </c>
       <c r="F127" t="n">
-        <v>0.007003388361637686</v>
+        <v>0.007017595670588594</v>
       </c>
       <c r="G127" t="n">
-        <v>0.0002271072531033909</v>
+        <v>0.0002092410282586621</v>
       </c>
       <c r="H127" t="n">
-        <v>0.1245550244380561</v>
+        <v>0.1227200647692696</v>
       </c>
       <c r="I127" t="n">
-        <v>0.006153505965945771</v>
+        <v>0.006194754313513466</v>
       </c>
     </row>
     <row r="128">
@@ -4134,28 +4134,28 @@
         <v>126</v>
       </c>
       <c r="B128" t="n">
-        <v>0.001128332313656807</v>
+        <v>0.001159186624974012</v>
       </c>
       <c r="C128" t="n">
-        <v>0.0001963180130850524</v>
+        <v>0.0001951277319258079</v>
       </c>
       <c r="D128" t="n">
-        <v>0.1254956340551376</v>
+        <v>0.121615628259182</v>
       </c>
       <c r="E128" t="n">
-        <v>0.0003045361576657742</v>
+        <v>0.0003559807714931667</v>
       </c>
       <c r="F128" t="n">
-        <v>0.008205651467875691</v>
+        <v>0.00700530872946122</v>
       </c>
       <c r="G128" t="n">
-        <v>0.0002024042608053461</v>
+        <v>0.0002052045046918924</v>
       </c>
       <c r="H128" t="n">
-        <v>0.123087612027348</v>
+        <v>0.1207700302030095</v>
       </c>
       <c r="I128" t="n">
-        <v>0.007387809081224886</v>
+        <v>0.006196254119793558</v>
       </c>
     </row>
     <row r="129">
@@ -4163,28 +4163,28 @@
         <v>127</v>
       </c>
       <c r="B129" t="n">
-        <v>0.001109764756478369</v>
+        <v>0.00112523017424345</v>
       </c>
       <c r="C129" t="n">
-        <v>0.0001959139881115407</v>
+        <v>0.0001968552350681275</v>
       </c>
       <c r="D129" t="n">
-        <v>0.1252042280673981</v>
+        <v>0.1219008125562668</v>
       </c>
       <c r="E129" t="n">
-        <v>0.0002878296360373497</v>
+        <v>0.0003188708901833743</v>
       </c>
       <c r="F129" t="n">
-        <v>0.007800978592446539</v>
+        <v>0.006701305272273391</v>
       </c>
       <c r="G129" t="n">
-        <v>0.0002055648304875271</v>
+        <v>0.0002074778681329632</v>
       </c>
       <c r="H129" t="n">
-        <v>0.1229115016897001</v>
+        <v>0.1238930948460277</v>
       </c>
       <c r="I129" t="n">
-        <v>0.006980856302335591</v>
+        <v>0.005874361912423644</v>
       </c>
     </row>
     <row r="130">
@@ -4192,28 +4192,28 @@
         <v>128</v>
       </c>
       <c r="B130" t="n">
-        <v>0.001111234126061201</v>
+        <v>0.001131729385606945</v>
       </c>
       <c r="C130" t="n">
-        <v>0.0001962704786891118</v>
+        <v>0.0001954938055062666</v>
       </c>
       <c r="D130" t="n">
-        <v>0.1250056565160751</v>
+        <v>0.1220284189629555</v>
       </c>
       <c r="E130" t="n">
-        <v>0.000289935387596488</v>
+        <v>0.000326093493510969</v>
       </c>
       <c r="F130" t="n">
-        <v>0.006634540001134013</v>
+        <v>0.007213657956059907</v>
       </c>
       <c r="G130" t="n">
-        <v>0.000192446019174797</v>
+        <v>0.0001959667383736078</v>
       </c>
       <c r="H130" t="n">
-        <v>0.1264262786356893</v>
+        <v>0.1207756319063523</v>
       </c>
       <c r="I130" t="n">
-        <v>0.00580996254960388</v>
+        <v>0.006413813063883956</v>
       </c>
     </row>
     <row r="131">
@@ -4221,28 +4221,28 @@
         <v>129</v>
       </c>
       <c r="B131" t="n">
-        <v>0.001102155915133655</v>
+        <v>0.001117645957797766</v>
       </c>
       <c r="C131" t="n">
-        <v>0.0001939063465939835</v>
+        <v>0.000194673332285136</v>
       </c>
       <c r="D131" t="n">
-        <v>0.1251007582550049</v>
+        <v>0.1222851284852028</v>
       </c>
       <c r="E131" t="n">
-        <v>0.0002827457870077342</v>
+        <v>0.0003115470037115738</v>
       </c>
       <c r="F131" t="n">
-        <v>0.006860824438787353</v>
+        <v>0.006749071428798394</v>
       </c>
       <c r="G131" t="n">
-        <v>0.0001874920215142806</v>
+        <v>0.000207122317276026</v>
       </c>
       <c r="H131" t="n">
-        <v>0.1254125886017891</v>
+        <v>0.1217260340040893</v>
       </c>
       <c r="I131" t="n">
-        <v>0.006046269561329683</v>
+        <v>0.005933318929275768</v>
       </c>
     </row>
     <row r="132">
@@ -4250,28 +4250,28 @@
         <v>130</v>
       </c>
       <c r="B132" t="n">
-        <v>0.001082143738366663</v>
+        <v>0.001116672355376184</v>
       </c>
       <c r="C132" t="n">
-        <v>0.0001931277235634625</v>
+        <v>0.0001949766989462078</v>
       </c>
       <c r="D132" t="n">
-        <v>0.125565494433403</v>
+        <v>0.1219961215867996</v>
       </c>
       <c r="E132" t="n">
-        <v>0.000261188545435667</v>
+        <v>0.0003117150713177398</v>
       </c>
       <c r="F132" t="n">
-        <v>0.006427872399989437</v>
+        <v>0.007125049181355446</v>
       </c>
       <c r="G132" t="n">
-        <v>0.0001971797029486649</v>
+        <v>0.0001919634050638741</v>
       </c>
       <c r="H132" t="n">
-        <v>0.1288874640054454</v>
+        <v>0.1225906617441146</v>
       </c>
       <c r="I132" t="n">
-        <v>0.005586255341494793</v>
+        <v>0.006320132440560745</v>
       </c>
     </row>
     <row r="133">
@@ -4279,28 +4279,28 @@
         <v>131</v>
       </c>
       <c r="B133" t="n">
-        <v>0.001093260477244854</v>
+        <v>0.001110830659106374</v>
       </c>
       <c r="C133" t="n">
-        <v>0.0001934336823811755</v>
+        <v>0.0001928115092432126</v>
       </c>
       <c r="D133" t="n">
-        <v>0.1256141961164474</v>
+        <v>0.1221402914733887</v>
       </c>
       <c r="E133" t="n">
-        <v>0.0002717558265812695</v>
+        <v>0.0003073176934979856</v>
       </c>
       <c r="F133" t="n">
-        <v>0.007279398055294404</v>
+        <v>0.006731862656067187</v>
       </c>
       <c r="G133" t="n">
-        <v>0.0001963544118536794</v>
+        <v>0.0001936567327209717</v>
       </c>
       <c r="H133" t="n">
-        <v>0.1252780031243895</v>
+        <v>0.1234107725028113</v>
       </c>
       <c r="I133" t="n">
-        <v>0.00645665360638966</v>
+        <v>0.00592115215884239</v>
       </c>
     </row>
     <row r="134">
@@ -4308,28 +4308,28 @@
         <v>132</v>
       </c>
       <c r="B134" t="n">
-        <v>0.001073211726538837</v>
+        <v>0.001092692996740341</v>
       </c>
       <c r="C134" t="n">
-        <v>0.000193528053265065</v>
+        <v>0.0001930494537986815</v>
       </c>
       <c r="D134" t="n">
-        <v>0.1256764906311035</v>
+        <v>0.1224619909501076</v>
       </c>
       <c r="E134" t="n">
-        <v>0.0002513012343086302</v>
+        <v>0.0002873335949257016</v>
       </c>
       <c r="F134" t="n">
-        <v>0.006838594421404026</v>
+        <v>0.008285804578448004</v>
       </c>
       <c r="G134" t="n">
-        <v>0.0002050868633258662</v>
+        <v>0.0001987276177930829</v>
       </c>
       <c r="H134" t="n">
-        <v>0.1275774301838914</v>
+        <v>0.1212439509535886</v>
       </c>
       <c r="I134" t="n">
-        <v>0.005995620401974214</v>
+        <v>0.007480857242536876</v>
       </c>
     </row>
     <row r="135">
@@ -4337,28 +4337,28 @@
         <v>133</v>
       </c>
       <c r="B135" t="n">
-        <v>0.001062792634159327</v>
+        <v>0.001086971045158804</v>
       </c>
       <c r="C135" t="n">
-        <v>0.000192779248682782</v>
+        <v>0.0001909117589071393</v>
       </c>
       <c r="D135" t="n">
-        <v>0.1256805346393585</v>
+        <v>0.1227092016830444</v>
       </c>
       <c r="E135" t="n">
-        <v>0.0002416107100732625</v>
+        <v>0.0002825132987052202</v>
       </c>
       <c r="F135" t="n">
-        <v>0.007249767539390707</v>
+        <v>0.006541459504909948</v>
       </c>
       <c r="G135" t="n">
-        <v>0.0001832495833713665</v>
+        <v>0.0001977170693542243</v>
       </c>
       <c r="H135" t="n">
-        <v>0.126007292648902</v>
+        <v>0.1253666334167779</v>
       </c>
       <c r="I135" t="n">
-        <v>0.006436481447981558</v>
+        <v>0.005716909287439668</v>
       </c>
     </row>
     <row r="136">
@@ -4366,28 +4366,28 @@
         <v>134</v>
       </c>
       <c r="B136" t="n">
-        <v>0.001051997493475676</v>
+        <v>0.001071749133139849</v>
       </c>
       <c r="C136" t="n">
-        <v>0.0001914829225949943</v>
+        <v>0.0001924707014560699</v>
       </c>
       <c r="D136" t="n">
-        <v>0.1258230919399261</v>
+        <v>0.1231178550834656</v>
       </c>
       <c r="E136" t="n">
-        <v>0.0002313991309143603</v>
+        <v>0.0002636891655772924</v>
       </c>
       <c r="F136" t="n">
-        <v>0.00692758546452392</v>
+        <v>0.007183838451028988</v>
       </c>
       <c r="G136" t="n">
-        <v>0.000191663615351435</v>
+        <v>0.0001852904524799242</v>
       </c>
       <c r="H136" t="n">
-        <v>0.1263743922819321</v>
+        <v>0.1232994606366554</v>
       </c>
       <c r="I136" t="n">
-        <v>0.006104049912819465</v>
+        <v>0.006382050798115052</v>
       </c>
     </row>
     <row r="137">
@@ -4395,28 +4395,28 @@
         <v>135</v>
       </c>
       <c r="B137" t="n">
-        <v>0.001050086403973401</v>
+        <v>0.001060441502563655</v>
       </c>
       <c r="C137" t="n">
-        <v>0.0001919275227710605</v>
+        <v>0.0001905068230712786</v>
       </c>
       <c r="D137" t="n">
-        <v>0.1256618215956688</v>
+        <v>0.1229543069214821</v>
       </c>
       <c r="E137" t="n">
-        <v>0.0002298497648276389</v>
+        <v>0.0002551631526043639</v>
       </c>
       <c r="F137" t="n">
-        <v>0.006763555529279723</v>
+        <v>0.006837204859651272</v>
       </c>
       <c r="G137" t="n">
-        <v>0.000190909691984867</v>
+        <v>0.0001981408691028403</v>
       </c>
       <c r="H137" t="n">
-        <v>0.1278655345171544</v>
+        <v>0.1235963544789185</v>
       </c>
       <c r="I137" t="n">
-        <v>0.005933318200322144</v>
+        <v>0.006021082256244553</v>
       </c>
     </row>
     <row r="138">
@@ -4424,28 +4424,28 @@
         <v>136</v>
       </c>
       <c r="B138" t="n">
-        <v>0.001039429571904242</v>
+        <v>0.001054844106033444</v>
       </c>
       <c r="C138" t="n">
-        <v>0.0001905621213549748</v>
+        <v>0.0001908457261575386</v>
       </c>
       <c r="D138" t="n">
-        <v>0.1260224284925461</v>
+        <v>0.1231012770719528</v>
       </c>
       <c r="E138" t="n">
-        <v>0.0002187553135091439</v>
+        <v>0.0002484920158069581</v>
       </c>
       <c r="F138" t="n">
-        <v>0.007092269335677437</v>
+        <v>0.006714884708065777</v>
       </c>
       <c r="G138" t="n">
-        <v>0.0001824759472255347</v>
+        <v>0.0001831039096487817</v>
       </c>
       <c r="H138" t="n">
-        <v>0.1264740835327114</v>
+        <v>0.1233799530869596</v>
       </c>
       <c r="I138" t="n">
-        <v>0.006277422980112168</v>
+        <v>0.0059148809701496</v>
       </c>
     </row>
     <row r="139">
@@ -4453,28 +4453,28 @@
         <v>137</v>
       </c>
       <c r="B139" t="n">
-        <v>0.001034967818938196</v>
+        <v>0.001045138433761895</v>
       </c>
       <c r="C139" t="n">
-        <v>0.0001898065635105595</v>
+        <v>0.0001900547987818718</v>
       </c>
       <c r="D139" t="n">
-        <v>0.1259763936266899</v>
+        <v>0.1233805710992813</v>
       </c>
       <c r="E139" t="n">
-        <v>0.0002152793099526316</v>
+        <v>0.0002381807971280068</v>
       </c>
       <c r="F139" t="n">
-        <v>0.006629414945889453</v>
+        <v>0.007159769695683657</v>
       </c>
       <c r="G139" t="n">
-        <v>0.0001910989602676746</v>
+        <v>0.0001986575481211417</v>
       </c>
       <c r="H139" t="n">
-        <v>0.1272433276549833</v>
+        <v>0.1229868960643087</v>
       </c>
       <c r="I139" t="n">
-        <v>0.005802099363905716</v>
+        <v>0.006346177721417359</v>
       </c>
     </row>
     <row r="140">
@@ -4482,28 +4482,28 @@
         <v>138</v>
       </c>
       <c r="B140" t="n">
-        <v>0.001028889524020255</v>
+        <v>0.001040736361987889</v>
       </c>
       <c r="C140" t="n">
-        <v>0.0001899805209068581</v>
+        <v>0.0001896635063514113</v>
       </c>
       <c r="D140" t="n">
-        <v>0.1262730336046219</v>
+        <v>0.1232925027470589</v>
       </c>
       <c r="E140" t="n">
-        <v>0.0002075438575809821</v>
+        <v>0.0002346103566465899</v>
       </c>
       <c r="F140" t="n">
-        <v>0.007468967626378742</v>
+        <v>0.00704029387449557</v>
       </c>
       <c r="G140" t="n">
-        <v>0.0001903170449433234</v>
+        <v>0.0001791793967465768</v>
       </c>
       <c r="H140" t="n">
-        <v>0.125542038296992</v>
+        <v>0.1242778777906012</v>
       </c>
       <c r="I140" t="n">
-        <v>0.006650940373625004</v>
+        <v>0.006239725136810376</v>
       </c>
     </row>
     <row r="141">
@@ -4511,28 +4511,28 @@
         <v>139</v>
       </c>
       <c r="B141" t="n">
-        <v>0.001018964140690863</v>
+        <v>0.001035244346864522</v>
       </c>
       <c r="C141" t="n">
-        <v>0.0001888689874680713</v>
+        <v>0.0001891101926211268</v>
       </c>
       <c r="D141" t="n">
-        <v>0.1262963894805908</v>
+        <v>0.1233432622361183</v>
       </c>
       <c r="E141" t="n">
-        <v>0.0001986132244439796</v>
+        <v>0.0002294178611570969</v>
       </c>
       <c r="F141" t="n">
-        <v>0.006900568506627254</v>
+        <v>0.006844539456616412</v>
       </c>
       <c r="G141" t="n">
-        <v>0.0001879493807122297</v>
+        <v>0.0001913812418478172</v>
       </c>
       <c r="H141" t="n">
-        <v>0.1278107783922752</v>
+        <v>0.1225359587325163</v>
       </c>
       <c r="I141" t="n">
-        <v>0.0060735651962216</v>
+        <v>0.00604047840737645</v>
       </c>
     </row>
     <row r="142">
@@ -4540,28 +4540,28 @@
         <v>140</v>
       </c>
       <c r="B142" t="n">
-        <v>0.001017461354210973</v>
+        <v>0.001018383459258825</v>
       </c>
       <c r="C142" t="n">
-        <v>0.000189529414864257</v>
+        <v>0.0001885826198291033</v>
       </c>
       <c r="D142" t="n">
-        <v>0.1265042093162537</v>
+        <v>0.1236044241127968</v>
       </c>
       <c r="E142" t="n">
-        <v>0.0001954109062310308</v>
+        <v>0.0002117787403268739</v>
       </c>
       <c r="F142" t="n">
-        <v>0.007381931455717779</v>
+        <v>0.00724299179730393</v>
       </c>
       <c r="G142" t="n">
-        <v>0.0001914955076233971</v>
+        <v>0.0001922715212084386</v>
       </c>
       <c r="H142" t="n">
-        <v>0.1256271980180242</v>
+        <v>0.1232764929975421</v>
       </c>
       <c r="I142" t="n">
-        <v>0.006562299935289979</v>
+        <v>0.006434337865761793</v>
       </c>
     </row>
     <row r="143">
@@ -4569,28 +4569,28 @@
         <v>141</v>
       </c>
       <c r="B143" t="n">
-        <v>0.001005725646026433</v>
+        <v>0.001035491864144802</v>
       </c>
       <c r="C143" t="n">
-        <v>0.0001873803703971207</v>
+        <v>0.0001893307331996038</v>
       </c>
       <c r="D143" t="n">
-        <v>0.1267904926624298</v>
+        <v>0.1236947705497742</v>
       </c>
       <c r="E143" t="n">
-        <v>0.0001843928252663463</v>
+        <v>0.0002276873066257685</v>
       </c>
       <c r="F143" t="n">
-        <v>0.006885334179078823</v>
+        <v>0.006733185549799906</v>
       </c>
       <c r="G143" t="n">
-        <v>0.0001890445329521617</v>
+        <v>0.0001839854843404788</v>
       </c>
       <c r="H143" t="n">
-        <v>0.1275910890608005</v>
+        <v>0.1250273465410142</v>
       </c>
       <c r="I143" t="n">
-        <v>0.006058334233376029</v>
+        <v>0.005924063270780916</v>
       </c>
     </row>
     <row r="144">
@@ -4598,28 +4598,28 @@
         <v>142</v>
       </c>
       <c r="B144" t="n">
-        <v>0.001006111730463803</v>
+        <v>0.001015239651337266</v>
       </c>
       <c r="C144" t="n">
-        <v>0.0001882287341468036</v>
+        <v>0.0001886635261494666</v>
       </c>
       <c r="D144" t="n">
-        <v>0.1269428295001984</v>
+        <v>0.1236470669879913</v>
       </c>
       <c r="E144" t="n">
-        <v>0.0001831688557816669</v>
+        <v>0.0002083407939113677</v>
       </c>
       <c r="F144" t="n">
-        <v>0.007177745619026084</v>
+        <v>0.007241236151091231</v>
       </c>
       <c r="G144" t="n">
-        <v>0.0001900961953638802</v>
+        <v>0.0001858996570846795</v>
       </c>
       <c r="H144" t="n">
-        <v>0.1258205942364735</v>
+        <v>0.1239898116451492</v>
       </c>
       <c r="I144" t="n">
-        <v>0.006358546497206071</v>
+        <v>0.006435387417625447</v>
       </c>
     </row>
     <row r="145">
@@ -4627,28 +4627,28 @@
         <v>143</v>
       </c>
       <c r="B145" t="n">
-        <v>0.0009956681044399739</v>
+        <v>0.001004327302977443</v>
       </c>
       <c r="C145" t="n">
-        <v>0.0001876347534554079</v>
+        <v>0.0001868591729169712</v>
       </c>
       <c r="D145" t="n">
-        <v>0.1269664912834167</v>
+        <v>0.1239746414084435</v>
       </c>
       <c r="E145" t="n">
-        <v>0.0001732009080834687</v>
+        <v>0.0001975949417576194</v>
       </c>
       <c r="F145" t="n">
-        <v>0.007519344004907237</v>
+        <v>0.006696700745643547</v>
       </c>
       <c r="G145" t="n">
-        <v>0.0001879892035499124</v>
+        <v>0.0001875219911243463</v>
       </c>
       <c r="H145" t="n">
-        <v>0.1261992493412817</v>
+        <v>0.1258342028169803</v>
       </c>
       <c r="I145" t="n">
-        <v>0.006700358591688156</v>
+        <v>0.005880007765227002</v>
       </c>
     </row>
     <row r="146">
@@ -4656,28 +4656,28 @@
         <v>144</v>
       </c>
       <c r="B146" t="n">
-        <v>0.001003360255330801</v>
+        <v>0.001012217047199607</v>
       </c>
       <c r="C146" t="n">
-        <v>0.0001867322670808062</v>
+        <v>0.0001870869661998004</v>
       </c>
       <c r="D146" t="n">
-        <v>0.127156277179718</v>
+        <v>0.1243823515863419</v>
       </c>
       <c r="E146" t="n">
-        <v>0.0001808465983523056</v>
+        <v>0.0002032183406669647</v>
       </c>
       <c r="F146" t="n">
-        <v>0.006891187773455317</v>
+        <v>0.006590766690331124</v>
       </c>
       <c r="G146" t="n">
-        <v>0.0001894851853644861</v>
+        <v>0.000186970641902613</v>
       </c>
       <c r="H146" t="n">
-        <v>0.1276558532236451</v>
+        <v>0.1244049431070029</v>
       </c>
       <c r="I146" t="n">
-        <v>0.006063423378979499</v>
+        <v>0.00578177139570186</v>
       </c>
     </row>
     <row r="147">
@@ -4685,28 +4685,28 @@
         <v>145</v>
       </c>
       <c r="B147" t="n">
-        <v>0.000985686970308423</v>
+        <v>0.0009968065903037786</v>
       </c>
       <c r="C147" t="n">
-        <v>0.0001881331917531788</v>
+        <v>0.0001862475549979135</v>
       </c>
       <c r="D147" t="n">
-        <v>0.1270884595432281</v>
+        <v>0.1243829732170105</v>
       </c>
       <c r="E147" t="n">
-        <v>0.000162111490403302</v>
+        <v>0.0001886441817488521</v>
       </c>
       <c r="F147" t="n">
-        <v>0.006966022016696304</v>
+        <v>0.007041957068848036</v>
       </c>
       <c r="G147" t="n">
-        <v>0.0001856892417345673</v>
+        <v>0.0001848678549606927</v>
       </c>
       <c r="H147" t="n">
-        <v>0.1270917023278372</v>
+        <v>0.1254312284074444</v>
       </c>
       <c r="I147" t="n">
-        <v>0.006144874363280772</v>
+        <v>0.006229933093971957</v>
       </c>
     </row>
     <row r="148">
@@ -4714,28 +4714,28 @@
         <v>146</v>
       </c>
       <c r="B148" t="n">
-        <v>0.0009882254014685751</v>
+        <v>0.0009897528023347258</v>
       </c>
       <c r="C148" t="n">
-        <v>0.0001861713339034468</v>
+        <v>0.0001862908233487979</v>
       </c>
       <c r="D148" t="n">
-        <v>0.1272264813871384</v>
+        <v>0.1247470713348389</v>
       </c>
       <c r="E148" t="n">
-        <v>0.0001659216779684648</v>
+        <v>0.0001797266386412084</v>
       </c>
       <c r="F148" t="n">
-        <v>0.006795314119317452</v>
+        <v>0.006838718778917149</v>
       </c>
       <c r="G148" t="n">
-        <v>0.0001883525754331549</v>
+        <v>0.0001858650917547404</v>
       </c>
       <c r="H148" t="n">
-        <v>0.1278377407614208</v>
+        <v>0.1258919950867555</v>
       </c>
       <c r="I148" t="n">
-        <v>0.005967772841714869</v>
+        <v>0.006023393705074005</v>
       </c>
     </row>
     <row r="149">
@@ -4743,28 +4743,28 @@
         <v>147</v>
       </c>
       <c r="B149" t="n">
-        <v>0.000978330828052014</v>
+        <v>0.0009878915729597212</v>
       </c>
       <c r="C149" t="n">
-        <v>0.0001863196354676038</v>
+        <v>0.0001854807967022061</v>
       </c>
       <c r="D149" t="n">
-        <v>0.127426956486702</v>
+        <v>0.1250953026943207</v>
       </c>
       <c r="E149" t="n">
-        <v>0.000154876414376311</v>
+        <v>0.0001769342689374462</v>
       </c>
       <c r="F149" t="n">
-        <v>0.00688762997679692</v>
+        <v>0.007049130372168286</v>
       </c>
       <c r="G149" t="n">
-        <v>0.000182912619163466</v>
+        <v>0.0001837287323280096</v>
       </c>
       <c r="H149" t="n">
-        <v>0.1275467528439268</v>
+        <v>0.12459086934612</v>
       </c>
       <c r="I149" t="n">
-        <v>0.006066983556724343</v>
+        <v>0.006242447236087933</v>
       </c>
     </row>
     <row r="150">
@@ -4772,28 +4772,28 @@
         <v>148</v>
       </c>
       <c r="B150" t="n">
-        <v>0.0009729444895349443</v>
+        <v>0.0009777021011710167</v>
       </c>
       <c r="C150" t="n">
-        <v>0.0001860369940092787</v>
+        <v>0.0001859592971932143</v>
       </c>
       <c r="D150" t="n">
-        <v>0.1275611635313034</v>
+        <v>0.1251929201965332</v>
       </c>
       <c r="E150" t="n">
-        <v>0.0001491016947748139</v>
+        <v>0.0001657782182293013</v>
       </c>
       <c r="F150" t="n">
-        <v>0.00670038973924751</v>
+        <v>0.006841876128503102</v>
       </c>
       <c r="G150" t="n">
-        <v>0.0001867987794462032</v>
+        <v>0.00018439121668088</v>
       </c>
       <c r="H150" t="n">
-        <v>0.1287718417642556</v>
+        <v>0.1260158856473195</v>
       </c>
       <c r="I150" t="n">
-        <v>0.005869731782323287</v>
+        <v>0.00602740545482124</v>
       </c>
     </row>
     <row r="151">
@@ -4801,28 +4801,28 @@
         <v>149</v>
       </c>
       <c r="B151" t="n">
-        <v>0.0009712672612741589</v>
+        <v>0.0009707898832857608</v>
       </c>
       <c r="C151" t="n">
-        <v>0.0001859163137217983</v>
+        <v>0.0001852823027474806</v>
       </c>
       <c r="D151" t="n">
-        <v>0.1276507153530121</v>
+        <v>0.1253217151422501</v>
       </c>
       <c r="E151" t="n">
-        <v>0.0001470973757840693</v>
+        <v>0.0001588990082051605</v>
       </c>
       <c r="F151" t="n">
-        <v>0.007116015258125146</v>
+        <v>0.007273977912786199</v>
       </c>
       <c r="G151" t="n">
-        <v>0.000189152491475694</v>
+        <v>0.0001876274064830071</v>
       </c>
       <c r="H151" t="n">
-        <v>0.127092282462859</v>
+        <v>0.124274263645463</v>
       </c>
       <c r="I151" t="n">
-        <v>0.00629140135052737</v>
+        <v>0.006464979206963911</v>
       </c>
     </row>
     <row r="152">
@@ -4830,28 +4830,28 @@
         <v>150</v>
       </c>
       <c r="B152" t="n">
-        <v>0.0009641576162576675</v>
+        <v>0.0009737662261426449</v>
       </c>
       <c r="C152" t="n">
-        <v>0.0001847824174882844</v>
+        <v>0.0001842430540155619</v>
       </c>
       <c r="D152" t="n">
-        <v>0.1278014603128433</v>
+        <v>0.1255030790081024</v>
       </c>
       <c r="E152" t="n">
-        <v>0.000140367910775356</v>
+        <v>0.0001620077841291204</v>
       </c>
       <c r="F152" t="n">
-        <v>0.007086679790819255</v>
+        <v>0.006707867049106183</v>
       </c>
       <c r="G152" t="n">
-        <v>0.0001847507959447473</v>
+        <v>0.0001851867434100003</v>
       </c>
       <c r="H152" t="n">
-        <v>0.1275227240442646</v>
+        <v>0.1257037037649902</v>
       </c>
       <c r="I152" t="n">
-        <v>0.006264315460843519</v>
+        <v>0.005894161788761908</v>
       </c>
     </row>
     <row r="153">
@@ -4859,28 +4859,28 @@
         <v>151</v>
       </c>
       <c r="B153" t="n">
-        <v>0.0009605547508113086</v>
+        <v>0.0009745493503808975</v>
       </c>
       <c r="C153" t="n">
-        <v>0.0001856737856045365</v>
+        <v>0.0001847642334122211</v>
       </c>
       <c r="D153" t="n">
-        <v>0.1278011474151611</v>
+        <v>0.1254881322088242</v>
       </c>
       <c r="E153" t="n">
-        <v>0.0001358752327249385</v>
+        <v>0.0001623444683365524</v>
       </c>
       <c r="F153" t="n">
-        <v>0.006913912799604371</v>
+        <v>0.007268895123087076</v>
       </c>
       <c r="G153" t="n">
-        <v>0.0001857999538830717</v>
+        <v>0.0001883120143343201</v>
       </c>
       <c r="H153" t="n">
-        <v>0.1277965597198216</v>
+        <v>0.1250377178065734</v>
       </c>
       <c r="I153" t="n">
-        <v>0.006089130068033763</v>
+        <v>0.006455394539216361</v>
       </c>
     </row>
     <row r="154">
@@ -4888,28 +4888,28 @@
         <v>152</v>
       </c>
       <c r="B154" t="n">
-        <v>0.0009593227597475052</v>
+        <v>0.0009682069008387625</v>
       </c>
       <c r="C154" t="n">
-        <v>0.000184296695780009</v>
+        <v>0.0001862713109711185</v>
       </c>
       <c r="D154" t="n">
-        <v>0.1280686607198715</v>
+        <v>0.1253095279779434</v>
       </c>
       <c r="E154" t="n">
-        <v>0.0001346827691718936</v>
+        <v>0.0001553879623487592</v>
       </c>
       <c r="F154" t="n">
-        <v>0.007075491931720912</v>
+        <v>0.006877310223099556</v>
       </c>
       <c r="G154" t="n">
-        <v>0.0001935327176369657</v>
+        <v>0.0001841260610052596</v>
       </c>
       <c r="H154" t="n">
-        <v>0.1273061823436525</v>
+        <v>0.1264683869466502</v>
       </c>
       <c r="I154" t="n">
-        <v>0.006245428359965516</v>
+        <v>0.006060842273492506</v>
       </c>
     </row>
     <row r="155">
@@ -4917,28 +4917,28 @@
         <v>153</v>
       </c>
       <c r="B155" t="n">
-        <v>0.0009555149687863886</v>
+        <v>0.0009589014205485583</v>
       </c>
       <c r="C155" t="n">
-        <v>0.0001848087568124756</v>
+        <v>0.0001848439101045951</v>
       </c>
       <c r="D155" t="n">
-        <v>0.1280531875925064</v>
+        <v>0.1254258143281937</v>
       </c>
       <c r="E155" t="n">
-        <v>0.0001304402873255312</v>
+        <v>0.000146928459440358</v>
       </c>
       <c r="F155" t="n">
-        <v>0.006935415456578937</v>
+        <v>0.006911043735315224</v>
       </c>
       <c r="G155" t="n">
-        <v>0.000189212243763774</v>
+        <v>0.0001847104569826789</v>
       </c>
       <c r="H155" t="n">
-        <v>0.1284151513949887</v>
+        <v>0.1253824759570071</v>
       </c>
       <c r="I155" t="n">
-        <v>0.006104127524472275</v>
+        <v>0.006099420882712862</v>
       </c>
     </row>
     <row r="156">
@@ -4946,28 +4946,28 @@
         <v>154</v>
       </c>
       <c r="B156" t="n">
-        <v>0.0009512559566274286</v>
+        <v>0.0009556115002445877</v>
       </c>
       <c r="C156" t="n">
-        <v>0.0001852333604851738</v>
+        <v>0.0001833807615209371</v>
       </c>
       <c r="D156" t="n">
-        <v>0.128057686841011</v>
+        <v>0.1257197014260292</v>
       </c>
       <c r="E156" t="n">
-        <v>0.0001257341752341017</v>
+        <v>0.0001436322469161823</v>
       </c>
       <c r="F156" t="n">
-        <v>0.007063938109158594</v>
+        <v>0.006752988243472518</v>
       </c>
       <c r="G156" t="n">
-        <v>0.0001843135322086729</v>
+        <v>0.0001838955290694941</v>
       </c>
       <c r="H156" t="n">
-        <v>0.1274607672718571</v>
+        <v>0.1264504588622642</v>
       </c>
       <c r="I156" t="n">
-        <v>0.006242320762664615</v>
+        <v>0.00593684045057045</v>
       </c>
     </row>
     <row r="157">
@@ -4975,28 +4975,28 @@
         <v>155</v>
       </c>
       <c r="B157" t="n">
-        <v>0.000945807094939053</v>
+        <v>0.0009525582918934524</v>
       </c>
       <c r="C157" t="n">
-        <v>0.0001837260053548962</v>
+        <v>0.0001831924078753218</v>
       </c>
       <c r="D157" t="n">
-        <v>0.1281818969717026</v>
+        <v>0.1259684620351791</v>
       </c>
       <c r="E157" t="n">
-        <v>0.0001211716094752774</v>
+        <v>0.0001395235815504566</v>
       </c>
       <c r="F157" t="n">
-        <v>0.006848723196331868</v>
+        <v>0.007385955517579836</v>
       </c>
       <c r="G157" t="n">
-        <v>0.0001846062987376245</v>
+        <v>0.0001870446906084739</v>
       </c>
       <c r="H157" t="n">
-        <v>0.1287610198185455</v>
+        <v>0.1251852967221819</v>
       </c>
       <c r="I157" t="n">
-        <v>0.006020311759465768</v>
+        <v>0.006572984302778034</v>
       </c>
     </row>
     <row r="158">
@@ -5004,28 +5004,28 @@
         <v>156</v>
       </c>
       <c r="B158" t="n">
-        <v>0.0009433739817999304</v>
+        <v>0.0009544864197149873</v>
       </c>
       <c r="C158" t="n">
-        <v>0.0001842664888594299</v>
+        <v>0.000183426844086498</v>
       </c>
       <c r="D158" t="n">
-        <v>0.1282538335762024</v>
+        <v>0.1260605321245193</v>
       </c>
       <c r="E158" t="n">
-        <v>0.0001178383379308507</v>
+        <v>0.0001407569244988263</v>
       </c>
       <c r="F158" t="n">
-        <v>0.007165439867248932</v>
+        <v>0.006749387519771376</v>
       </c>
       <c r="G158" t="n">
-        <v>0.0001858272529588891</v>
+        <v>0.0001794408604337076</v>
       </c>
       <c r="H158" t="n">
-        <v>0.1275727152970253</v>
+        <v>0.1269778845944179</v>
       </c>
       <c r="I158" t="n">
-        <v>0.00634174900132476</v>
+        <v>0.005935057227273409</v>
       </c>
     </row>
     <row r="159">
@@ -5033,28 +5033,28 @@
         <v>157</v>
       </c>
       <c r="B159" t="n">
-        <v>0.0009424639144539833</v>
+        <v>0.0009495656869523227</v>
       </c>
       <c r="C159" t="n">
-        <v>0.000183809262663126</v>
+        <v>0.0001832775288959965</v>
       </c>
       <c r="D159" t="n">
-        <v>0.1284371304616928</v>
+        <v>0.1262592052755356</v>
       </c>
       <c r="E159" t="n">
-        <v>0.0001164690154660493</v>
+        <v>0.0001349921392169781</v>
       </c>
       <c r="F159" t="n">
-        <v>0.006791565921248756</v>
+        <v>0.007041578205852339</v>
       </c>
       <c r="G159" t="n">
-        <v>0.0001824085673438476</v>
+        <v>0.0001841819099483702</v>
       </c>
       <c r="H159" t="n">
-        <v>0.1294513558913599</v>
+        <v>0.1261452924573208</v>
       </c>
       <c r="I159" t="n">
-        <v>0.005961900542461318</v>
+        <v>0.006226669859754903</v>
       </c>
     </row>
     <row r="160">
@@ -5062,28 +5062,28 @@
         <v>158</v>
       </c>
       <c r="B160" t="n">
-        <v>0.0009408779614455998</v>
+        <v>0.0009432136232629418</v>
       </c>
       <c r="C160" t="n">
-        <v>0.0001831152263982222</v>
+        <v>0.0001830005058869719</v>
       </c>
       <c r="D160" t="n">
-        <v>0.1286083120288849</v>
+        <v>0.1262720756864548</v>
       </c>
       <c r="E160" t="n">
-        <v>0.000114721177842468</v>
+        <v>0.0001288527512270957</v>
       </c>
       <c r="F160" t="n">
-        <v>0.006876352507906676</v>
+        <v>0.007111395825077377</v>
       </c>
       <c r="G160" t="n">
-        <v>0.0001837764805460844</v>
+        <v>0.0001837263557206092</v>
       </c>
       <c r="H160" t="n">
-        <v>0.127991568283778</v>
+        <v>0.126264718952809</v>
       </c>
       <c r="I160" t="n">
-        <v>0.006052618278023372</v>
+        <v>0.006296345849398396</v>
       </c>
     </row>
     <row r="161">
@@ -5091,28 +5091,28 @@
         <v>159</v>
       </c>
       <c r="B161" t="n">
-        <v>0.0009355365040935576</v>
+        <v>0.0009397112474925816</v>
       </c>
       <c r="C161" t="n">
-        <v>0.0001826666255360469</v>
+        <v>0.0001826002901606262</v>
       </c>
       <c r="D161" t="n">
-        <v>0.1286720659599304</v>
+        <v>0.1264439838819504</v>
       </c>
       <c r="E161" t="n">
-        <v>0.0001095095523945056</v>
+        <v>0.0001248910530051217</v>
       </c>
       <c r="F161" t="n">
-        <v>0.00694401650168427</v>
+        <v>0.006829220444620337</v>
       </c>
       <c r="G161" t="n">
-        <v>0.0001817647057173691</v>
+        <v>0.0001802399641308906</v>
       </c>
       <c r="H161" t="n">
-        <v>0.1295589842833275</v>
+        <v>0.1273820577146179</v>
       </c>
       <c r="I161" t="n">
-        <v>0.006114456930591271</v>
+        <v>0.006012070261422077</v>
       </c>
     </row>
     <row r="162">
@@ -5120,28 +5120,28 @@
         <v>160</v>
       </c>
       <c r="B162" t="n">
-        <v>0.0009319588649272919</v>
+        <v>0.0009372506351582706</v>
       </c>
       <c r="C162" t="n">
-        <v>0.0001831483046030626</v>
+        <v>0.0001817455799104646</v>
       </c>
       <c r="D162" t="n">
-        <v>0.1287703987646103</v>
+        <v>0.1268593360595703</v>
       </c>
       <c r="E162" t="n">
-        <v>0.0001049585836441256</v>
+        <v>0.0001212083848686889</v>
       </c>
       <c r="F162" t="n">
-        <v>0.007273382314983725</v>
+        <v>0.006976702069532472</v>
       </c>
       <c r="G162" t="n">
-        <v>0.0001873642271312431</v>
+        <v>0.0001829975585720607</v>
       </c>
       <c r="H162" t="n">
-        <v>0.1276068722696133</v>
+        <v>0.1264497808326905</v>
       </c>
       <c r="I162" t="n">
-        <v>0.006447983695434172</v>
+        <v>0.006161455642826989</v>
       </c>
     </row>
     <row r="163">
@@ -5149,28 +5149,28 @@
         <v>161</v>
       </c>
       <c r="B163" t="n">
-        <v>0.0009297482316493988</v>
+        <v>0.000932958052340895</v>
       </c>
       <c r="C163" t="n">
-        <v>0.0001829293638570234</v>
+        <v>0.0001825728867920116</v>
       </c>
       <c r="D163" t="n">
-        <v>0.1288105258169174</v>
+        <v>0.1266679598731995</v>
       </c>
       <c r="E163" t="n">
-        <v>0.000102766252678819</v>
+        <v>0.0001170453861458227</v>
       </c>
       <c r="F163" t="n">
-        <v>0.006810244834399972</v>
+        <v>0.006862738661553109</v>
       </c>
       <c r="G163" t="n">
-        <v>0.0001834384096814107</v>
+        <v>0.0001791548841123182</v>
       </c>
       <c r="H163" t="n">
-        <v>0.1290087274966388</v>
+        <v>0.1277898997710152</v>
       </c>
       <c r="I163" t="n">
-        <v>0.005981762887360026</v>
+        <v>0.00604463427553947</v>
       </c>
     </row>
     <row r="164">
@@ -5178,28 +5178,28 @@
         <v>162</v>
       </c>
       <c r="B164" t="n">
-        <v>0.0009290276096649468</v>
+        <v>0.0009363978620134294</v>
       </c>
       <c r="C164" t="n">
-        <v>0.0001829586090343073</v>
+        <v>0.0001821430844115093</v>
       </c>
       <c r="D164" t="n">
-        <v>0.128750169013977</v>
+        <v>0.1269010620412827</v>
       </c>
       <c r="E164" t="n">
-        <v>0.00010231817294145</v>
+        <v>0.0001197494854913093</v>
       </c>
       <c r="F164" t="n">
-        <v>0.007021372887939458</v>
+        <v>0.006988576889755189</v>
       </c>
       <c r="G164" t="n">
-        <v>0.0001842403701469712</v>
+        <v>0.0001834476072600242</v>
       </c>
       <c r="H164" t="n">
-        <v>0.1286130369458268</v>
+        <v>0.1263658571301627</v>
       </c>
       <c r="I164" t="n">
-        <v>0.006194067332182584</v>
+        <v>0.00617330004839412</v>
       </c>
     </row>
     <row r="165">
@@ -5207,28 +5207,28 @@
         <v>163</v>
       </c>
       <c r="B165" t="n">
-        <v>0.0009278618951886892</v>
+        <v>0.0009297669699378312</v>
       </c>
       <c r="C165" t="n">
-        <v>0.0001823257738398388</v>
+        <v>0.000182469151917845</v>
       </c>
       <c r="D165" t="n">
-        <v>0.1289451926412582</v>
+        <v>0.1268803436670303</v>
       </c>
       <c r="E165" t="n">
-        <v>0.0001008101725750603</v>
+        <v>0.0001128961160890758</v>
       </c>
       <c r="F165" t="n">
-        <v>0.0069410895142054</v>
+        <v>0.006911310848292286</v>
       </c>
       <c r="G165" t="n">
-        <v>0.00018142903774565</v>
+        <v>0.0001821581482954497</v>
       </c>
       <c r="H165" t="n">
-        <v>0.1293335374086172</v>
+        <v>0.1271984099913966</v>
       </c>
       <c r="I165" t="n">
-        <v>0.006112992815326954</v>
+        <v>0.006093160690524012</v>
       </c>
     </row>
     <row r="166">
@@ -5236,28 +5236,28 @@
         <v>164</v>
       </c>
       <c r="B166" t="n">
-        <v>0.0009229322988018394</v>
+        <v>0.0009303954587131739</v>
       </c>
       <c r="C166" t="n">
-        <v>0.0001821133661307394</v>
+        <v>0.0001821322186551988</v>
       </c>
       <c r="D166" t="n">
-        <v>0.1290434981365204</v>
+        <v>0.1269051725664139</v>
       </c>
       <c r="E166" t="n">
-        <v>9.560145567683503e-05</v>
+        <v>0.0001137373831435107</v>
       </c>
       <c r="F166" t="n">
-        <v>0.007076449484866702</v>
+        <v>0.006897912016518256</v>
       </c>
       <c r="G166" t="n">
-        <v>0.0001835357628868692</v>
+        <v>0.0001803916079027511</v>
       </c>
       <c r="H166" t="n">
-        <v>0.1289214040881075</v>
+        <v>0.1272289421556435</v>
       </c>
       <c r="I166" t="n">
-        <v>0.006248306718185472</v>
+        <v>0.00608137576957803</v>
       </c>
     </row>
     <row r="167">
@@ -5265,28 +5265,28 @@
         <v>165</v>
       </c>
       <c r="B167" t="n">
-        <v>0.0009225183623284101</v>
+        <v>0.0009230175019428134</v>
       </c>
       <c r="C167" t="n">
-        <v>0.0001822066927626729</v>
+        <v>0.000181308088876307</v>
       </c>
       <c r="D167" t="n">
-        <v>0.1290316206178665</v>
+        <v>0.1271617194385529</v>
       </c>
       <c r="E167" t="n">
-        <v>9.51535761076957e-05</v>
+        <v>0.0001059008286213502</v>
       </c>
       <c r="F167" t="n">
-        <v>0.006849110928010104</v>
+        <v>0.006853674553322558</v>
       </c>
       <c r="G167" t="n">
-        <v>0.0001803781405206372</v>
+        <v>0.0001807889425099659</v>
       </c>
       <c r="H167" t="n">
-        <v>0.1295793682735468</v>
+        <v>0.1275373219811702</v>
       </c>
       <c r="I167" t="n">
-        <v>0.006020835857340067</v>
+        <v>0.006035199016606098</v>
       </c>
     </row>
     <row r="168">
@@ -5294,28 +5294,28 @@
         <v>166</v>
       </c>
       <c r="B168" t="n">
-        <v>0.0009215538077317179</v>
+        <v>0.0009227531365454197</v>
       </c>
       <c r="C168" t="n">
-        <v>0.0001819847704451531</v>
+        <v>0.0001811752440566197</v>
       </c>
       <c r="D168" t="n">
-        <v>0.1291103226451874</v>
+        <v>0.1272507929420471</v>
       </c>
       <c r="E168" t="n">
-        <v>9.401743472227827e-05</v>
+        <v>0.0001053239449532703</v>
       </c>
       <c r="F168" t="n">
-        <v>0.007016215749346267</v>
+        <v>0.007135028841846043</v>
       </c>
       <c r="G168" t="n">
-        <v>0.0001822203161349888</v>
+        <v>0.0001835769382863781</v>
       </c>
       <c r="H168" t="n">
-        <v>0.1290947934523298</v>
+        <v>0.1267635687568254</v>
       </c>
       <c r="I168" t="n">
-        <v>0.006188521407040209</v>
+        <v>0.006317634040802766</v>
       </c>
     </row>
     <row r="169">
@@ -5323,28 +5323,28 @@
         <v>167</v>
       </c>
       <c r="B169" t="n">
-        <v>0.0009190861561745405</v>
+        <v>0.0009193733318448066</v>
       </c>
       <c r="C169" t="n">
-        <v>0.0001817651525093243</v>
+        <v>0.0001804127957355231</v>
       </c>
       <c r="D169" t="n">
-        <v>0.1291792641553879</v>
+        <v>0.1274071436939239</v>
       </c>
       <c r="E169" t="n">
-        <v>9.142469695862383e-05</v>
+        <v>0.0001019248366174288</v>
       </c>
       <c r="F169" t="n">
-        <v>0.006780724111415726</v>
+        <v>0.007020020954383819</v>
       </c>
       <c r="G169" t="n">
-        <v>0.0001801193888233838</v>
+        <v>0.0001802200498249303</v>
       </c>
       <c r="H169" t="n">
-        <v>0.1299083043593567</v>
+        <v>0.1272475074768844</v>
       </c>
       <c r="I169" t="n">
-        <v>0.005951063176146048</v>
+        <v>0.006203563334283587</v>
       </c>
     </row>
     <row r="170">
@@ -5352,28 +5352,28 @@
         <v>168</v>
       </c>
       <c r="B170" t="n">
-        <v>0.00091833829510957</v>
+        <v>0.0009192988459020853</v>
       </c>
       <c r="C170" t="n">
-        <v>0.0001811360424337909</v>
+        <v>0.0001802555656088516</v>
       </c>
       <c r="D170" t="n">
-        <v>0.1293608467445373</v>
+        <v>0.1275035112829208</v>
       </c>
       <c r="E170" t="n">
-        <v>9.039802655018867e-05</v>
+        <v>0.0001015257329940796</v>
       </c>
       <c r="F170" t="n">
-        <v>0.007086318654189004</v>
+        <v>0.006903672116955964</v>
       </c>
       <c r="G170" t="n">
-        <v>0.0001828418891127928</v>
+        <v>0.0001798777504490619</v>
       </c>
       <c r="H170" t="n">
-        <v>0.1287680129271736</v>
+        <v>0.1275137490228572</v>
       </c>
       <c r="I170" t="n">
-        <v>0.006259636805251509</v>
+        <v>0.00608622559311315</v>
       </c>
     </row>
     <row r="171">
@@ -5381,28 +5381,28 @@
         <v>169</v>
       </c>
       <c r="B171" t="n">
-        <v>0.0009167469326853752</v>
+        <v>0.0009186007460728287</v>
       </c>
       <c r="C171" t="n">
-        <v>0.0001812663780115545</v>
+        <v>0.0001807817819705233</v>
       </c>
       <c r="D171" t="n">
-        <v>0.1293686338739395</v>
+        <v>0.1275096709384918</v>
       </c>
       <c r="E171" t="n">
-        <v>8.863741151569411e-05</v>
+        <v>0.0001002706241779961</v>
       </c>
       <c r="F171" t="n">
-        <v>0.007093723203263702</v>
+        <v>0.006804359596508265</v>
       </c>
       <c r="G171" t="n">
-        <v>0.0001807411352638155</v>
+        <v>0.0001795807759297273</v>
       </c>
       <c r="H171" t="n">
-        <v>0.1294198383310685</v>
+        <v>0.1280775448509764</v>
       </c>
       <c r="I171" t="n">
-        <v>0.006265882877222768</v>
+        <v>0.005984391148337338</v>
       </c>
     </row>
     <row r="172">
@@ -5410,28 +5410,28 @@
         <v>170</v>
       </c>
       <c r="B172" t="n">
-        <v>0.0009158492847457528</v>
+        <v>0.0009156522966958583</v>
       </c>
       <c r="C172" t="n">
-        <v>0.0001804470305331051</v>
+        <v>0.0001811985079245642</v>
       </c>
       <c r="D172" t="n">
-        <v>0.1295861844329834</v>
+        <v>0.1274736299552917</v>
       </c>
       <c r="E172" t="n">
-        <v>8.747134947078303e-05</v>
+        <v>9.708564957231283e-05</v>
       </c>
       <c r="F172" t="n">
-        <v>0.006991210363951146</v>
+        <v>0.007255402493243505</v>
       </c>
       <c r="G172" t="n">
-        <v>0.0001804312291472685</v>
+        <v>0.0001828435684152048</v>
       </c>
       <c r="H172" t="n">
-        <v>0.1298849106253069</v>
+        <v>0.1270503606347042</v>
       </c>
       <c r="I172" t="n">
-        <v>0.006161354573847662</v>
+        <v>0.006437307216385061</v>
       </c>
     </row>
     <row r="173">
@@ -5439,28 +5439,28 @@
         <v>171</v>
       </c>
       <c r="B173" t="n">
-        <v>0.0009139660004749894</v>
+        <v>0.0009164279275685549</v>
       </c>
       <c r="C173" t="n">
-        <v>0.0001808884817566723</v>
+        <v>0.0001803557121939957</v>
       </c>
       <c r="D173" t="n">
-        <v>0.1295806819257736</v>
+        <v>0.127682396525383</v>
       </c>
       <c r="E173" t="n">
-        <v>8.517413281090558e-05</v>
+        <v>9.766024975571781e-05</v>
       </c>
       <c r="F173" t="n">
-        <v>0.00700109450465606</v>
+        <v>0.007061621441641065</v>
       </c>
       <c r="G173" t="n">
-        <v>0.0001817515006989277</v>
+        <v>0.0001795285539581937</v>
       </c>
       <c r="H173" t="n">
-        <v>0.1292357104987538</v>
+        <v>0.1278339860013414</v>
       </c>
       <c r="I173" t="n">
-        <v>0.006173164512001914</v>
+        <v>0.006242922893429074</v>
       </c>
     </row>
     <row r="174">
@@ -5468,28 +5468,28 @@
         <v>172</v>
       </c>
       <c r="B174" t="n">
-        <v>0.0009118225229941308</v>
+        <v>0.0009156526324041187</v>
       </c>
       <c r="C174" t="n">
-        <v>0.0001809152272455394</v>
+        <v>0.0001799436730807647</v>
       </c>
       <c r="D174" t="n">
-        <v>0.1295234503164291</v>
+        <v>0.1278011195793152</v>
       </c>
       <c r="E174" t="n">
-        <v>8.329006747202948e-05</v>
+        <v>9.670337467733771e-05</v>
       </c>
       <c r="F174" t="n">
-        <v>0.006876345909767302</v>
+        <v>0.007025864282486197</v>
       </c>
       <c r="G174" t="n">
-        <v>0.0001799935371708809</v>
+        <v>0.0001807897202355322</v>
       </c>
       <c r="H174" t="n">
-        <v>0.1296689850685064</v>
+        <v>0.1275226171710946</v>
       </c>
       <c r="I174" t="n">
-        <v>0.006048007484944765</v>
+        <v>0.006207461567446711</v>
       </c>
     </row>
     <row r="175">
@@ -5497,28 +5497,28 @@
         <v>173</v>
       </c>
       <c r="B175" t="n">
-        <v>0.0009133351953998208</v>
+        <v>0.0009125213689506054</v>
       </c>
       <c r="C175" t="n">
-        <v>0.0001809177011987195</v>
+        <v>0.0001799840008188039</v>
       </c>
       <c r="D175" t="n">
-        <v>0.1295855832262039</v>
+        <v>0.1278725338106155</v>
       </c>
       <c r="E175" t="n">
-        <v>8.448959037754684e-05</v>
+        <v>9.317470483388752e-05</v>
       </c>
       <c r="F175" t="n">
-        <v>0.006833003832127589</v>
+        <v>0.006913338383693145</v>
       </c>
       <c r="G175" t="n">
-        <v>0.0001790023351657519</v>
+        <v>0.0001792753569411074</v>
       </c>
       <c r="H175" t="n">
-        <v>0.1300481320001173</v>
+        <v>0.1279690523209813</v>
       </c>
       <c r="I175" t="n">
-        <v>0.006003760843496727</v>
+        <v>0.006094217717550319</v>
       </c>
     </row>
     <row r="176">
@@ -5526,28 +5526,28 @@
         <v>174</v>
       </c>
       <c r="B176" t="n">
-        <v>0.0009109839295968413</v>
+        <v>0.0009122265440300107</v>
       </c>
       <c r="C176" t="n">
-        <v>0.0001809185127224773</v>
+        <v>0.0001798605665415526</v>
       </c>
       <c r="D176" t="n">
-        <v>0.1295487993021011</v>
+        <v>0.1279302690525055</v>
       </c>
       <c r="E176" t="n">
-        <v>8.232143339747564e-05</v>
+        <v>9.271464416850358e-05</v>
       </c>
       <c r="F176" t="n">
-        <v>0.007012404167742072</v>
+        <v>0.006920446842744776</v>
       </c>
       <c r="G176" t="n">
-        <v>0.0001817134490111679</v>
+        <v>0.0001791092836705217</v>
       </c>
       <c r="H176" t="n">
-        <v>0.1295334129971353</v>
+        <v>0.128086076964173</v>
       </c>
       <c r="I176" t="n">
-        <v>0.006183023648685965</v>
+        <v>0.006100907174332544</v>
       </c>
     </row>
     <row r="177">
@@ -5555,28 +5555,28 @@
         <v>175</v>
       </c>
       <c r="B177" t="n">
-        <v>0.0009098926831297577</v>
+        <v>0.000912136484939605</v>
       </c>
       <c r="C177" t="n">
-        <v>0.0001805915833227336</v>
+        <v>0.000179320043628104</v>
       </c>
       <c r="D177" t="n">
-        <v>0.1297032064113617</v>
+        <v>0.1280137103948593</v>
       </c>
       <c r="E177" t="n">
-        <v>8.078509237384423e-05</v>
+        <v>9.274791023228318e-05</v>
       </c>
       <c r="F177" t="n">
-        <v>0.007055954855318268</v>
+        <v>0.006949816927599431</v>
       </c>
       <c r="G177" t="n">
-        <v>0.0001809682765482586</v>
+        <v>0.0001799737935871354</v>
       </c>
       <c r="H177" t="n">
-        <v>0.1296621025279529</v>
+        <v>0.1278946257979407</v>
       </c>
       <c r="I177" t="n">
-        <v>0.006226676080017359</v>
+        <v>0.006130370154679064</v>
       </c>
     </row>
     <row r="178">
@@ -5584,28 +5584,28 @@
         <v>176</v>
       </c>
       <c r="B178" t="n">
-        <v>0.0009095525967031717</v>
+        <v>0.0009098093328885734</v>
       </c>
       <c r="C178" t="n">
-        <v>0.000180490820594132</v>
+        <v>0.0001794404258802533</v>
       </c>
       <c r="D178" t="n">
-        <v>0.1296868330917358</v>
+        <v>0.1281055097236633</v>
       </c>
       <c r="E178" t="n">
-        <v>8.062761449581012e-05</v>
+        <v>8.98413685890846e-05</v>
       </c>
       <c r="F178" t="n">
-        <v>0.006924358580723332</v>
+        <v>0.006844231985011069</v>
       </c>
       <c r="G178" t="n">
-        <v>0.000180287302653442</v>
+        <v>0.0001779452495614589</v>
       </c>
       <c r="H178" t="n">
-        <v>0.1297232314550468</v>
+        <v>0.1284701880934188</v>
       </c>
       <c r="I178" t="n">
-        <v>0.006095455030031004</v>
+        <v>0.006023935765350088</v>
       </c>
     </row>
     <row r="179">
@@ -5613,28 +5613,28 @@
         <v>177</v>
       </c>
       <c r="B179" t="n">
-        <v>0.0009083287722058594</v>
+        <v>0.0009091527126468718</v>
       </c>
       <c r="C179" t="n">
-        <v>0.0001809554248359054</v>
+        <v>0.000179663527042605</v>
       </c>
       <c r="D179" t="n">
-        <v>0.1295810557489395</v>
+        <v>0.1280961288480759</v>
       </c>
       <c r="E179" t="n">
-        <v>7.946808344265446e-05</v>
+        <v>8.900855588680134e-05</v>
       </c>
       <c r="F179" t="n">
-        <v>0.006994617265933247</v>
+        <v>0.007005056508013076</v>
       </c>
       <c r="G179" t="n">
-        <v>0.0001805643425587045</v>
+        <v>0.0001799385684472471</v>
       </c>
       <c r="H179" t="n">
-        <v>0.1296805970198179</v>
+        <v>0.1280767360470618</v>
       </c>
       <c r="I179" t="n">
-        <v>0.006165649954709688</v>
+        <v>0.006184734272699177</v>
       </c>
     </row>
     <row r="180">
@@ -5642,28 +5642,28 @@
         <v>178</v>
       </c>
       <c r="B180" t="n">
-        <v>0.000909230010509491</v>
+        <v>0.0009086345981061458</v>
       </c>
       <c r="C180" t="n">
-        <v>0.0001799521889062598</v>
+        <v>0.000179352471630089</v>
       </c>
       <c r="D180" t="n">
-        <v>0.1298324233970642</v>
+        <v>0.1281920445051193</v>
       </c>
       <c r="E180" t="n">
-        <v>8.011572151212022e-05</v>
+        <v>8.832191363256424e-05</v>
       </c>
       <c r="F180" t="n">
-        <v>0.006939548397433699</v>
+        <v>0.006897125924659397</v>
       </c>
       <c r="G180" t="n">
-        <v>0.0001808737344015466</v>
+        <v>0.0001789711944213468</v>
       </c>
       <c r="H180" t="n">
-        <v>0.1297209703309695</v>
+        <v>0.1282941676450204</v>
       </c>
       <c r="I180" t="n">
-        <v>0.006110069760156349</v>
+        <v>0.006076683883614486</v>
       </c>
     </row>
     <row r="181">
@@ -5671,28 +5671,28 @@
         <v>179</v>
       </c>
       <c r="B181" t="n">
-        <v>0.0009064397771880031</v>
+        <v>0.0009086155869625509</v>
       </c>
       <c r="C181" t="n">
-        <v>0.00018030753512308</v>
+        <v>0.0001792971227923408</v>
       </c>
       <c r="D181" t="n">
-        <v>0.1297488643827438</v>
+        <v>0.1282191475095749</v>
       </c>
       <c r="E181" t="n">
-        <v>7.738793548569083e-05</v>
+        <v>8.822274313541129e-05</v>
       </c>
       <c r="F181" t="n">
-        <v>0.006910798654057462</v>
+        <v>0.006860602944390468</v>
       </c>
       <c r="G181" t="n">
-        <v>0.0001791865256002331</v>
+        <v>0.0001776710348509535</v>
       </c>
       <c r="H181" t="n">
-        <v>0.1299920529166015</v>
+        <v>0.1285235832040889</v>
       </c>
       <c r="I181" t="n">
-        <v>0.006081651901768529</v>
+        <v>0.006040314003357247</v>
       </c>
     </row>
     <row r="182">
@@ -5700,28 +5700,28 @@
         <v>180</v>
       </c>
       <c r="B182" t="n">
-        <v>0.000907193412847817</v>
+        <v>0.0009072826956436038</v>
       </c>
       <c r="C182" t="n">
-        <v>0.0001800118079017848</v>
+        <v>0.000178774138841778</v>
       </c>
       <c r="D182" t="n">
-        <v>0.1297962924127579</v>
+        <v>0.1283741673688888</v>
       </c>
       <c r="E182" t="n">
-        <v>7.820016407314688e-05</v>
+        <v>8.663774280436336e-05</v>
       </c>
       <c r="F182" t="n">
-        <v>0.00702238635128124</v>
+        <v>0.00697062106046455</v>
       </c>
       <c r="G182" t="n">
-        <v>0.0001805091588161612</v>
+        <v>0.0001793069078539138</v>
       </c>
       <c r="H182" t="n">
-        <v>0.1296722180419412</v>
+        <v>0.1283277439507147</v>
       </c>
       <c r="I182" t="n">
-        <v>0.006193516068312463</v>
+        <v>0.006149675413163995</v>
       </c>
     </row>
     <row r="183">
@@ -5729,28 +5729,28 @@
         <v>181</v>
       </c>
       <c r="B183" t="n">
-        <v>0.0009063946623913944</v>
+        <v>0.0009076065068691969</v>
       </c>
       <c r="C183" t="n">
-        <v>0.0001801242897771299</v>
+        <v>0.0001794059205045924</v>
       </c>
       <c r="D183" t="n">
-        <v>0.1298233037433624</v>
+        <v>0.1283153974733353</v>
       </c>
       <c r="E183" t="n">
-        <v>7.715386919304729e-05</v>
+        <v>8.662361870333553e-05</v>
       </c>
       <c r="F183" t="n">
-        <v>0.006985107894992945</v>
+        <v>0.006893131665940143</v>
       </c>
       <c r="G183" t="n">
-        <v>0.0001801022533511554</v>
+        <v>0.0001783200539107287</v>
       </c>
       <c r="H183" t="n">
-        <v>0.1297624225007768</v>
+        <v>0.1283885038122656</v>
       </c>
       <c r="I183" t="n">
-        <v>0.006156193486385983</v>
+        <v>0.00607286906514019</v>
       </c>
     </row>
     <row r="184">
@@ -5758,28 +5758,28 @@
         <v>182</v>
       </c>
       <c r="B184" t="n">
-        <v>0.0009050116757974029</v>
+        <v>0.0009065807970687747</v>
       </c>
       <c r="C184" t="n">
-        <v>0.000179915537212044</v>
+        <v>0.0001790497364187613</v>
       </c>
       <c r="D184" t="n">
-        <v>0.1298346451349258</v>
+        <v>0.1283428901987076</v>
       </c>
       <c r="E184" t="n">
-        <v>7.592292129760609e-05</v>
+        <v>8.58166211405769e-05</v>
       </c>
       <c r="F184" t="n">
-        <v>0.006961546045884514</v>
+        <v>0.006943688240892833</v>
       </c>
       <c r="G184" t="n">
-        <v>0.0001807263077718705</v>
+        <v>0.0001781549074323954</v>
       </c>
       <c r="H184" t="n">
-        <v>0.1296368768475767</v>
+        <v>0.1285760274155105</v>
       </c>
       <c r="I184" t="n">
-        <v>0.006132635423703937</v>
+        <v>0.00612265323916204</v>
       </c>
     </row>
     <row r="185">
@@ -5787,28 +5787,28 @@
         <v>183</v>
       </c>
       <c r="B185" t="n">
-        <v>0.0009054226484745741</v>
+        <v>0.0009065132868438959</v>
       </c>
       <c r="C185" t="n">
-        <v>0.0001799724299646914</v>
+        <v>0.0001790225339373574</v>
       </c>
       <c r="D185" t="n">
-        <v>0.1298105901556015</v>
+        <v>0.1284149335346222</v>
       </c>
       <c r="E185" t="n">
-        <v>7.639728210493923e-05</v>
+        <v>8.541610149433836e-05</v>
       </c>
       <c r="F185" t="n">
-        <v>0.006948853177102025</v>
+        <v>0.006970152116667777</v>
       </c>
       <c r="G185" t="n">
-        <v>0.0001788282179078816</v>
+        <v>0.0001789238598242517</v>
       </c>
       <c r="H185" t="n">
-        <v>0.1301024284574764</v>
+        <v>0.1283712242371106</v>
       </c>
       <c r="I185" t="n">
-        <v>0.006119512724029249</v>
+        <v>0.006149372135639968</v>
       </c>
     </row>
     <row r="186">
@@ -5816,28 +5816,28 @@
         <v>184</v>
       </c>
       <c r="B186" t="n">
-        <v>0.0009040224729627371</v>
+        <v>0.0009047861115038395</v>
       </c>
       <c r="C186" t="n">
-        <v>0.0001795740613611415</v>
+        <v>0.0001788408694248646</v>
       </c>
       <c r="D186" t="n">
-        <v>0.1299244408073425</v>
+        <v>0.1284554483222961</v>
       </c>
       <c r="E186" t="n">
-        <v>7.48262144853361e-05</v>
+        <v>8.366801650263369e-05</v>
       </c>
       <c r="F186" t="n">
-        <v>0.006946215925595403</v>
+        <v>0.006926343559787333</v>
       </c>
       <c r="G186" t="n">
-        <v>0.000178742737141453</v>
+        <v>0.0001789085433794091</v>
       </c>
       <c r="H186" t="n">
-        <v>0.1300461839705851</v>
+        <v>0.1284776831120496</v>
       </c>
       <c r="I186" t="n">
-        <v>0.006117242308938192</v>
+        <v>0.006105046556931336</v>
       </c>
     </row>
     <row r="187">
@@ -5845,28 +5845,28 @@
         <v>185</v>
       </c>
       <c r="B187" t="n">
-        <v>0.0009037465178482235</v>
+        <v>0.0009052135761640966</v>
       </c>
       <c r="C187" t="n">
-        <v>0.0001795272622816265</v>
+        <v>0.0001790025074193254</v>
       </c>
       <c r="D187" t="n">
-        <v>0.1299315354690552</v>
+        <v>0.1284569681959152</v>
       </c>
       <c r="E187" t="n">
-        <v>7.456159306829796e-05</v>
+        <v>8.392624020483345e-05</v>
       </c>
       <c r="F187" t="n">
-        <v>0.006960167603029415</v>
+        <v>0.006878278440238261</v>
       </c>
       <c r="G187" t="n">
-        <v>0.0001797262835107458</v>
+        <v>0.0001784386045487862</v>
       </c>
       <c r="H187" t="n">
-        <v>0.1298331453030105</v>
+        <v>0.1285033058945156</v>
       </c>
       <c r="I187" t="n">
-        <v>0.006131275592198623</v>
+        <v>0.006057323351484187</v>
       </c>
     </row>
     <row r="188">
@@ -5874,28 +5874,28 @@
         <v>186</v>
       </c>
       <c r="B188" t="n">
-        <v>0.0009031237701587379</v>
+        <v>0.0009042402347028256</v>
       </c>
       <c r="C188" t="n">
-        <v>0.000179928149423562</v>
+        <v>0.0001789090209444985</v>
       </c>
       <c r="D188" t="n">
-        <v>0.1298691840515137</v>
+        <v>0.128452410697937</v>
       </c>
       <c r="E188" t="n">
-        <v>7.384972127806396e-05</v>
+        <v>8.306917294580489e-05</v>
       </c>
       <c r="F188" t="n">
-        <v>0.006984034680304092</v>
+        <v>0.006976654773386617</v>
       </c>
       <c r="G188" t="n">
-        <v>0.0001797787068912313</v>
+        <v>0.0001797177148018136</v>
       </c>
       <c r="H188" t="n">
-        <v>0.1298380033207562</v>
+        <v>0.1282477713117397</v>
       </c>
       <c r="I188" t="n">
-        <v>0.006155065914181473</v>
+        <v>0.006155698258296069</v>
       </c>
     </row>
     <row r="189">
@@ -5903,28 +5903,28 @@
         <v>187</v>
       </c>
       <c r="B189" t="n">
-        <v>0.0009032550000697375</v>
+        <v>0.0009049659644402564</v>
       </c>
       <c r="C189" t="n">
-        <v>0.0001798411010811105</v>
+        <v>0.0001792468309486285</v>
       </c>
       <c r="D189" t="n">
-        <v>0.129866810046196</v>
+        <v>0.1284261376619339</v>
       </c>
       <c r="E189" t="n">
-        <v>7.407987109990791e-05</v>
+        <v>8.35884562204592e-05</v>
       </c>
       <c r="F189" t="n">
-        <v>0.006996916439414608</v>
+        <v>0.006954863029448574</v>
       </c>
       <c r="G189" t="n">
-        <v>0.0001806150067090186</v>
+        <v>0.0001791279913886446</v>
       </c>
       <c r="H189" t="n">
-        <v>0.1296515401337314</v>
+        <v>0.1284308222991218</v>
       </c>
       <c r="I189" t="n">
-        <v>0.006168043786510946</v>
+        <v>0.006133580937568359</v>
       </c>
     </row>
     <row r="190">
@@ -5932,28 +5932,28 @@
         <v>188</v>
       </c>
       <c r="B190" t="n">
-        <v>0.0009029820164069534</v>
+        <v>0.0009036151638068258</v>
       </c>
       <c r="C190" t="n">
-        <v>0.0001801185762891546</v>
+        <v>0.0001789224227285013</v>
       </c>
       <c r="D190" t="n">
-        <v>0.1298138453845978</v>
+        <v>0.1285018975458145</v>
       </c>
       <c r="E190" t="n">
-        <v>7.379422225058079e-05</v>
+        <v>8.218326614890247e-05</v>
       </c>
       <c r="F190" t="n">
-        <v>0.006993760204529101</v>
+        <v>0.006944487608124488</v>
       </c>
       <c r="G190" t="n">
-        <v>0.0001798623769103852</v>
+        <v>0.0001786110187483022</v>
       </c>
       <c r="H190" t="n">
-        <v>0.1297730466844985</v>
+        <v>0.1285085919163939</v>
       </c>
       <c r="I190" t="n">
-        <v>0.006165032631567213</v>
+        <v>0.006123333629524582</v>
       </c>
     </row>
     <row r="191">
@@ -5961,28 +5961,28 @@
         <v>189</v>
       </c>
       <c r="B191" t="n">
-        <v>0.0009025831493288278</v>
+        <v>0.0009034850243963301</v>
       </c>
       <c r="C191" t="n">
-        <v>0.0001797504443116486</v>
+        <v>0.0001789223926356062</v>
       </c>
       <c r="D191" t="n">
-        <v>0.1298772953805923</v>
+        <v>0.1285037363491058</v>
       </c>
       <c r="E191" t="n">
-        <v>7.34462467059493e-05</v>
+        <v>8.204397745383903e-05</v>
       </c>
       <c r="F191" t="n">
-        <v>0.006965636544379285</v>
+        <v>0.006966507757252742</v>
       </c>
       <c r="G191" t="n">
-        <v>0.0001795597327056494</v>
+        <v>0.0001787539534889873</v>
       </c>
       <c r="H191" t="n">
-        <v>0.129900554299938</v>
+        <v>0.1285051246033602</v>
       </c>
       <c r="I191" t="n">
-        <v>0.0061365740800954</v>
+        <v>0.006145228124216053</v>
       </c>
     </row>
     <row r="192">
@@ -5990,28 +5990,28 @@
         <v>190</v>
       </c>
       <c r="B192" t="n">
-        <v>0.0009020900545082986</v>
+        <v>0.000903064148016274</v>
       </c>
       <c r="C192" t="n">
-        <v>0.0001795914839860052</v>
+        <v>0.0001788532977700234</v>
       </c>
       <c r="D192" t="n">
-        <v>0.1299156475839615</v>
+        <v>0.1285147590236664</v>
       </c>
       <c r="E192" t="n">
-        <v>7.292035821685567e-05</v>
+        <v>8.16370774297975e-05</v>
       </c>
       <c r="F192" t="n">
-        <v>0.006950722856516988</v>
+        <v>0.006946411252015713</v>
       </c>
       <c r="G192" t="n">
-        <v>0.0001794466913381871</v>
+        <v>0.000178654692174683</v>
       </c>
       <c r="H192" t="n">
-        <v>0.1299009562695785</v>
+        <v>0.1285335245305523</v>
       </c>
       <c r="I192" t="n">
-        <v>0.006121771431924565</v>
+        <v>0.006125088978412927</v>
       </c>
     </row>
     <row r="193">
@@ -6019,28 +6019,28 @@
         <v>191</v>
       </c>
       <c r="B193" t="n">
-        <v>0.0009008878484219313</v>
+        <v>0.0009044133328720927</v>
       </c>
       <c r="C193" t="n">
-        <v>0.0001794932495392859</v>
+        <v>0.0001787572167264298</v>
       </c>
       <c r="D193" t="n">
-        <v>0.1299128892364502</v>
+        <v>0.1285465660619736</v>
       </c>
       <c r="E193" t="n">
-        <v>7.183017160929739e-05</v>
+        <v>8.292329421034083e-05</v>
       </c>
       <c r="F193" t="n">
-        <v>0.006995431982394046</v>
+        <v>0.006960839177580584</v>
       </c>
       <c r="G193" t="n">
-        <v>0.0001794896343182453</v>
+        <v>0.0001788076694479719</v>
       </c>
       <c r="H193" t="n">
-        <v>0.1298464765994039</v>
+        <v>0.1284825458864987</v>
       </c>
       <c r="I193" t="n">
-        <v>0.006166709929364346</v>
+        <v>0.006139618745180027</v>
       </c>
     </row>
     <row r="194">
@@ -6048,28 +6048,28 @@
         <v>192</v>
       </c>
       <c r="B194" t="n">
-        <v>0.000901061641857028</v>
+        <v>0.0009035277457237244</v>
       </c>
       <c r="C194" t="n">
-        <v>0.0001793666751272976</v>
+        <v>0.0001789482682133093</v>
       </c>
       <c r="D194" t="n">
-        <v>0.129941777009964</v>
+        <v>0.1285036767082214</v>
       </c>
       <c r="E194" t="n">
-        <v>7.198609031224623e-05</v>
+        <v>8.206112036248669e-05</v>
       </c>
       <c r="F194" t="n">
-        <v>0.006977161623683392</v>
+        <v>0.006966650888724875</v>
       </c>
       <c r="G194" t="n">
-        <v>0.0001793160854301721</v>
+        <v>0.0001787196172702887</v>
       </c>
       <c r="H194" t="n">
-        <v>0.1299342980509287</v>
+        <v>0.1284926485529148</v>
       </c>
       <c r="I194" t="n">
-        <v>0.006148174061161902</v>
+        <v>0.006145468000170652</v>
       </c>
     </row>
     <row r="195">
@@ -6077,28 +6077,28 @@
         <v>193</v>
       </c>
       <c r="B195" t="n">
-        <v>0.0009018073288835585</v>
+        <v>0.0009020052794255316</v>
       </c>
       <c r="C195" t="n">
-        <v>0.0001794418027652428</v>
+        <v>0.0001787898263614625</v>
       </c>
       <c r="D195" t="n">
-        <v>0.1299273203754425</v>
+        <v>0.1285431738204956</v>
       </c>
       <c r="E195" t="n">
-        <v>7.272893290640786e-05</v>
+        <v>8.049960039835423e-05</v>
       </c>
       <c r="F195" t="n">
-        <v>0.006970737583959569</v>
+        <v>0.006958731326470562</v>
       </c>
       <c r="G195" t="n">
-        <v>0.0001795030025944576</v>
+        <v>0.0001787171671569627</v>
       </c>
       <c r="H195" t="n">
-        <v>0.1298844876394381</v>
+        <v>0.1285116920580094</v>
       </c>
       <c r="I195" t="n">
-        <v>0.00614181214183885</v>
+        <v>0.006137455682806537</v>
       </c>
     </row>
     <row r="196">
@@ -6106,28 +6106,28 @@
         <v>194</v>
       </c>
       <c r="B196" t="n">
-        <v>0.0009018940742313862</v>
+        <v>0.0009017031915485859</v>
       </c>
       <c r="C196" t="n">
-        <v>0.0001793613552004099</v>
+        <v>0.0001786265959786251</v>
       </c>
       <c r="D196" t="n">
-        <v>0.1299351820869446</v>
+        <v>0.1285648160457611</v>
       </c>
       <c r="E196" t="n">
-        <v>7.285681242472491e-05</v>
+        <v>8.02525341110304e-05</v>
       </c>
       <c r="F196" t="n">
-        <v>0.006964339130356008</v>
+        <v>0.006968467826415674</v>
       </c>
       <c r="G196" t="n">
-        <v>0.0001794402041551497</v>
+        <v>0.0001787032680867049</v>
       </c>
       <c r="H196" t="n">
-        <v>0.129913163092747</v>
+        <v>0.1285096002743256</v>
       </c>
       <c r="I196" t="n">
-        <v>0.006135333094040926</v>
+        <v>0.006147216588143278</v>
       </c>
     </row>
     <row r="197">
@@ -6135,28 +6135,28 @@
         <v>195</v>
       </c>
       <c r="B197" t="n">
-        <v>0.0009010952806249261</v>
+        <v>0.0009024197128787636</v>
       </c>
       <c r="C197" t="n">
-        <v>0.000179361783103086</v>
+        <v>0.0001786792895691469</v>
       </c>
       <c r="D197" t="n">
-        <v>0.1299498178920746</v>
+        <v>0.1285605328102112</v>
       </c>
       <c r="E197" t="n">
-        <v>7.198442291747779e-05</v>
+        <v>8.09377788840793e-05</v>
       </c>
       <c r="F197" t="n">
-        <v>0.006959831857199964</v>
+        <v>0.006971504844293655</v>
       </c>
       <c r="G197" t="n">
-        <v>0.0001792623633750506</v>
+        <v>0.0001786867502338419</v>
       </c>
       <c r="H197" t="n">
-        <v>0.1299468875096634</v>
+        <v>0.1285386259472195</v>
       </c>
       <c r="I197" t="n">
-        <v>0.006130835053345361</v>
+        <v>0.006150124926715603</v>
       </c>
     </row>
     <row r="198">
@@ -6164,28 +6164,28 @@
         <v>196</v>
       </c>
       <c r="B198" t="n">
-        <v>0.0009017061603218317</v>
+        <v>0.0009022785867899656</v>
       </c>
       <c r="C198" t="n">
-        <v>0.0001793754595667124</v>
+        <v>0.0001787874727100134</v>
       </c>
       <c r="D198" t="n">
-        <v>0.1299520036935806</v>
+        <v>0.1285570301923752</v>
       </c>
       <c r="E198" t="n">
-        <v>7.257070820126683e-05</v>
+        <v>8.0705977876205e-05</v>
       </c>
       <c r="F198" t="n">
-        <v>0.006967123854376655</v>
+        <v>0.006951964089941677</v>
       </c>
       <c r="G198" t="n">
-        <v>0.0001793192158144371</v>
+        <v>0.0001787452751492966</v>
       </c>
       <c r="H198" t="n">
-        <v>0.1299286692828961</v>
+        <v>0.1285318257048313</v>
       </c>
       <c r="I198" t="n">
-        <v>0.006138161371323792</v>
+        <v>0.006130559735036597</v>
       </c>
     </row>
     <row r="199">
@@ -6193,28 +6193,28 @@
         <v>197</v>
       </c>
       <c r="B199" t="n">
-        <v>0.0009009758109264076</v>
+        <v>0.000901635171316564</v>
       </c>
       <c r="C199" t="n">
-        <v>0.0001794149437975139</v>
+        <v>0.0001787068844102323</v>
       </c>
       <c r="D199" t="n">
-        <v>0.1299507402029038</v>
+        <v>0.1285673098478317</v>
       </c>
       <c r="E199" t="n">
-        <v>7.180716958502308e-05</v>
+        <v>8.009175976878032e-05</v>
       </c>
       <c r="F199" t="n">
-        <v>0.006966843496685996</v>
+        <v>0.006966162860138284</v>
       </c>
       <c r="G199" t="n">
-        <v>0.0001793265587830275</v>
+        <v>0.0001787412122355738</v>
       </c>
       <c r="H199" t="n">
-        <v>0.129925181950286</v>
+        <v>0.1285159938467657</v>
       </c>
       <c r="I199" t="n">
-        <v>0.006137891068301038</v>
+        <v>0.006144841665593485</v>
       </c>
     </row>
     <row r="200">
@@ -6222,28 +6222,28 @@
         <v>198</v>
       </c>
       <c r="B200" t="n">
-        <v>0.0009010776671022177</v>
+        <v>0.0009028240031264723</v>
       </c>
       <c r="C200" t="n">
-        <v>0.0001794691711068153</v>
+        <v>0.0001787583185918629</v>
       </c>
       <c r="D200" t="n">
-        <v>0.129955365067482</v>
+        <v>0.1285544088554382</v>
       </c>
       <c r="E200" t="n">
-        <v>7.183168232487515e-05</v>
+        <v>8.129364572511985e-05</v>
       </c>
       <c r="F200" t="n">
-        <v>0.006967995686192205</v>
+        <v>0.006963790897705378</v>
       </c>
       <c r="G200" t="n">
-        <v>0.0001794264087970801</v>
+        <v>0.0001786894286465398</v>
       </c>
       <c r="H200" t="n">
-        <v>0.1299139678147644</v>
+        <v>0.1285246088250037</v>
       </c>
       <c r="I200" t="n">
-        <v>0.006138999460699557</v>
+        <v>0.006142478450634448</v>
       </c>
     </row>
     <row r="201">
@@ -6251,28 +6251,28 @@
         <v>199</v>
       </c>
       <c r="B201" t="n">
-        <v>0.0009006171423830092</v>
+        <v>0.0009017952824495733</v>
       </c>
       <c r="C201" t="n">
-        <v>0.0001793843994177878</v>
+        <v>0.0001787073863530532</v>
       </c>
       <c r="D201" t="n">
-        <v>0.1299480014925003</v>
+        <v>0.1285584063835144</v>
       </c>
       <c r="E201" t="n">
-        <v>7.14927539746277e-05</v>
+        <v>8.02958761448972e-05</v>
       </c>
       <c r="F201" t="n">
-        <v>0.006974942139661332</v>
+        <v>0.006970964612083762</v>
       </c>
       <c r="G201" t="n">
-        <v>0.000179386441913953</v>
+        <v>0.0001786875799968671</v>
       </c>
       <c r="H201" t="n">
-        <v>0.1299132439839315</v>
+        <v>0.128525003619723</v>
       </c>
       <c r="I201" t="n">
-        <v>0.006145989441420719</v>
+        <v>0.006149651961215752</v>
       </c>
     </row>
   </sheetData>
